--- a/260729_K5M_Project Calendar.xlsx
+++ b/260729_K5M_Project Calendar.xlsx
@@ -14,11 +14,11 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Oct 2026" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Nov 2026" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dec 2026" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Deadlines Summary" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Hard Milestones" sheetId="8" state="visible" r:id="rId8"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Project Development Log" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Data'!$A$4:$F$50</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Data'!$A$5:$I$53</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -27,7 +27,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="7">
+  <fonts count="11">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -43,14 +43,20 @@
     </font>
     <font>
       <name val="Lato"/>
-      <i val="1"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Lato"/>
+      <b val="1"/>
       <color rgb="00292B2B"/>
       <sz val="9"/>
     </font>
     <font>
       <name val="Lato"/>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <i val="1"/>
+      <color rgb="00292B2B"/>
       <sz val="9"/>
     </font>
     <font>
@@ -61,17 +67,34 @@
     <font>
       <name val="Lato"/>
       <b val="1"/>
-      <color rgb="00292B2B"/>
-      <sz val="9"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="10"/>
     </font>
     <font>
       <name val="Lato"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
-      <sz val="10"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Lato"/>
+      <color rgb="00292B2B"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Lato"/>
+      <b val="1"/>
+      <color rgb="00292B2B"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Lato"/>
+      <i val="1"/>
+      <color rgb="00E4572E"/>
+      <sz val="7"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="12">
     <fill>
       <patternFill/>
     </fill>
@@ -85,7 +108,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F8F3EE"/>
+        <fgColor rgb="0026547C"/>
       </patternFill>
     </fill>
     <fill>
@@ -95,12 +118,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="0026547C"/>
+        <fgColor rgb="00A7A7A7"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00A7A7A7"/>
+        <fgColor rgb="00F8F3EE"/>
       </patternFill>
     </fill>
     <fill>
@@ -110,17 +133,46 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00AFC5D6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E6D4CE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E2E2E2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00E4572E"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="7">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
       <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color rgb="00E4572E"/>
+      </left>
+      <right style="thick">
+        <color rgb="00E4572E"/>
+      </right>
+      <top style="thick">
+        <color rgb="00E4572E"/>
+      </top>
+      <bottom style="thick">
+        <color rgb="00E4572E"/>
+      </bottom>
     </border>
     <border>
       <left style="thin">
@@ -137,90 +189,155 @@
       </bottom>
     </border>
     <border>
-      <left style="thick">
-        <color rgb="00E4572E"/>
-      </left>
-      <right style="thick">
-        <color rgb="00E4572E"/>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00000000"/>
       </right>
-      <top style="thick">
-        <color rgb="00E4572E"/>
+      <top style="thin">
+        <color rgb="00000000"/>
       </top>
-      <bottom style="thick">
-        <color rgb="00E4572E"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00000000"/>
       </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="00000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00000000"/>
+      </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -586,15 +703,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F50"/>
+  <dimension ref="A1:I53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="40" customWidth="1" min="4" max="4"/>
-    <col width="44" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
@@ -604,1429 +724,1697 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="28" customHeight="1">
+    <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>v1 — 29 July 2026. Merged from the client-facing schedule (260721_T1B1_ProjectSchedule.xlsx) and the supplier-facing schedule (260729_K5M_Production_Partner_Project Schedule.xlsx), plus decisions/developments from the client schedule's own change log. This table drives the monthly calendar tabs — add new rows here, not directly on a month tab, to keep both in sync.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+          <t xml:space="preserve">  Client</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Supplier</t>
+        </is>
+      </c>
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  WDCO Internal PM</t>
+        </is>
+      </c>
+      <c r="G2" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Deadline (red border)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="26" customHeight="1">
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>v2 — 29 July 2026. One-off activities above the recurring-rule rows at the bottom. Recurring tasks need only one row (Recurs/Weekday/Until filled in) — they expand automatically onto the month tabs, not as individual rows here.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="7" t="inlineStr">
         <is>
           <t>Start</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B5" s="7" t="inlineStr">
         <is>
           <t>End</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C5" s="7" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D5" s="7" t="inlineStr">
         <is>
           <t>Activity</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="E5" s="7" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="F5" s="7" t="inlineStr">
         <is>
           <t>Is Deadline</t>
         </is>
       </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="G5" s="7" t="inlineStr">
+        <is>
+          <t>Recurs</t>
+        </is>
+      </c>
+      <c r="H5" s="7" t="inlineStr">
+        <is>
+          <t>Recurs Weekday</t>
+        </is>
+      </c>
+      <c r="I5" s="7" t="inlineStr">
+        <is>
+          <t>Recurs Until</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="8" t="inlineStr">
         <is>
           <t>2026-07-15</t>
         </is>
       </c>
-      <c r="B5" s="4" t="inlineStr"/>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="B6" s="8" t="inlineStr"/>
+      <c r="C6" s="8" t="inlineStr">
         <is>
           <t>Client</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="D6" s="8" t="inlineStr">
         <is>
           <t>Project kick-off</t>
         </is>
       </c>
-      <c r="E5" s="4" t="inlineStr">
+      <c r="E6" s="8" t="inlineStr">
         <is>
           <t>Milestone.</t>
         </is>
       </c>
-      <c r="F5" s="4" t="inlineStr">
+      <c r="F6" s="8" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="G6" s="8" t="inlineStr"/>
+      <c r="H6" s="8" t="inlineStr"/>
+      <c r="I6" s="8" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="8" t="inlineStr">
         <is>
           <t>2026-07-15</t>
         </is>
       </c>
-      <c r="B6" s="4" t="inlineStr"/>
-      <c r="C6" s="4" t="inlineStr">
+      <c r="B7" s="8" t="inlineStr"/>
+      <c r="C7" s="8" t="inlineStr">
         <is>
           <t>WDCO Internal PM</t>
         </is>
       </c>
-      <c r="D6" s="4" t="inlineStr">
+      <c r="D7" s="8" t="inlineStr">
         <is>
           <t>G&amp;B office unavailable 1-24 Aug</t>
         </is>
       </c>
-      <c r="E6" s="4" t="inlineStr">
+      <c r="E7" s="8" t="inlineStr">
         <is>
           <t>Informed at kick-off meeting.</t>
         </is>
       </c>
-      <c r="F6" s="4" t="inlineStr">
+      <c r="F7" s="8" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="G7" s="8" t="inlineStr"/>
+      <c r="H7" s="8" t="inlineStr"/>
+      <c r="I7" s="8" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="8" t="inlineStr">
         <is>
           <t>2026-07-16</t>
         </is>
       </c>
-      <c r="B7" s="4" t="inlineStr">
+      <c r="B8" s="8" t="inlineStr">
         <is>
           <t>2026-07-22</t>
         </is>
       </c>
-      <c r="C7" s="4" t="inlineStr">
+      <c r="C8" s="8" t="inlineStr">
         <is>
           <t>Client</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="D8" s="8" t="inlineStr">
         <is>
           <t>First RFI and FF&amp;E SHD V00 issue</t>
         </is>
       </c>
-      <c r="E7" s="4" t="inlineStr">
+      <c r="E8" s="8" t="inlineStr">
         <is>
           <t>Issued within 7 days of kick-off.</t>
         </is>
       </c>
-      <c r="F7" s="4" t="inlineStr">
+      <c r="F8" s="8" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="4" t="inlineStr">
+      <c r="G8" s="8" t="inlineStr"/>
+      <c r="H8" s="8" t="inlineStr"/>
+      <c r="I8" s="8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="8" t="inlineStr">
         <is>
           <t>2026-07-17</t>
         </is>
       </c>
-      <c r="B8" s="4" t="inlineStr"/>
-      <c r="C8" s="4" t="inlineStr">
+      <c r="B9" s="8" t="inlineStr"/>
+      <c r="C9" s="8" t="inlineStr">
         <is>
           <t>WDCO Internal PM</t>
         </is>
       </c>
-      <c r="D8" s="4" t="inlineStr">
+      <c r="D9" s="8" t="inlineStr">
         <is>
           <t>White-box availability confirmed as 30 Aug</t>
         </is>
       </c>
-      <c r="E8" s="4" t="inlineStr">
+      <c r="E9" s="8" t="inlineStr">
         <is>
           <t>Was assumed immediate before.</t>
         </is>
       </c>
-      <c r="F8" s="4" t="inlineStr">
+      <c r="F9" s="8" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="G9" s="8" t="inlineStr"/>
+      <c r="H9" s="8" t="inlineStr"/>
+      <c r="I9" s="8" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="8" t="inlineStr">
         <is>
           <t>2026-07-22</t>
         </is>
       </c>
-      <c r="B9" s="4" t="inlineStr">
+      <c r="B10" s="8" t="inlineStr">
         <is>
           <t>2026-07-28</t>
         </is>
       </c>
-      <c r="C9" s="4" t="inlineStr">
+      <c r="C10" s="8" t="inlineStr">
         <is>
           <t>Supplier</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="D10" s="8" t="inlineStr">
         <is>
           <t>SHD V00 parallel review &amp; feedback</t>
         </is>
       </c>
-      <c r="E9" s="4" t="inlineStr">
+      <c r="E10" s="8" t="inlineStr">
         <is>
           <t>28 Jul is the hard feedback deadline.</t>
         </is>
       </c>
-      <c r="F9" s="4" t="inlineStr">
+      <c r="F10" s="8" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="4" t="inlineStr">
+      <c r="G10" s="8" t="inlineStr"/>
+      <c r="H10" s="8" t="inlineStr"/>
+      <c r="I10" s="8" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="8" t="inlineStr">
         <is>
           <t>2026-07-23</t>
         </is>
       </c>
-      <c r="B10" s="4" t="inlineStr">
+      <c r="B11" s="8" t="inlineStr">
         <is>
           <t>2026-07-29</t>
         </is>
       </c>
-      <c r="C10" s="4" t="inlineStr">
+      <c r="C11" s="8" t="inlineStr">
         <is>
           <t>Client</t>
         </is>
       </c>
-      <c r="D10" s="4" t="inlineStr">
+      <c r="D11" s="8" t="inlineStr">
         <is>
           <t>FF&amp;E SHD V00 parallel review &amp; feedback</t>
         </is>
       </c>
-      <c r="E10" s="4" t="inlineStr"/>
-      <c r="F10" s="4" t="inlineStr">
+      <c r="E11" s="8" t="inlineStr"/>
+      <c r="F11" s="8" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="4" t="inlineStr">
+      <c r="G11" s="8" t="inlineStr"/>
+      <c r="H11" s="8" t="inlineStr"/>
+      <c r="I11" s="8" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="8" t="inlineStr">
         <is>
           <t>2026-07-27</t>
         </is>
       </c>
-      <c r="B11" s="4" t="inlineStr"/>
-      <c r="C11" s="4" t="inlineStr">
+      <c r="B12" s="8" t="inlineStr"/>
+      <c r="C12" s="8" t="inlineStr">
         <is>
           <t>Supplier</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="D12" s="8" t="inlineStr">
         <is>
           <t>Material scope issued to Production Partner</t>
         </is>
       </c>
-      <c r="E11" s="4" t="inlineStr">
+      <c r="E12" s="8" t="inlineStr">
         <is>
           <t>Milestone.</t>
         </is>
       </c>
-      <c r="F11" s="4" t="inlineStr">
+      <c r="F12" s="8" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="4" t="inlineStr">
+      <c r="G12" s="8" t="inlineStr"/>
+      <c r="H12" s="8" t="inlineStr"/>
+      <c r="I12" s="8" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="8" t="inlineStr">
         <is>
           <t>2026-07-27</t>
         </is>
       </c>
-      <c r="B12" s="4" t="inlineStr">
+      <c r="B13" s="8" t="inlineStr">
         <is>
           <t>2026-08-07</t>
         </is>
       </c>
-      <c r="C12" s="4" t="inlineStr">
+      <c r="C13" s="8" t="inlineStr">
         <is>
           <t>Supplier</t>
         </is>
       </c>
-      <c r="D12" s="4" t="inlineStr">
+      <c r="D13" s="8" t="inlineStr">
         <is>
           <t>Round 1 sample-box development</t>
         </is>
       </c>
-      <c r="E12" s="4" t="inlineStr">
+      <c r="E13" s="8" t="inlineStr">
         <is>
           <t>12 calendar days.</t>
         </is>
       </c>
-      <c r="F12" s="4" t="inlineStr">
+      <c r="F13" s="8" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="4" t="inlineStr">
+      <c r="G13" s="8" t="inlineStr"/>
+      <c r="H13" s="8" t="inlineStr"/>
+      <c r="I13" s="8" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="8" t="inlineStr">
         <is>
           <t>2026-07-29</t>
         </is>
       </c>
-      <c r="B13" s="4" t="inlineStr">
+      <c r="B14" s="8" t="inlineStr">
         <is>
           <t>2026-08-04</t>
         </is>
       </c>
-      <c r="C13" s="4" t="inlineStr">
+      <c r="C14" s="8" t="inlineStr">
         <is>
           <t>Supplier</t>
         </is>
       </c>
-      <c r="D13" s="4" t="inlineStr">
+      <c r="D14" s="8" t="inlineStr">
         <is>
           <t>SHD V01 drafting and issue</t>
         </is>
       </c>
-      <c r="E13" s="4" t="inlineStr"/>
-      <c r="F13" s="4" t="inlineStr">
+      <c r="E14" s="8" t="inlineStr"/>
+      <c r="F14" s="8" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="4" t="inlineStr">
+      <c r="G14" s="8" t="inlineStr"/>
+      <c r="H14" s="8" t="inlineStr"/>
+      <c r="I14" s="8" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="8" t="inlineStr">
         <is>
           <t>2026-07-30</t>
         </is>
       </c>
-      <c r="B14" s="4" t="inlineStr">
+      <c r="B15" s="8" t="inlineStr">
         <is>
           <t>2026-08-03</t>
         </is>
       </c>
-      <c r="C14" s="4" t="inlineStr">
+      <c r="C15" s="8" t="inlineStr">
         <is>
           <t>Client</t>
         </is>
       </c>
-      <c r="D14" s="4" t="inlineStr">
+      <c r="D15" s="8" t="inlineStr">
         <is>
           <t>FF&amp;E SHD V01 drafting</t>
         </is>
       </c>
-      <c r="E14" s="4" t="inlineStr">
+      <c r="E15" s="8" t="inlineStr">
         <is>
           <t>Developed while G&amp;B review unavailable.</t>
         </is>
       </c>
-      <c r="F14" s="4" t="inlineStr">
+      <c r="F15" s="8" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="4" t="inlineStr">
+      <c r="G15" s="8" t="inlineStr"/>
+      <c r="H15" s="8" t="inlineStr"/>
+      <c r="I15" s="8" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="8" t="inlineStr">
         <is>
           <t>2026-07-30</t>
         </is>
       </c>
-      <c r="B15" s="4" t="inlineStr"/>
-      <c r="C15" s="4" t="inlineStr">
+      <c r="B16" s="8" t="inlineStr"/>
+      <c r="C16" s="8" t="inlineStr">
         <is>
           <t>Client</t>
         </is>
       </c>
-      <c r="D15" s="4" t="inlineStr">
+      <c r="D16" s="8" t="inlineStr">
         <is>
           <t>Fit-out RFI closure</t>
         </is>
       </c>
-      <c r="E15" s="4" t="inlineStr">
+      <c r="E16" s="8" t="inlineStr">
         <is>
           <t>Milestone.</t>
         </is>
       </c>
-      <c r="F15" s="4" t="inlineStr">
+      <c r="F16" s="8" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="4" t="inlineStr">
+      <c r="G16" s="8" t="inlineStr"/>
+      <c r="H16" s="8" t="inlineStr"/>
+      <c r="I16" s="8" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="8" t="inlineStr">
         <is>
           <t>2026-07-31</t>
         </is>
       </c>
-      <c r="B16" s="4" t="inlineStr">
+      <c r="B17" s="8" t="inlineStr">
         <is>
           <t>2026-08-20</t>
         </is>
       </c>
-      <c r="C16" s="4" t="inlineStr">
+      <c r="C17" s="8" t="inlineStr">
         <is>
           <t>Supplier</t>
         </is>
       </c>
-      <c r="D16" s="4" t="inlineStr">
+      <c r="D17" s="8" t="inlineStr">
         <is>
           <t>Fit-Out SHD Version 00</t>
         </is>
       </c>
-      <c r="E16" s="4" t="inlineStr">
+      <c r="E17" s="8" t="inlineStr">
         <is>
           <t>Prepared from available architectural info.</t>
         </is>
       </c>
-      <c r="F16" s="4" t="inlineStr">
+      <c r="F17" s="8" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="4" t="inlineStr">
+      <c r="G17" s="8" t="inlineStr"/>
+      <c r="H17" s="8" t="inlineStr"/>
+      <c r="I17" s="8" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="8" t="inlineStr">
         <is>
           <t>2026-08-03</t>
         </is>
       </c>
-      <c r="B17" s="4" t="inlineStr">
+      <c r="B18" s="8" t="inlineStr">
         <is>
           <t>2026-08-21</t>
         </is>
       </c>
-      <c r="C17" s="4" t="inlineStr">
+      <c r="C18" s="8" t="inlineStr">
         <is>
           <t>Client</t>
         </is>
       </c>
-      <c r="D17" s="4" t="inlineStr">
+      <c r="D18" s="8" t="inlineStr">
         <is>
           <t>Fit-out SHD V00 &amp; preliminary material package</t>
         </is>
       </c>
-      <c r="E17" s="4" t="inlineStr"/>
-      <c r="F17" s="4" t="inlineStr">
+      <c r="E18" s="8" t="inlineStr"/>
+      <c r="F18" s="8" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="4" t="inlineStr">
+      <c r="G18" s="8" t="inlineStr"/>
+      <c r="H18" s="8" t="inlineStr"/>
+      <c r="I18" s="8" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="8" t="inlineStr">
         <is>
           <t>2026-08-05</t>
         </is>
       </c>
-      <c r="B18" s="4" t="inlineStr">
+      <c r="B19" s="8" t="inlineStr">
         <is>
           <t>2026-08-11</t>
         </is>
       </c>
-      <c r="C18" s="4" t="inlineStr">
+      <c r="C19" s="8" t="inlineStr">
         <is>
           <t>Supplier</t>
         </is>
       </c>
-      <c r="D18" s="4" t="inlineStr">
+      <c r="D19" s="8" t="inlineStr">
         <is>
           <t>SHD V01 parallel review &amp; feedback</t>
         </is>
       </c>
-      <c r="E18" s="4" t="inlineStr">
+      <c r="E19" s="8" t="inlineStr">
         <is>
           <t>Only controlled final coordination follows.</t>
         </is>
       </c>
-      <c r="F18" s="4" t="inlineStr">
+      <c r="F19" s="8" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="4" t="inlineStr">
+      <c r="G19" s="8" t="inlineStr"/>
+      <c r="H19" s="8" t="inlineStr"/>
+      <c r="I19" s="8" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="8" t="inlineStr">
         <is>
           <t>2026-08-08</t>
         </is>
       </c>
-      <c r="B19" s="4" t="inlineStr">
+      <c r="B20" s="8" t="inlineStr">
         <is>
           <t>2026-08-10</t>
         </is>
       </c>
-      <c r="C19" s="4" t="inlineStr">
+      <c r="C20" s="8" t="inlineStr">
         <is>
           <t>Supplier</t>
         </is>
       </c>
-      <c r="D19" s="4" t="inlineStr">
+      <c r="D20" s="8" t="inlineStr">
         <is>
           <t>Dispatch/delivery Round 1 sample box to Dubai</t>
         </is>
       </c>
-      <c r="E19" s="4" t="inlineStr">
+      <c r="E20" s="8" t="inlineStr">
         <is>
           <t>Must reach WDCO Dubai by 10 Aug.</t>
         </is>
       </c>
-      <c r="F19" s="4" t="inlineStr">
+      <c r="F20" s="8" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="4" t="inlineStr">
+      <c r="G20" s="8" t="inlineStr"/>
+      <c r="H20" s="8" t="inlineStr"/>
+      <c r="I20" s="8" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="8" t="inlineStr">
         <is>
           <t>2026-08-11</t>
         </is>
       </c>
-      <c r="B20" s="4" t="inlineStr">
+      <c r="B21" s="8" t="inlineStr">
         <is>
           <t>2026-09-10</t>
         </is>
       </c>
-      <c r="C20" s="4" t="inlineStr">
+      <c r="C21" s="8" t="inlineStr">
         <is>
           <t>Supplier</t>
         </is>
       </c>
-      <c r="D20" s="4" t="inlineStr">
+      <c r="D21" s="8" t="inlineStr">
         <is>
           <t>Feedback round &amp; final approved material box</t>
         </is>
       </c>
-      <c r="E20" s="4" t="inlineStr">
+      <c r="E21" s="8" t="inlineStr">
         <is>
           <t>Close by 10 Sept.</t>
         </is>
       </c>
-      <c r="F20" s="4" t="inlineStr">
+      <c r="F21" s="8" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="4" t="inlineStr">
+      <c r="G21" s="8" t="inlineStr"/>
+      <c r="H21" s="8" t="inlineStr"/>
+      <c r="I21" s="8" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="8" t="inlineStr">
         <is>
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="B21" s="4" t="inlineStr">
+      <c r="B22" s="8" t="inlineStr">
         <is>
           <t>2026-09-10</t>
         </is>
       </c>
-      <c r="C21" s="4" t="inlineStr">
+      <c r="C22" s="8" t="inlineStr">
         <is>
           <t>Supplier</t>
         </is>
       </c>
-      <c r="D21" s="4" t="inlineStr">
+      <c r="D22" s="8" t="inlineStr">
         <is>
           <t>Signed GFP SHD Version 02</t>
         </is>
       </c>
-      <c r="E21" s="4" t="inlineStr">
+      <c r="E22" s="8" t="inlineStr">
         <is>
           <t>Required before production release.</t>
         </is>
       </c>
-      <c r="F21" s="4" t="inlineStr">
+      <c r="F22" s="8" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="4" t="inlineStr">
+      <c r="G22" s="8" t="inlineStr"/>
+      <c r="H22" s="8" t="inlineStr"/>
+      <c r="I22" s="8" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="8" t="inlineStr">
         <is>
           <t>2026-08-24</t>
         </is>
       </c>
-      <c r="B22" s="4" t="inlineStr"/>
-      <c r="C22" s="4" t="inlineStr">
+      <c r="B23" s="8" t="inlineStr"/>
+      <c r="C23" s="8" t="inlineStr">
         <is>
           <t>Client</t>
         </is>
       </c>
-      <c r="D22" s="4" t="inlineStr">
+      <c r="D23" s="8" t="inlineStr">
         <is>
           <t>G&amp;B team availability resumes</t>
         </is>
       </c>
-      <c r="E22" s="4" t="inlineStr">
+      <c r="E23" s="8" t="inlineStr">
         <is>
           <t>Office unavailable 1-24 Aug.</t>
         </is>
       </c>
-      <c r="F22" s="4" t="inlineStr">
+      <c r="F23" s="8" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="4" t="inlineStr">
+      <c r="G23" s="8" t="inlineStr"/>
+      <c r="H23" s="8" t="inlineStr"/>
+      <c r="I23" s="8" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="8" t="inlineStr">
         <is>
           <t>2026-08-24</t>
         </is>
       </c>
-      <c r="B23" s="4" t="inlineStr">
+      <c r="B24" s="8" t="inlineStr">
         <is>
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="C23" s="4" t="inlineStr">
+      <c r="C24" s="8" t="inlineStr">
         <is>
           <t>Client</t>
         </is>
       </c>
-      <c r="D23" s="4" t="inlineStr">
+      <c r="D24" s="8" t="inlineStr">
         <is>
           <t>FF&amp;E SHD V01 &amp; Material Package review</t>
         </is>
       </c>
-      <c r="E23" s="4" t="inlineStr">
+      <c r="E24" s="8" t="inlineStr">
         <is>
           <t>Formal parallel review resumes 24 Aug.</t>
         </is>
       </c>
-      <c r="F23" s="4" t="inlineStr">
+      <c r="F24" s="8" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="4" t="inlineStr">
+      <c r="G24" s="8" t="inlineStr"/>
+      <c r="H24" s="8" t="inlineStr"/>
+      <c r="I24" s="8" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="8" t="inlineStr">
         <is>
           <t>2026-08-24</t>
         </is>
       </c>
-      <c r="B24" s="4" t="inlineStr">
+      <c r="B25" s="8" t="inlineStr">
         <is>
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="C24" s="4" t="inlineStr">
+      <c r="C25" s="8" t="inlineStr">
         <is>
           <t>Client</t>
         </is>
       </c>
-      <c r="D24" s="4" t="inlineStr">
+      <c r="D25" s="8" t="inlineStr">
         <is>
           <t>Fit-out SHD V00 review &amp; agreement in principle</t>
         </is>
       </c>
-      <c r="E24" s="4" t="inlineStr">
+      <c r="E25" s="8" t="inlineStr">
         <is>
           <t>Assumes approval from Architect office.</t>
         </is>
       </c>
-      <c r="F24" s="4" t="inlineStr">
+      <c r="F25" s="8" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="4" t="inlineStr">
+      <c r="G25" s="8" t="inlineStr"/>
+      <c r="H25" s="8" t="inlineStr"/>
+      <c r="I25" s="8" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="8" t="inlineStr">
         <is>
           <t>2026-08-25</t>
         </is>
       </c>
-      <c r="B25" s="4" t="inlineStr">
+      <c r="B26" s="8" t="inlineStr">
         <is>
           <t>2026-09-15</t>
         </is>
       </c>
-      <c r="C25" s="4" t="inlineStr">
+      <c r="C26" s="8" t="inlineStr">
         <is>
           <t>WDCO Internal PM</t>
         </is>
       </c>
-      <c r="D25" s="4" t="inlineStr">
+      <c r="D26" s="8" t="inlineStr">
         <is>
           <t>Site holiday period (Mawlid)</t>
         </is>
       </c>
-      <c r="E25" s="4" t="inlineStr">
+      <c r="E26" s="8" t="inlineStr">
         <is>
           <t>Open confirmation: is site accessible for the 31 Aug survey despite this?</t>
         </is>
       </c>
-      <c r="F25" s="4" t="inlineStr">
+      <c r="F26" s="8" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="4" t="inlineStr">
+      <c r="G26" s="8" t="inlineStr"/>
+      <c r="H26" s="8" t="inlineStr"/>
+      <c r="I26" s="8" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="8" t="inlineStr">
         <is>
           <t>2026-08-31</t>
         </is>
       </c>
-      <c r="B26" s="4" t="inlineStr">
+      <c r="B27" s="8" t="inlineStr">
         <is>
           <t>2026-09-02</t>
         </is>
       </c>
-      <c r="C26" s="4" t="inlineStr">
+      <c r="C27" s="8" t="inlineStr">
         <is>
           <t>Client</t>
         </is>
       </c>
-      <c r="D26" s="4" t="inlineStr">
+      <c r="D27" s="8" t="inlineStr">
         <is>
           <t>FF&amp;E SHD V02 drafting</t>
         </is>
       </c>
-      <c r="E26" s="4" t="inlineStr">
+      <c r="E27" s="8" t="inlineStr">
         <is>
           <t>Final drafting after V01 feedback.</t>
         </is>
       </c>
-      <c r="F26" s="4" t="inlineStr">
+      <c r="F27" s="8" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="4" t="inlineStr">
+      <c r="G27" s="8" t="inlineStr"/>
+      <c r="H27" s="8" t="inlineStr"/>
+      <c r="I27" s="8" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="8" t="inlineStr">
         <is>
           <t>2026-08-31</t>
         </is>
       </c>
-      <c r="B27" s="4" t="inlineStr"/>
-      <c r="C27" s="4" t="inlineStr">
+      <c r="B28" s="8" t="inlineStr"/>
+      <c r="C28" s="8" t="inlineStr">
         <is>
           <t>Client</t>
         </is>
       </c>
-      <c r="D27" s="4" t="inlineStr">
+      <c r="D28" s="8" t="inlineStr">
         <is>
           <t>Fit-out site survey</t>
         </is>
       </c>
-      <c r="E27" s="4" t="inlineStr">
+      <c r="E28" s="8" t="inlineStr">
         <is>
           <t>Planned once white box is ready.</t>
         </is>
       </c>
-      <c r="F27" s="4" t="inlineStr">
+      <c r="F28" s="8" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="4" t="inlineStr">
+      <c r="G28" s="8" t="inlineStr"/>
+      <c r="H28" s="8" t="inlineStr"/>
+      <c r="I28" s="8" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="8" t="inlineStr">
         <is>
           <t>2026-08-31</t>
         </is>
       </c>
-      <c r="B28" s="4" t="inlineStr"/>
-      <c r="C28" s="4" t="inlineStr">
+      <c r="B29" s="8" t="inlineStr"/>
+      <c r="C29" s="8" t="inlineStr">
         <is>
           <t>Supplier</t>
         </is>
       </c>
-      <c r="D28" s="4" t="inlineStr">
+      <c r="D29" s="8" t="inlineStr">
         <is>
           <t>Site visit / measurement</t>
         </is>
       </c>
-      <c r="E28" s="4" t="inlineStr">
+      <c r="E29" s="8" t="inlineStr">
         <is>
           <t>Milestone.</t>
         </is>
       </c>
-      <c r="F28" s="4" t="inlineStr">
+      <c r="F29" s="8" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="4" t="inlineStr">
+      <c r="G29" s="8" t="inlineStr"/>
+      <c r="H29" s="8" t="inlineStr"/>
+      <c r="I29" s="8" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="8" t="inlineStr">
         <is>
           <t>2026-09-01</t>
         </is>
       </c>
-      <c r="B29" s="4" t="inlineStr">
+      <c r="B30" s="8" t="inlineStr">
         <is>
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="C29" s="4" t="inlineStr">
+      <c r="C30" s="8" t="inlineStr">
         <is>
           <t>Client</t>
         </is>
       </c>
-      <c r="D29" s="4" t="inlineStr">
+      <c r="D30" s="8" t="inlineStr">
         <is>
           <t>Fit-out site-survey report</t>
         </is>
       </c>
-      <c r="E29" s="4" t="inlineStr">
+      <c r="E30" s="8" t="inlineStr">
         <is>
           <t>3-4 working days after survey.</t>
         </is>
       </c>
-      <c r="F29" s="4" t="inlineStr">
+      <c r="F30" s="8" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="4" t="inlineStr">
+      <c r="G30" s="8" t="inlineStr"/>
+      <c r="H30" s="8" t="inlineStr"/>
+      <c r="I30" s="8" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="8" t="inlineStr">
         <is>
           <t>2026-09-01</t>
         </is>
       </c>
-      <c r="B30" s="4" t="inlineStr">
+      <c r="B31" s="8" t="inlineStr">
         <is>
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="C30" s="4" t="inlineStr">
+      <c r="C31" s="8" t="inlineStr">
         <is>
           <t>Supplier</t>
         </is>
       </c>
-      <c r="D30" s="4" t="inlineStr">
+      <c r="D31" s="8" t="inlineStr">
         <is>
           <t>Site survey report</t>
         </is>
       </c>
-      <c r="E30" s="4" t="inlineStr">
+      <c r="E31" s="8" t="inlineStr">
         <is>
           <t>Issued by 3 Sept.</t>
         </is>
       </c>
-      <c r="F30" s="4" t="inlineStr">
+      <c r="F31" s="8" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="4" t="inlineStr">
+      <c r="G31" s="8" t="inlineStr"/>
+      <c r="H31" s="8" t="inlineStr"/>
+      <c r="I31" s="8" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="8" t="inlineStr">
         <is>
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="B31" s="4" t="inlineStr">
+      <c r="B32" s="8" t="inlineStr">
         <is>
           <t>2026-09-08</t>
         </is>
       </c>
-      <c r="C31" s="4" t="inlineStr">
+      <c r="C32" s="8" t="inlineStr">
         <is>
           <t>Client</t>
         </is>
       </c>
-      <c r="D31" s="4" t="inlineStr">
+      <c r="D32" s="8" t="inlineStr">
         <is>
           <t>Signed FF&amp;E SHD V02 &amp; confirmed material package</t>
         </is>
       </c>
-      <c r="E31" s="4" t="inlineStr">
+      <c r="E32" s="8" t="inlineStr">
         <is>
           <t>Production starts only after this.</t>
         </is>
       </c>
-      <c r="F31" s="4" t="inlineStr">
+      <c r="F32" s="8" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="4" t="inlineStr">
+      <c r="G32" s="8" t="inlineStr"/>
+      <c r="H32" s="8" t="inlineStr"/>
+      <c r="I32" s="8" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="8" t="inlineStr">
         <is>
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="B32" s="4" t="inlineStr">
+      <c r="B33" s="8" t="inlineStr">
         <is>
           <t>2026-09-10</t>
         </is>
       </c>
-      <c r="C32" s="4" t="inlineStr">
+      <c r="C33" s="8" t="inlineStr">
         <is>
           <t>Supplier</t>
         </is>
       </c>
-      <c r="D32" s="4" t="inlineStr">
+      <c r="D33" s="8" t="inlineStr">
         <is>
           <t>Fit-Out SHD V01 incorporating survey</t>
         </is>
       </c>
-      <c r="E32" s="4" t="inlineStr"/>
-      <c r="F32" s="4" t="inlineStr">
+      <c r="E33" s="8" t="inlineStr"/>
+      <c r="F33" s="8" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="4" t="inlineStr">
+      <c r="G33" s="8" t="inlineStr"/>
+      <c r="H33" s="8" t="inlineStr"/>
+      <c r="I33" s="8" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="8" t="inlineStr">
         <is>
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="B33" s="4" t="inlineStr">
+      <c r="B34" s="8" t="inlineStr">
         <is>
           <t>2026-09-15</t>
         </is>
       </c>
-      <c r="C33" s="4" t="inlineStr">
+      <c r="C34" s="8" t="inlineStr">
         <is>
           <t>Client</t>
         </is>
       </c>
-      <c r="D33" s="4" t="inlineStr">
+      <c r="D34" s="8" t="inlineStr">
         <is>
           <t>Fit-out SHD V01 revisions</t>
         </is>
       </c>
-      <c r="E33" s="4" t="inlineStr">
+      <c r="E34" s="8" t="inlineStr">
         <is>
           <t>Site-survey findings incorporated.</t>
         </is>
       </c>
-      <c r="F33" s="4" t="inlineStr">
+      <c r="F34" s="8" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="4" t="inlineStr">
+      <c r="G34" s="8" t="inlineStr"/>
+      <c r="H34" s="8" t="inlineStr"/>
+      <c r="I34" s="8" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="8" t="inlineStr">
         <is>
           <t>2026-09-09</t>
         </is>
       </c>
-      <c r="B34" s="4" t="inlineStr">
+      <c r="B35" s="8" t="inlineStr">
         <is>
           <t>2026-10-23</t>
         </is>
       </c>
-      <c r="C34" s="4" t="inlineStr">
+      <c r="C35" s="8" t="inlineStr">
         <is>
           <t>Client</t>
         </is>
       </c>
-      <c r="D34" s="4" t="inlineStr">
+      <c r="D35" s="8" t="inlineStr">
         <is>
           <t>FF&amp;E mock-up production, QC and packing</t>
         </is>
       </c>
-      <c r="E34" s="4" t="inlineStr"/>
-      <c r="F34" s="4" t="inlineStr">
+      <c r="E35" s="8" t="inlineStr"/>
+      <c r="F35" s="8" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="4" t="inlineStr">
+      <c r="G35" s="8" t="inlineStr"/>
+      <c r="H35" s="8" t="inlineStr"/>
+      <c r="I35" s="8" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="8" t="inlineStr">
         <is>
           <t>2026-09-10</t>
         </is>
       </c>
-      <c r="B35" s="4" t="inlineStr">
+      <c r="B36" s="8" t="inlineStr">
         <is>
           <t>2026-10-09</t>
         </is>
       </c>
-      <c r="C35" s="4" t="inlineStr">
+      <c r="C36" s="8" t="inlineStr">
         <is>
           <t>Supplier</t>
         </is>
       </c>
-      <c r="D35" s="4" t="inlineStr">
+      <c r="D36" s="8" t="inlineStr">
         <is>
           <t>FF&amp;E production</t>
         </is>
       </c>
-      <c r="E35" s="4" t="inlineStr">
+      <c r="E36" s="8" t="inlineStr">
         <is>
           <t>Begins only after signed GFP SHD.</t>
         </is>
       </c>
-      <c r="F35" s="4" t="inlineStr">
+      <c r="F36" s="8" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="4" t="inlineStr">
+      <c r="G36" s="8" t="inlineStr"/>
+      <c r="H36" s="8" t="inlineStr"/>
+      <c r="I36" s="8" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="8" t="inlineStr">
         <is>
           <t>2026-09-10</t>
         </is>
       </c>
-      <c r="B36" s="4" t="inlineStr"/>
-      <c r="C36" s="4" t="inlineStr">
+      <c r="B37" s="8" t="inlineStr"/>
+      <c r="C37" s="8" t="inlineStr">
         <is>
           <t>Supplier</t>
         </is>
       </c>
-      <c r="D36" s="4" t="inlineStr">
+      <c r="D37" s="8" t="inlineStr">
         <is>
           <t>Signed GFP Fit-Out SHD</t>
         </is>
       </c>
-      <c r="E36" s="4" t="inlineStr">
+      <c r="E37" s="8" t="inlineStr">
         <is>
           <t>Required before production starts.</t>
         </is>
       </c>
-      <c r="F36" s="4" t="inlineStr">
+      <c r="F37" s="8" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="4" t="inlineStr">
+      <c r="G37" s="8" t="inlineStr"/>
+      <c r="H37" s="8" t="inlineStr"/>
+      <c r="I37" s="8" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="8" t="inlineStr">
         <is>
           <t>2026-09-10</t>
         </is>
       </c>
-      <c r="B37" s="4" t="inlineStr">
+      <c r="B38" s="8" t="inlineStr">
         <is>
           <t>2026-09-24</t>
         </is>
       </c>
-      <c r="C37" s="4" t="inlineStr">
+      <c r="C38" s="8" t="inlineStr">
         <is>
           <t>Supplier</t>
         </is>
       </c>
-      <c r="D37" s="4" t="inlineStr">
+      <c r="D38" s="8" t="inlineStr">
         <is>
           <t>Fit-Out production</t>
         </is>
       </c>
-      <c r="E37" s="4" t="inlineStr"/>
-      <c r="F37" s="4" t="inlineStr">
+      <c r="E38" s="8" t="inlineStr"/>
+      <c r="F38" s="8" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="4" t="inlineStr">
+      <c r="G38" s="8" t="inlineStr"/>
+      <c r="H38" s="8" t="inlineStr"/>
+      <c r="I38" s="8" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="8" t="inlineStr">
         <is>
           <t>2026-09-16</t>
         </is>
       </c>
-      <c r="B38" s="4" t="inlineStr">
+      <c r="B39" s="8" t="inlineStr">
         <is>
           <t>2026-09-21</t>
         </is>
       </c>
-      <c r="C38" s="4" t="inlineStr">
+      <c r="C39" s="8" t="inlineStr">
         <is>
           <t>Client</t>
         </is>
       </c>
-      <c r="D38" s="4" t="inlineStr">
+      <c r="D39" s="8" t="inlineStr">
         <is>
           <t>Fit-out SHD V01 &amp; material-package approval</t>
         </is>
       </c>
-      <c r="E38" s="4" t="inlineStr">
+      <c r="E39" s="8" t="inlineStr">
         <is>
           <t>Final fit-out production-release gate.</t>
         </is>
       </c>
-      <c r="F38" s="4" t="inlineStr">
+      <c r="F39" s="8" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="4" t="inlineStr">
+      <c r="G39" s="8" t="inlineStr"/>
+      <c r="H39" s="8" t="inlineStr"/>
+      <c r="I39" s="8" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="8" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
       </c>
-      <c r="B39" s="4" t="inlineStr">
+      <c r="B40" s="8" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="C39" s="4" t="inlineStr">
+      <c r="C40" s="8" t="inlineStr">
         <is>
           <t>Client</t>
         </is>
       </c>
-      <c r="D39" s="4" t="inlineStr">
+      <c r="D40" s="8" t="inlineStr">
         <is>
           <t>Fit-out production, QC and packing</t>
         </is>
       </c>
-      <c r="E39" s="4" t="inlineStr"/>
-      <c r="F39" s="4" t="inlineStr">
+      <c r="E40" s="8" t="inlineStr"/>
+      <c r="F40" s="8" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="4" t="inlineStr">
+      <c r="G40" s="8" t="inlineStr"/>
+      <c r="H40" s="8" t="inlineStr"/>
+      <c r="I40" s="8" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="8" t="inlineStr">
         <is>
           <t>2026-10-10</t>
         </is>
       </c>
-      <c r="B40" s="4" t="inlineStr">
+      <c r="B41" s="8" t="inlineStr">
         <is>
           <t>2026-11-28</t>
         </is>
       </c>
-      <c r="C40" s="4" t="inlineStr">
+      <c r="C41" s="8" t="inlineStr">
         <is>
           <t>Supplier</t>
         </is>
       </c>
-      <c r="D40" s="4" t="inlineStr">
+      <c r="D41" s="8" t="inlineStr">
         <is>
           <t>Packing, dispatch, sea freight, customs, delivery</t>
         </is>
       </c>
-      <c r="E40" s="4" t="inlineStr">
+      <c r="E41" s="8" t="inlineStr">
         <is>
           <t>Both packages together.</t>
         </is>
       </c>
-      <c r="F40" s="4" t="inlineStr">
+      <c r="F41" s="8" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="4" t="inlineStr">
+      <c r="G41" s="8" t="inlineStr"/>
+      <c r="H41" s="8" t="inlineStr"/>
+      <c r="I41" s="8" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="8" t="inlineStr">
         <is>
           <t>2026-10-25</t>
         </is>
       </c>
-      <c r="B41" s="4" t="inlineStr"/>
-      <c r="C41" s="4" t="inlineStr">
+      <c r="B42" s="8" t="inlineStr"/>
+      <c r="C42" s="8" t="inlineStr">
         <is>
           <t>Client</t>
         </is>
       </c>
-      <c r="D41" s="4" t="inlineStr">
+      <c r="D42" s="8" t="inlineStr">
         <is>
           <t>Combined dispatch on next available sailing</t>
         </is>
       </c>
-      <c r="E41" s="4" t="inlineStr">
+      <c r="E42" s="8" t="inlineStr">
         <is>
           <t>Milestone.</t>
         </is>
       </c>
-      <c r="F41" s="4" t="inlineStr">
+      <c r="F42" s="8" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="4" t="inlineStr">
+      <c r="G42" s="8" t="inlineStr"/>
+      <c r="H42" s="8" t="inlineStr"/>
+      <c r="I42" s="8" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="8" t="inlineStr">
         <is>
           <t>2026-10-25</t>
         </is>
       </c>
-      <c r="B42" s="4" t="inlineStr">
+      <c r="B43" s="8" t="inlineStr">
         <is>
           <t>2026-12-03</t>
         </is>
       </c>
-      <c r="C42" s="4" t="inlineStr">
+      <c r="C43" s="8" t="inlineStr">
         <is>
           <t>Client</t>
         </is>
       </c>
-      <c r="D42" s="4" t="inlineStr">
+      <c r="D43" s="8" t="inlineStr">
         <is>
           <t>Sea freight to Casablanca</t>
         </is>
       </c>
-      <c r="E42" s="4" t="inlineStr"/>
-      <c r="F42" s="4" t="inlineStr">
+      <c r="E43" s="8" t="inlineStr"/>
+      <c r="F43" s="8" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="4" t="inlineStr">
+      <c r="G43" s="8" t="inlineStr"/>
+      <c r="H43" s="8" t="inlineStr"/>
+      <c r="I43" s="8" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="8" t="inlineStr">
         <is>
           <t>2026-11-15</t>
         </is>
       </c>
-      <c r="B43" s="4" t="inlineStr"/>
-      <c r="C43" s="4" t="inlineStr">
+      <c r="B44" s="8" t="inlineStr"/>
+      <c r="C44" s="8" t="inlineStr">
         <is>
           <t>WDCO Internal PM</t>
         </is>
       </c>
-      <c r="D43" s="4" t="inlineStr">
+      <c r="D44" s="8" t="inlineStr">
         <is>
           <t>Internal working deadline</t>
         </is>
       </c>
-      <c r="E43" s="4" t="inlineStr">
-        <is>
-          <t>Supplier's communicated 15 Dec hard deadline is unconfirmed; treat 15 Nov as the real internal target.</t>
-        </is>
-      </c>
-      <c r="F43" s="4" t="inlineStr">
+      <c r="E44" s="8" t="inlineStr">
+        <is>
+          <t>Supplier's 15 Dec hard deadline is unconfirmed; treat 15 Nov as the real internal target.</t>
+        </is>
+      </c>
+      <c r="F44" s="8" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="4" t="inlineStr">
+      <c r="G44" s="8" t="inlineStr"/>
+      <c r="H44" s="8" t="inlineStr"/>
+      <c r="I44" s="8" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="8" t="inlineStr">
         <is>
           <t>2026-11-29</t>
         </is>
       </c>
-      <c r="B44" s="4" t="inlineStr">
+      <c r="B45" s="8" t="inlineStr">
         <is>
           <t>2026-12-13</t>
         </is>
       </c>
-      <c r="C44" s="4" t="inlineStr">
+      <c r="C45" s="8" t="inlineStr">
         <is>
           <t>Supplier</t>
         </is>
       </c>
-      <c r="D44" s="4" t="inlineStr">
+      <c r="D45" s="8" t="inlineStr">
         <is>
           <t>Fit-Out and FF&amp;E installation</t>
         </is>
       </c>
-      <c r="E44" s="4" t="inlineStr"/>
-      <c r="F44" s="4" t="inlineStr">
+      <c r="E45" s="8" t="inlineStr"/>
+      <c r="F45" s="8" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="4" t="inlineStr">
+      <c r="G45" s="8" t="inlineStr"/>
+      <c r="H45" s="8" t="inlineStr"/>
+      <c r="I45" s="8" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="8" t="inlineStr">
         <is>
           <t>2026-12-03</t>
         </is>
       </c>
-      <c r="B45" s="4" t="inlineStr">
+      <c r="B46" s="8" t="inlineStr">
         <is>
           <t>2026-12-07</t>
         </is>
       </c>
-      <c r="C45" s="4" t="inlineStr">
+      <c r="C46" s="8" t="inlineStr">
         <is>
           <t>Client</t>
         </is>
       </c>
-      <c r="D45" s="4" t="inlineStr">
+      <c r="D46" s="8" t="inlineStr">
         <is>
           <t>Customs, port release, delivery to site</t>
         </is>
       </c>
-      <c r="E45" s="4" t="inlineStr"/>
-      <c r="F45" s="4" t="inlineStr">
+      <c r="E46" s="8" t="inlineStr"/>
+      <c r="F46" s="8" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="4" t="inlineStr">
+      <c r="G46" s="8" t="inlineStr"/>
+      <c r="H46" s="8" t="inlineStr"/>
+      <c r="I46" s="8" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="8" t="inlineStr">
         <is>
           <t>2026-12-04</t>
         </is>
       </c>
-      <c r="B46" s="4" t="inlineStr">
+      <c r="B47" s="8" t="inlineStr">
         <is>
           <t>2026-12-18</t>
         </is>
       </c>
-      <c r="C46" s="4" t="inlineStr">
+      <c r="C47" s="8" t="inlineStr">
         <is>
           <t>Client</t>
         </is>
       </c>
-      <c r="D46" s="4" t="inlineStr">
+      <c r="D47" s="8" t="inlineStr">
         <is>
           <t>Fit-out installation</t>
         </is>
       </c>
-      <c r="E46" s="4" t="inlineStr">
+      <c r="E47" s="8" t="inlineStr">
         <is>
           <t>Precedes FF&amp;E installation.</t>
         </is>
       </c>
-      <c r="F46" s="4" t="inlineStr">
+      <c r="F47" s="8" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="4" t="inlineStr">
+      <c r="G47" s="8" t="inlineStr"/>
+      <c r="H47" s="8" t="inlineStr"/>
+      <c r="I47" s="8" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="8" t="inlineStr">
         <is>
           <t>2026-12-14</t>
         </is>
       </c>
-      <c r="B47" s="4" t="inlineStr"/>
-      <c r="C47" s="4" t="inlineStr">
+      <c r="B48" s="8" t="inlineStr"/>
+      <c r="C48" s="8" t="inlineStr">
         <is>
           <t>Supplier</t>
         </is>
       </c>
-      <c r="D47" s="4" t="inlineStr">
+      <c r="D48" s="8" t="inlineStr">
         <is>
           <t>Ready for site inspection</t>
         </is>
       </c>
-      <c r="E47" s="4" t="inlineStr">
+      <c r="E48" s="8" t="inlineStr">
         <is>
           <t>All contracted installation complete.</t>
         </is>
       </c>
-      <c r="F47" s="4" t="inlineStr">
+      <c r="F48" s="8" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="4" t="inlineStr">
+      <c r="G48" s="8" t="inlineStr"/>
+      <c r="H48" s="8" t="inlineStr"/>
+      <c r="I48" s="8" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="8" t="inlineStr">
         <is>
           <t>2026-12-15</t>
         </is>
       </c>
-      <c r="B48" s="4" t="inlineStr"/>
-      <c r="C48" s="4" t="inlineStr">
+      <c r="B49" s="8" t="inlineStr"/>
+      <c r="C49" s="8" t="inlineStr">
         <is>
           <t>Supplier</t>
         </is>
       </c>
-      <c r="D48" s="4" t="inlineStr">
+      <c r="D49" s="8" t="inlineStr">
         <is>
           <t>Hard deadline (as communicated to supplier)</t>
         </is>
       </c>
-      <c r="E48" s="4" t="inlineStr">
+      <c r="E49" s="8" t="inlineStr">
         <is>
           <t>Tentative, not yet confirmed.</t>
         </is>
       </c>
-      <c r="F48" s="4" t="inlineStr">
+      <c r="F49" s="8" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="4" t="inlineStr">
+      <c r="G49" s="8" t="inlineStr"/>
+      <c r="H49" s="8" t="inlineStr"/>
+      <c r="I49" s="8" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="8" t="inlineStr">
         <is>
           <t>2026-12-19</t>
         </is>
       </c>
-      <c r="B49" s="4" t="inlineStr">
+      <c r="B50" s="8" t="inlineStr">
         <is>
           <t>2026-12-20</t>
         </is>
       </c>
-      <c r="C49" s="4" t="inlineStr">
+      <c r="C50" s="8" t="inlineStr">
         <is>
           <t>Client</t>
         </is>
       </c>
-      <c r="D49" s="4" t="inlineStr">
+      <c r="D50" s="8" t="inlineStr">
         <is>
           <t>FF&amp;E installation</t>
         </is>
       </c>
-      <c r="E49" s="4" t="inlineStr"/>
-      <c r="F49" s="4" t="inlineStr">
+      <c r="E50" s="8" t="inlineStr"/>
+      <c r="F50" s="8" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="4" t="inlineStr">
+      <c r="G50" s="8" t="inlineStr"/>
+      <c r="H50" s="8" t="inlineStr"/>
+      <c r="I50" s="8" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="8" t="inlineStr">
         <is>
           <t>2026-12-20</t>
         </is>
       </c>
-      <c r="B50" s="4" t="inlineStr"/>
-      <c r="C50" s="4" t="inlineStr">
+      <c r="B51" s="8" t="inlineStr"/>
+      <c r="C51" s="8" t="inlineStr">
         <is>
           <t>Client</t>
         </is>
       </c>
-      <c r="D50" s="4" t="inlineStr">
+      <c r="D51" s="8" t="inlineStr">
         <is>
           <t>Complete T1B1 mock-up ready for inspection</t>
         </is>
       </c>
-      <c r="E50" s="4" t="inlineStr">
+      <c r="E51" s="8" t="inlineStr">
         <is>
           <t>Indicative revised readiness date.</t>
         </is>
       </c>
-      <c r="F50" s="4" t="inlineStr">
+      <c r="F51" s="8" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
+      <c r="G51" s="8" t="inlineStr"/>
+      <c r="H51" s="8" t="inlineStr"/>
+      <c r="I51" s="8" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B52" s="9" t="inlineStr"/>
+      <c r="C52" s="9" t="inlineStr">
+        <is>
+          <t>Client</t>
+        </is>
+      </c>
+      <c r="D52" s="9" t="inlineStr">
+        <is>
+          <t>Send project update to client-facing group</t>
+        </is>
+      </c>
+      <c r="E52" s="9" t="inlineStr">
+        <is>
+          <t>Recurring — biweekly, anchored 31 Jul 2026.</t>
+        </is>
+      </c>
+      <c r="F52" s="9" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G52" s="9" t="inlineStr">
+        <is>
+          <t>Biweekly</t>
+        </is>
+      </c>
+      <c r="H52" s="9" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="I52" s="9" t="inlineStr">
+        <is>
+          <t>2026-12-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B53" s="9" t="inlineStr"/>
+      <c r="C53" s="9" t="inlineStr">
+        <is>
+          <t>WDCO Internal PM</t>
+        </is>
+      </c>
+      <c r="D53" s="9" t="inlineStr">
+        <is>
+          <t>Send project update to internal WDCO K5M group</t>
+        </is>
+      </c>
+      <c r="E53" s="9" t="inlineStr">
+        <is>
+          <t>Recurring — weekly, anchored 31 Jul 2026.</t>
+        </is>
+      </c>
+      <c r="F53" s="9" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G53" s="9" t="inlineStr">
+        <is>
+          <t>Weekly</t>
+        </is>
+      </c>
+      <c r="H53" s="9" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="I53" s="9" t="inlineStr">
+        <is>
+          <t>2026-12-31</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:F50"/>
-  <mergeCells count="2">
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A1:F1"/>
+  <autoFilter ref="A5:I53"/>
+  <mergeCells count="6">
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="G2:H2"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A3:I3"/>
   </mergeCells>
-  <dataValidations count="2">
-    <dataValidation sqref="C5:C50" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+  <dataValidations count="3">
+    <dataValidation sqref="C6:C53" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Client,Supplier,WDCO Internal PM"</formula1>
     </dataValidation>
-    <dataValidation sqref="F5:F50" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F6:F53" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Y,N"</formula1>
+    </dataValidation>
+    <dataValidation sqref="G6:G53" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Weekly,Biweekly"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2039,272 +2427,608 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:G39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="26" customWidth="1" min="5" max="5"/>
+    <col width="26" customWidth="1" min="6" max="6"/>
+    <col width="26" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="5" t="inlineStr">
+      <c r="A1" s="10" t="inlineStr">
         <is>
           <t>K5M — JULY 2026</t>
         </is>
       </c>
     </row>
     <row r="2" ht="16" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">  Client</t>
         </is>
       </c>
-      <c r="C2" s="7" t="inlineStr">
+      <c r="B2" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">  Supplier</t>
         </is>
       </c>
-      <c r="E2" s="8" t="inlineStr">
+      <c r="C2" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">  WDCO Internal PM</t>
         </is>
       </c>
-      <c r="G2" s="9" t="inlineStr">
+      <c r="D2" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">  Deadline (red border)</t>
         </is>
       </c>
     </row>
     <row r="4" ht="18" customHeight="1">
-      <c r="A4" s="10" t="inlineStr">
+      <c r="A4" s="11" t="inlineStr">
         <is>
           <t>Sunday</t>
         </is>
       </c>
-      <c r="B4" s="10" t="inlineStr">
+      <c r="B4" s="11" t="inlineStr">
         <is>
           <t>Monday</t>
         </is>
       </c>
-      <c r="C4" s="10" t="inlineStr">
+      <c r="C4" s="11" t="inlineStr">
         <is>
           <t>Tuesday</t>
         </is>
       </c>
-      <c r="D4" s="10" t="inlineStr">
+      <c r="D4" s="11" t="inlineStr">
         <is>
           <t>Wednesday</t>
         </is>
       </c>
-      <c r="E4" s="10" t="inlineStr">
+      <c r="E4" s="11" t="inlineStr">
         <is>
           <t>Thursday</t>
         </is>
       </c>
-      <c r="F4" s="10" t="inlineStr">
+      <c r="F4" s="11" t="inlineStr">
         <is>
           <t>Friday</t>
         </is>
       </c>
-      <c r="G4" s="10" t="inlineStr">
+      <c r="G4" s="11" t="inlineStr">
         <is>
           <t>Saturday</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="60" customHeight="1">
-      <c r="A5" s="11" t="n"/>
-      <c r="B5" s="11" t="n"/>
-      <c r="C5" s="11" t="n"/>
-      <c r="D5" s="12" t="inlineStr">
+    <row r="5" ht="16" customHeight="1">
+      <c r="A5" s="12" t="n"/>
+      <c r="B5" s="12" t="n"/>
+      <c r="C5" s="12" t="n"/>
+      <c r="D5" s="13" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E5" s="12" t="inlineStr">
+      <c r="E5" s="13" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="F5" s="12" t="inlineStr">
+      <c r="F5" s="13" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="G5" s="12" t="inlineStr">
+      <c r="G5" s="13" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="60" customHeight="1">
-      <c r="A6" s="12" t="inlineStr">
+    <row r="6" ht="34" customHeight="1">
+      <c r="A6" s="14" t="n"/>
+      <c r="B6" s="14" t="n"/>
+      <c r="C6" s="14" t="n"/>
+      <c r="D6" s="14" t="n"/>
+      <c r="E6" s="14" t="n"/>
+      <c r="F6" s="14" t="n"/>
+      <c r="G6" s="14" t="n"/>
+    </row>
+    <row r="7" ht="34" customHeight="1">
+      <c r="A7" s="14" t="n"/>
+      <c r="B7" s="14" t="n"/>
+      <c r="C7" s="14" t="n"/>
+      <c r="D7" s="14" t="n"/>
+      <c r="E7" s="14" t="n"/>
+      <c r="F7" s="14" t="n"/>
+      <c r="G7" s="14" t="n"/>
+    </row>
+    <row r="8" ht="34" customHeight="1">
+      <c r="A8" s="14" t="n"/>
+      <c r="B8" s="14" t="n"/>
+      <c r="C8" s="14" t="n"/>
+      <c r="D8" s="14" t="n"/>
+      <c r="E8" s="14" t="n"/>
+      <c r="F8" s="14" t="n"/>
+      <c r="G8" s="14" t="n"/>
+    </row>
+    <row r="9" ht="34" customHeight="1">
+      <c r="A9" s="14" t="n"/>
+      <c r="B9" s="14" t="n"/>
+      <c r="C9" s="14" t="n"/>
+      <c r="D9" s="14" t="n"/>
+      <c r="E9" s="14" t="n"/>
+      <c r="F9" s="14" t="n"/>
+      <c r="G9" s="14" t="n"/>
+    </row>
+    <row r="10" ht="34" customHeight="1">
+      <c r="A10" s="14" t="n"/>
+      <c r="B10" s="14" t="n"/>
+      <c r="C10" s="14" t="n"/>
+      <c r="D10" s="14" t="n"/>
+      <c r="E10" s="14" t="n"/>
+      <c r="F10" s="14" t="n"/>
+      <c r="G10" s="14" t="n"/>
+    </row>
+    <row r="11" ht="34" customHeight="1">
+      <c r="A11" s="14" t="n"/>
+      <c r="B11" s="14" t="n"/>
+      <c r="C11" s="14" t="n"/>
+      <c r="D11" s="14" t="n"/>
+      <c r="E11" s="14" t="n"/>
+      <c r="F11" s="14" t="n"/>
+      <c r="G11" s="14" t="n"/>
+    </row>
+    <row r="12" ht="16" customHeight="1">
+      <c r="A12" s="13" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="B6" s="12" t="inlineStr">
+      <c r="B12" s="13" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="C6" s="12" t="inlineStr">
+      <c r="C12" s="13" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D6" s="12" t="inlineStr">
+      <c r="D12" s="13" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="E6" s="12" t="inlineStr">
+      <c r="E12" s="13" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="F6" s="12" t="inlineStr">
+      <c r="F12" s="13" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="G6" s="12" t="inlineStr">
+      <c r="G12" s="13" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="102" customHeight="1">
-      <c r="A7" s="12" t="inlineStr">
+    <row r="13" ht="34" customHeight="1">
+      <c r="A13" s="14" t="n"/>
+      <c r="B13" s="14" t="n"/>
+      <c r="C13" s="14" t="n"/>
+      <c r="D13" s="14" t="n"/>
+      <c r="E13" s="14" t="n"/>
+      <c r="F13" s="14" t="n"/>
+      <c r="G13" s="14" t="n"/>
+    </row>
+    <row r="14" ht="34" customHeight="1">
+      <c r="A14" s="14" t="n"/>
+      <c r="B14" s="14" t="n"/>
+      <c r="C14" s="14" t="n"/>
+      <c r="D14" s="14" t="n"/>
+      <c r="E14" s="14" t="n"/>
+      <c r="F14" s="14" t="n"/>
+      <c r="G14" s="14" t="n"/>
+    </row>
+    <row r="15" ht="34" customHeight="1">
+      <c r="A15" s="14" t="n"/>
+      <c r="B15" s="14" t="n"/>
+      <c r="C15" s="14" t="n"/>
+      <c r="D15" s="14" t="n"/>
+      <c r="E15" s="14" t="n"/>
+      <c r="F15" s="14" t="n"/>
+      <c r="G15" s="14" t="n"/>
+    </row>
+    <row r="16" ht="34" customHeight="1">
+      <c r="A16" s="14" t="n"/>
+      <c r="B16" s="14" t="n"/>
+      <c r="C16" s="14" t="n"/>
+      <c r="D16" s="14" t="n"/>
+      <c r="E16" s="14" t="n"/>
+      <c r="F16" s="14" t="n"/>
+      <c r="G16" s="14" t="n"/>
+    </row>
+    <row r="17" ht="34" customHeight="1">
+      <c r="A17" s="14" t="n"/>
+      <c r="B17" s="14" t="n"/>
+      <c r="C17" s="14" t="n"/>
+      <c r="D17" s="14" t="n"/>
+      <c r="E17" s="14" t="n"/>
+      <c r="F17" s="14" t="n"/>
+      <c r="G17" s="14" t="n"/>
+    </row>
+    <row r="18" ht="34" customHeight="1">
+      <c r="A18" s="14" t="n"/>
+      <c r="B18" s="14" t="n"/>
+      <c r="C18" s="14" t="n"/>
+      <c r="D18" s="14" t="n"/>
+      <c r="E18" s="14" t="n"/>
+      <c r="F18" s="14" t="n"/>
+      <c r="G18" s="14" t="n"/>
+    </row>
+    <row r="19" ht="16" customHeight="1">
+      <c r="A19" s="13" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="B7" s="12" t="inlineStr">
+      <c r="B19" s="13" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="C7" s="12" t="inlineStr">
+      <c r="C19" s="13" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="D7" s="13" t="inlineStr">
-        <is>
-          <t>15
-⚑ [Client] Project kick-off
-[WDCO Internal PM] G&amp;B office unavailable 1-24 Aug</t>
-        </is>
-      </c>
-      <c r="E7" s="14" t="inlineStr">
-        <is>
-          <t>16
-[Client] First RFI and FF&amp;E SHD V00 issue (16–22 Jul)</t>
-        </is>
-      </c>
-      <c r="F7" s="15" t="inlineStr">
-        <is>
-          <t>17
-[WDCO Internal PM] White-box availability confirmed as 30 Aug</t>
-        </is>
-      </c>
-      <c r="G7" s="12" t="inlineStr">
+      <c r="D19" s="13" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="E19" s="13" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="F19" s="13" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="G19" s="13" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="68" customHeight="1">
-      <c r="A8" s="12" t="inlineStr">
+    <row r="20" ht="34" customHeight="1">
+      <c r="A20" s="14" t="n"/>
+      <c r="B20" s="14" t="n"/>
+      <c r="C20" s="14" t="n"/>
+      <c r="D20" s="15" t="inlineStr">
+        <is>
+          <t>⚑ Project kick-off</t>
+        </is>
+      </c>
+      <c r="E20" s="16" t="inlineStr">
+        <is>
+          <t>First RFI and FF&amp;E SHD V00 issue</t>
+        </is>
+      </c>
+      <c r="F20" s="17" t="n"/>
+      <c r="G20" s="18" t="n"/>
+    </row>
+    <row r="21" ht="34" customHeight="1">
+      <c r="A21" s="14" t="n"/>
+      <c r="B21" s="14" t="n"/>
+      <c r="C21" s="14" t="n"/>
+      <c r="D21" s="19" t="inlineStr">
+        <is>
+          <t>G&amp;B office unavailable 1-24 Aug</t>
+        </is>
+      </c>
+      <c r="E21" s="14" t="n"/>
+      <c r="F21" s="19" t="inlineStr">
+        <is>
+          <t>White-box availability confirmed as 30 Aug</t>
+        </is>
+      </c>
+      <c r="G21" s="14" t="n"/>
+    </row>
+    <row r="22" ht="34" customHeight="1">
+      <c r="A22" s="14" t="n"/>
+      <c r="B22" s="14" t="n"/>
+      <c r="C22" s="14" t="n"/>
+      <c r="D22" s="14" t="n"/>
+      <c r="E22" s="14" t="n"/>
+      <c r="F22" s="14" t="n"/>
+      <c r="G22" s="14" t="n"/>
+    </row>
+    <row r="23" ht="34" customHeight="1">
+      <c r="A23" s="14" t="n"/>
+      <c r="B23" s="14" t="n"/>
+      <c r="C23" s="14" t="n"/>
+      <c r="D23" s="14" t="n"/>
+      <c r="E23" s="14" t="n"/>
+      <c r="F23" s="14" t="n"/>
+      <c r="G23" s="14" t="n"/>
+    </row>
+    <row r="24" ht="34" customHeight="1">
+      <c r="A24" s="14" t="n"/>
+      <c r="B24" s="14" t="n"/>
+      <c r="C24" s="14" t="n"/>
+      <c r="D24" s="14" t="n"/>
+      <c r="E24" s="14" t="n"/>
+      <c r="F24" s="14" t="n"/>
+      <c r="G24" s="14" t="n"/>
+    </row>
+    <row r="25" ht="34" customHeight="1">
+      <c r="A25" s="14" t="n"/>
+      <c r="B25" s="14" t="n"/>
+      <c r="C25" s="14" t="n"/>
+      <c r="D25" s="14" t="n"/>
+      <c r="E25" s="14" t="n"/>
+      <c r="F25" s="14" t="n"/>
+      <c r="G25" s="14" t="n"/>
+    </row>
+    <row r="26" ht="16" customHeight="1">
+      <c r="A26" s="13" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="B8" s="12" t="inlineStr">
+      <c r="B26" s="13" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="C8" s="12" t="inlineStr">
+      <c r="C26" s="13" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="D8" s="16" t="inlineStr">
-        <is>
-          <t>22
-⚑ [Supplier] SHD V00 parallel review &amp; feedback (22–28 Jul)</t>
-        </is>
-      </c>
-      <c r="E8" s="14" t="inlineStr">
-        <is>
-          <t>23
-[Client] FF&amp;E SHD V00 parallel review &amp; feedback (23–29 Jul)</t>
-        </is>
-      </c>
-      <c r="F8" s="12" t="inlineStr">
+      <c r="D26" s="13" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="E26" s="13" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="F26" s="13" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="G8" s="12" t="inlineStr">
+      <c r="G26" s="13" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="102" customHeight="1">
-      <c r="A9" s="12" t="inlineStr">
+    <row r="27" ht="34" customHeight="1">
+      <c r="A27" s="16" t="inlineStr">
+        <is>
+          <t>First RFI and FF&amp;E SHD V00 issue</t>
+        </is>
+      </c>
+      <c r="B27" s="17" t="n"/>
+      <c r="C27" s="17" t="n"/>
+      <c r="D27" s="18" t="n"/>
+      <c r="E27" s="16" t="inlineStr">
+        <is>
+          <t>FF&amp;E SHD V00 parallel review &amp; feedback</t>
+        </is>
+      </c>
+      <c r="F27" s="17" t="n"/>
+      <c r="G27" s="18" t="n"/>
+    </row>
+    <row r="28" ht="34" customHeight="1">
+      <c r="A28" s="14" t="n"/>
+      <c r="B28" s="14" t="n"/>
+      <c r="C28" s="14" t="n"/>
+      <c r="D28" s="20" t="inlineStr">
+        <is>
+          <t>⚑ SHD V00 parallel review &amp; feedback</t>
+        </is>
+      </c>
+      <c r="E28" s="17" t="n"/>
+      <c r="F28" s="17" t="n"/>
+      <c r="G28" s="18" t="n"/>
+    </row>
+    <row r="29" ht="34" customHeight="1">
+      <c r="A29" s="14" t="n"/>
+      <c r="B29" s="14" t="n"/>
+      <c r="C29" s="14" t="n"/>
+      <c r="D29" s="14" t="n"/>
+      <c r="E29" s="14" t="n"/>
+      <c r="F29" s="14" t="n"/>
+      <c r="G29" s="14" t="n"/>
+    </row>
+    <row r="30" ht="34" customHeight="1">
+      <c r="A30" s="14" t="n"/>
+      <c r="B30" s="14" t="n"/>
+      <c r="C30" s="14" t="n"/>
+      <c r="D30" s="14" t="n"/>
+      <c r="E30" s="14" t="n"/>
+      <c r="F30" s="14" t="n"/>
+      <c r="G30" s="14" t="n"/>
+    </row>
+    <row r="31" ht="34" customHeight="1">
+      <c r="A31" s="14" t="n"/>
+      <c r="B31" s="14" t="n"/>
+      <c r="C31" s="14" t="n"/>
+      <c r="D31" s="14" t="n"/>
+      <c r="E31" s="14" t="n"/>
+      <c r="F31" s="14" t="n"/>
+      <c r="G31" s="14" t="n"/>
+    </row>
+    <row r="32" ht="34" customHeight="1">
+      <c r="A32" s="14" t="n"/>
+      <c r="B32" s="14" t="n"/>
+      <c r="C32" s="14" t="n"/>
+      <c r="D32" s="14" t="n"/>
+      <c r="E32" s="14" t="n"/>
+      <c r="F32" s="14" t="n"/>
+      <c r="G32" s="14" t="n"/>
+    </row>
+    <row r="33" ht="16" customHeight="1">
+      <c r="A33" s="13" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="B9" s="13" t="inlineStr">
-        <is>
-          <t>27
-⚑ [Supplier] Material scope issued to Production Partner
-[Supplier] Round 1 sample-box development (27–7 Aug)</t>
-        </is>
-      </c>
-      <c r="C9" s="12" t="inlineStr">
+      <c r="B33" s="13" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="C33" s="13" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="D9" s="17" t="inlineStr">
-        <is>
-          <t>29
-[Supplier] SHD V01 drafting and issue (29–4 Aug)</t>
-        </is>
-      </c>
-      <c r="E9" s="13" t="inlineStr">
-        <is>
-          <t>30
-[Client] FF&amp;E SHD V01 drafting (30–3 Aug)
-⚑ [Client] Fit-out RFI closure</t>
-        </is>
-      </c>
-      <c r="F9" s="17" t="inlineStr">
-        <is>
-          <t>31
-[Supplier] Fit-Out SHD Version 00 (31–20 Aug)</t>
-        </is>
-      </c>
-      <c r="G9" s="11" t="n"/>
+      <c r="D33" s="13" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="E33" s="13" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="F33" s="13" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="G33" s="12" t="n"/>
+    </row>
+    <row r="34" ht="34" customHeight="1">
+      <c r="A34" s="16" t="inlineStr">
+        <is>
+          <t>FF&amp;E SHD V00 parallel review &amp; feedback</t>
+        </is>
+      </c>
+      <c r="B34" s="17" t="n"/>
+      <c r="C34" s="17" t="n"/>
+      <c r="D34" s="18" t="n"/>
+      <c r="E34" s="16" t="inlineStr">
+        <is>
+          <t>FF&amp;E SHD V01 drafting</t>
+        </is>
+      </c>
+      <c r="F34" s="17" t="n"/>
+      <c r="G34" s="18" t="n"/>
+    </row>
+    <row r="35" ht="34" customHeight="1">
+      <c r="A35" s="20" t="inlineStr">
+        <is>
+          <t>⚑ SHD V00 parallel review &amp; feedback</t>
+        </is>
+      </c>
+      <c r="B35" s="17" t="n"/>
+      <c r="C35" s="18" t="n"/>
+      <c r="D35" s="21" t="inlineStr">
+        <is>
+          <t>SHD V01 drafting and issue</t>
+        </is>
+      </c>
+      <c r="E35" s="17" t="n"/>
+      <c r="F35" s="17" t="n"/>
+      <c r="G35" s="18" t="n"/>
+    </row>
+    <row r="36" ht="34" customHeight="1">
+      <c r="A36" s="14" t="n"/>
+      <c r="B36" s="21" t="inlineStr">
+        <is>
+          <t>Round 1 sample-box development</t>
+        </is>
+      </c>
+      <c r="C36" s="17" t="n"/>
+      <c r="D36" s="17" t="n"/>
+      <c r="E36" s="17" t="n"/>
+      <c r="F36" s="17" t="n"/>
+      <c r="G36" s="18" t="n"/>
+    </row>
+    <row r="37" ht="34" customHeight="1">
+      <c r="A37" s="14" t="n"/>
+      <c r="B37" s="22" t="inlineStr">
+        <is>
+          <t>⚑ Material scope issued to Production Partner</t>
+        </is>
+      </c>
+      <c r="C37" s="14" t="n"/>
+      <c r="D37" s="14" t="n"/>
+      <c r="E37" s="15" t="inlineStr">
+        <is>
+          <t>⚑ Fit-out RFI closure</t>
+        </is>
+      </c>
+      <c r="F37" s="21" t="inlineStr">
+        <is>
+          <t>Fit-Out SHD Version 00</t>
+        </is>
+      </c>
+      <c r="G37" s="18" t="n"/>
+    </row>
+    <row r="38" ht="34" customHeight="1">
+      <c r="A38" s="14" t="n"/>
+      <c r="B38" s="14" t="n"/>
+      <c r="C38" s="14" t="n"/>
+      <c r="D38" s="14" t="n"/>
+      <c r="E38" s="14" t="n"/>
+      <c r="F38" s="23" t="inlineStr">
+        <is>
+          <t>Send project update to client-facing group</t>
+        </is>
+      </c>
+      <c r="G38" s="14" t="n"/>
+    </row>
+    <row r="39" ht="34" customHeight="1">
+      <c r="A39" s="14" t="n"/>
+      <c r="B39" s="14" t="n"/>
+      <c r="C39" s="14" t="n"/>
+      <c r="D39" s="14" t="n"/>
+      <c r="E39" s="14" t="n"/>
+      <c r="F39" s="19" t="inlineStr">
+        <is>
+          <t>Send project update to internal WDCO K5M group</t>
+        </is>
+      </c>
+      <c r="G39" s="14" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="5">
-    <mergeCell ref="A2:B2"/>
+  <mergeCells count="15">
+    <mergeCell ref="F37:G37"/>
+    <mergeCell ref="A27:D27"/>
     <mergeCell ref="A1:G1"/>
-    <mergeCell ref="C2:D2"/>
-    <mergeCell ref="G2:H2"/>
-    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="B36:G36"/>
+    <mergeCell ref="E27:G27"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="D35:G35"/>
+    <mergeCell ref="B2"/>
+    <mergeCell ref="A2"/>
+    <mergeCell ref="E34:G34"/>
+    <mergeCell ref="D2"/>
+    <mergeCell ref="C2"/>
+    <mergeCell ref="A35:C35"/>
+    <mergeCell ref="D28:G28"/>
+    <mergeCell ref="E20:G20"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2316,281 +3040,820 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H10"/>
+  <dimension ref="A1:G46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="26" customWidth="1" min="5" max="5"/>
+    <col width="26" customWidth="1" min="6" max="6"/>
+    <col width="26" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="5" t="inlineStr">
+      <c r="A1" s="10" t="inlineStr">
         <is>
           <t>K5M — AUGUST 2026</t>
         </is>
       </c>
     </row>
     <row r="2" ht="16" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">  Client</t>
         </is>
       </c>
-      <c r="C2" s="7" t="inlineStr">
+      <c r="B2" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">  Supplier</t>
         </is>
       </c>
-      <c r="E2" s="8" t="inlineStr">
+      <c r="C2" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">  WDCO Internal PM</t>
         </is>
       </c>
-      <c r="G2" s="9" t="inlineStr">
+      <c r="D2" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">  Deadline (red border)</t>
         </is>
       </c>
     </row>
     <row r="4" ht="18" customHeight="1">
-      <c r="A4" s="10" t="inlineStr">
+      <c r="A4" s="11" t="inlineStr">
         <is>
           <t>Sunday</t>
         </is>
       </c>
-      <c r="B4" s="10" t="inlineStr">
+      <c r="B4" s="11" t="inlineStr">
         <is>
           <t>Monday</t>
         </is>
       </c>
-      <c r="C4" s="10" t="inlineStr">
+      <c r="C4" s="11" t="inlineStr">
         <is>
           <t>Tuesday</t>
         </is>
       </c>
-      <c r="D4" s="10" t="inlineStr">
+      <c r="D4" s="11" t="inlineStr">
         <is>
           <t>Wednesday</t>
         </is>
       </c>
-      <c r="E4" s="10" t="inlineStr">
+      <c r="E4" s="11" t="inlineStr">
         <is>
           <t>Thursday</t>
         </is>
       </c>
-      <c r="F4" s="10" t="inlineStr">
+      <c r="F4" s="11" t="inlineStr">
         <is>
           <t>Friday</t>
         </is>
       </c>
-      <c r="G4" s="10" t="inlineStr">
+      <c r="G4" s="11" t="inlineStr">
         <is>
           <t>Saturday</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="60" customHeight="1">
-      <c r="A5" s="11" t="n"/>
-      <c r="B5" s="11" t="n"/>
-      <c r="C5" s="11" t="n"/>
-      <c r="D5" s="11" t="n"/>
-      <c r="E5" s="11" t="n"/>
-      <c r="F5" s="11" t="n"/>
-      <c r="G5" s="12" t="inlineStr">
+    <row r="5" ht="16" customHeight="1">
+      <c r="A5" s="12" t="n"/>
+      <c r="B5" s="12" t="n"/>
+      <c r="C5" s="12" t="n"/>
+      <c r="D5" s="12" t="n"/>
+      <c r="E5" s="12" t="n"/>
+      <c r="F5" s="12" t="n"/>
+      <c r="G5" s="13" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="68" customHeight="1">
-      <c r="A6" s="12" t="inlineStr">
+    <row r="6" ht="34" customHeight="1">
+      <c r="A6" s="16" t="inlineStr">
+        <is>
+          <t>FF&amp;E SHD V00 parallel review &amp; feedback</t>
+        </is>
+      </c>
+      <c r="B6" s="17" t="n"/>
+      <c r="C6" s="17" t="n"/>
+      <c r="D6" s="18" t="n"/>
+      <c r="E6" s="16" t="inlineStr">
+        <is>
+          <t>FF&amp;E SHD V01 drafting</t>
+        </is>
+      </c>
+      <c r="F6" s="17" t="n"/>
+      <c r="G6" s="18" t="n"/>
+    </row>
+    <row r="7" ht="34" customHeight="1">
+      <c r="A7" s="20" t="inlineStr">
+        <is>
+          <t>⚑ SHD V00 parallel review &amp; feedback</t>
+        </is>
+      </c>
+      <c r="B7" s="17" t="n"/>
+      <c r="C7" s="18" t="n"/>
+      <c r="D7" s="21" t="inlineStr">
+        <is>
+          <t>SHD V01 drafting and issue</t>
+        </is>
+      </c>
+      <c r="E7" s="17" t="n"/>
+      <c r="F7" s="17" t="n"/>
+      <c r="G7" s="18" t="n"/>
+    </row>
+    <row r="8" ht="34" customHeight="1">
+      <c r="A8" s="14" t="n"/>
+      <c r="B8" s="21" t="inlineStr">
+        <is>
+          <t>Round 1 sample-box development</t>
+        </is>
+      </c>
+      <c r="C8" s="17" t="n"/>
+      <c r="D8" s="17" t="n"/>
+      <c r="E8" s="17" t="n"/>
+      <c r="F8" s="17" t="n"/>
+      <c r="G8" s="18" t="n"/>
+    </row>
+    <row r="9" ht="34" customHeight="1">
+      <c r="A9" s="14" t="n"/>
+      <c r="B9" s="22" t="inlineStr">
+        <is>
+          <t>⚑ Material scope issued to Production Partner</t>
+        </is>
+      </c>
+      <c r="C9" s="14" t="n"/>
+      <c r="D9" s="14" t="n"/>
+      <c r="E9" s="15" t="inlineStr">
+        <is>
+          <t>⚑ Fit-out RFI closure</t>
+        </is>
+      </c>
+      <c r="F9" s="21" t="inlineStr">
+        <is>
+          <t>Fit-Out SHD Version 00</t>
+        </is>
+      </c>
+      <c r="G9" s="18" t="n"/>
+    </row>
+    <row r="10" ht="34" customHeight="1">
+      <c r="A10" s="14" t="n"/>
+      <c r="B10" s="14" t="n"/>
+      <c r="C10" s="14" t="n"/>
+      <c r="D10" s="14" t="n"/>
+      <c r="E10" s="14" t="n"/>
+      <c r="F10" s="23" t="inlineStr">
+        <is>
+          <t>Send project update to client-facing group</t>
+        </is>
+      </c>
+      <c r="G10" s="14" t="n"/>
+    </row>
+    <row r="11" ht="34" customHeight="1">
+      <c r="A11" s="14" t="n"/>
+      <c r="B11" s="14" t="n"/>
+      <c r="C11" s="14" t="n"/>
+      <c r="D11" s="14" t="n"/>
+      <c r="E11" s="14" t="n"/>
+      <c r="F11" s="19" t="inlineStr">
+        <is>
+          <t>Send project update to internal WDCO K5M group</t>
+        </is>
+      </c>
+      <c r="G11" s="14" t="n"/>
+    </row>
+    <row r="12" ht="16" customHeight="1">
+      <c r="A12" s="13" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B6" s="14" t="inlineStr">
-        <is>
-          <t>3
-[Client] Fit-out SHD V00 &amp; preliminary material package (3–21 Aug)</t>
-        </is>
-      </c>
-      <c r="C6" s="12" t="inlineStr">
+      <c r="B12" s="13" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C12" s="13" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D6" s="17" t="inlineStr">
-        <is>
-          <t>5
-[Supplier] SHD V01 parallel review &amp; feedback (5–11 Aug)</t>
-        </is>
-      </c>
-      <c r="E6" s="12" t="inlineStr">
+      <c r="D12" s="13" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E12" s="13" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="F6" s="12" t="inlineStr">
+      <c r="F12" s="13" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="G6" s="16" t="inlineStr">
-        <is>
-          <t>8
-⚑ [Supplier] Dispatch/delivery Round 1 sample box to Dubai (8–10 Aug)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="68" customHeight="1">
-      <c r="A7" s="12" t="inlineStr">
+      <c r="G12" s="13" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="34" customHeight="1">
+      <c r="A13" s="21" t="inlineStr">
+        <is>
+          <t>Fit-Out SHD Version 00</t>
+        </is>
+      </c>
+      <c r="B13" s="17" t="n"/>
+      <c r="C13" s="17" t="n"/>
+      <c r="D13" s="17" t="n"/>
+      <c r="E13" s="17" t="n"/>
+      <c r="F13" s="17" t="n"/>
+      <c r="G13" s="18" t="n"/>
+    </row>
+    <row r="14" ht="34" customHeight="1">
+      <c r="A14" s="21" t="inlineStr">
+        <is>
+          <t>Round 1 sample-box development</t>
+        </is>
+      </c>
+      <c r="B14" s="17" t="n"/>
+      <c r="C14" s="17" t="n"/>
+      <c r="D14" s="17" t="n"/>
+      <c r="E14" s="17" t="n"/>
+      <c r="F14" s="18" t="n"/>
+      <c r="G14" s="22" t="inlineStr">
+        <is>
+          <t>⚑ Dispatch/delivery Round 1 sample box to Dubai</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="34" customHeight="1">
+      <c r="A15" s="21" t="inlineStr">
+        <is>
+          <t>SHD V01 drafting and issue</t>
+        </is>
+      </c>
+      <c r="B15" s="17" t="n"/>
+      <c r="C15" s="18" t="n"/>
+      <c r="D15" s="21" t="inlineStr">
+        <is>
+          <t>SHD V01 parallel review &amp; feedback</t>
+        </is>
+      </c>
+      <c r="E15" s="17" t="n"/>
+      <c r="F15" s="17" t="n"/>
+      <c r="G15" s="18" t="n"/>
+    </row>
+    <row r="16" ht="34" customHeight="1">
+      <c r="A16" s="16" t="inlineStr">
+        <is>
+          <t>FF&amp;E SHD V01 drafting</t>
+        </is>
+      </c>
+      <c r="B16" s="18" t="n"/>
+      <c r="C16" s="14" t="n"/>
+      <c r="D16" s="14" t="n"/>
+      <c r="E16" s="14" t="n"/>
+      <c r="F16" s="19" t="inlineStr">
+        <is>
+          <t>Send project update to internal WDCO K5M group</t>
+        </is>
+      </c>
+      <c r="G16" s="14" t="n"/>
+    </row>
+    <row r="17" ht="34" customHeight="1">
+      <c r="A17" s="14" t="n"/>
+      <c r="B17" s="16" t="inlineStr">
+        <is>
+          <t>Fit-out SHD V00 &amp; preliminary material package</t>
+        </is>
+      </c>
+      <c r="C17" s="17" t="n"/>
+      <c r="D17" s="17" t="n"/>
+      <c r="E17" s="17" t="n"/>
+      <c r="F17" s="17" t="n"/>
+      <c r="G17" s="18" t="n"/>
+    </row>
+    <row r="18" ht="34" customHeight="1">
+      <c r="A18" s="14" t="n"/>
+      <c r="B18" s="14" t="n"/>
+      <c r="C18" s="14" t="n"/>
+      <c r="D18" s="14" t="n"/>
+      <c r="E18" s="14" t="n"/>
+      <c r="F18" s="14" t="n"/>
+      <c r="G18" s="14" t="n"/>
+    </row>
+    <row r="19" ht="16" customHeight="1">
+      <c r="A19" s="13" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="B7" s="12" t="inlineStr">
+      <c r="B19" s="13" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="C7" s="17" t="inlineStr">
-        <is>
-          <t>11
-[Supplier] Feedback round &amp; final approved material box (11–10 Sep)</t>
-        </is>
-      </c>
-      <c r="D7" s="16" t="inlineStr">
-        <is>
-          <t>12
-⚑ [Supplier] Signed GFP SHD Version 02 (12–10 Sep)</t>
-        </is>
-      </c>
-      <c r="E7" s="12" t="inlineStr">
+      <c r="C19" s="13" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D19" s="13" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E19" s="13" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="F7" s="12" t="inlineStr">
+      <c r="F19" s="13" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="G7" s="12" t="inlineStr">
+      <c r="G19" s="13" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="60" customHeight="1">
-      <c r="A8" s="12" t="inlineStr">
+    <row r="20" ht="34" customHeight="1">
+      <c r="A20" s="16" t="inlineStr">
+        <is>
+          <t>Fit-out SHD V00 &amp; preliminary material package</t>
+        </is>
+      </c>
+      <c r="B20" s="17" t="n"/>
+      <c r="C20" s="17" t="n"/>
+      <c r="D20" s="17" t="n"/>
+      <c r="E20" s="17" t="n"/>
+      <c r="F20" s="17" t="n"/>
+      <c r="G20" s="18" t="n"/>
+    </row>
+    <row r="21" ht="34" customHeight="1">
+      <c r="A21" s="21" t="inlineStr">
+        <is>
+          <t>Fit-Out SHD Version 00</t>
+        </is>
+      </c>
+      <c r="B21" s="17" t="n"/>
+      <c r="C21" s="17" t="n"/>
+      <c r="D21" s="17" t="n"/>
+      <c r="E21" s="17" t="n"/>
+      <c r="F21" s="17" t="n"/>
+      <c r="G21" s="18" t="n"/>
+    </row>
+    <row r="22" ht="34" customHeight="1">
+      <c r="A22" s="21" t="inlineStr">
+        <is>
+          <t>SHD V01 parallel review &amp; feedback</t>
+        </is>
+      </c>
+      <c r="B22" s="17" t="n"/>
+      <c r="C22" s="18" t="n"/>
+      <c r="D22" s="20" t="inlineStr">
+        <is>
+          <t>⚑ Signed GFP SHD Version 02</t>
+        </is>
+      </c>
+      <c r="E22" s="17" t="n"/>
+      <c r="F22" s="17" t="n"/>
+      <c r="G22" s="18" t="n"/>
+    </row>
+    <row r="23" ht="34" customHeight="1">
+      <c r="A23" s="20" t="inlineStr">
+        <is>
+          <t>⚑ Dispatch/delivery Round 1 sample box to Dubai</t>
+        </is>
+      </c>
+      <c r="B23" s="18" t="n"/>
+      <c r="C23" s="21" t="inlineStr">
+        <is>
+          <t>Feedback round &amp; final approved material box</t>
+        </is>
+      </c>
+      <c r="D23" s="17" t="n"/>
+      <c r="E23" s="17" t="n"/>
+      <c r="F23" s="17" t="n"/>
+      <c r="G23" s="18" t="n"/>
+    </row>
+    <row r="24" ht="34" customHeight="1">
+      <c r="A24" s="14" t="n"/>
+      <c r="B24" s="14" t="n"/>
+      <c r="C24" s="14" t="n"/>
+      <c r="D24" s="14" t="n"/>
+      <c r="E24" s="14" t="n"/>
+      <c r="F24" s="23" t="inlineStr">
+        <is>
+          <t>Send project update to client-facing group</t>
+        </is>
+      </c>
+      <c r="G24" s="14" t="n"/>
+    </row>
+    <row r="25" ht="34" customHeight="1">
+      <c r="A25" s="14" t="n"/>
+      <c r="B25" s="14" t="n"/>
+      <c r="C25" s="14" t="n"/>
+      <c r="D25" s="14" t="n"/>
+      <c r="E25" s="14" t="n"/>
+      <c r="F25" s="19" t="inlineStr">
+        <is>
+          <t>Send project update to internal WDCO K5M group</t>
+        </is>
+      </c>
+      <c r="G25" s="14" t="n"/>
+    </row>
+    <row r="26" ht="16" customHeight="1">
+      <c r="A26" s="13" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="B8" s="12" t="inlineStr">
+      <c r="B26" s="13" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="C8" s="12" t="inlineStr">
+      <c r="C26" s="13" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="D8" s="12" t="inlineStr">
+      <c r="D26" s="13" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="E8" s="12" t="inlineStr">
+      <c r="E26" s="13" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="F8" s="12" t="inlineStr">
+      <c r="F26" s="13" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="G8" s="12" t="inlineStr">
+      <c r="G26" s="13" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="136" customHeight="1">
-      <c r="A9" s="12" t="inlineStr">
+    <row r="27" ht="34" customHeight="1">
+      <c r="A27" s="21" t="inlineStr">
+        <is>
+          <t>Feedback round &amp; final approved material box</t>
+        </is>
+      </c>
+      <c r="B27" s="17" t="n"/>
+      <c r="C27" s="17" t="n"/>
+      <c r="D27" s="17" t="n"/>
+      <c r="E27" s="17" t="n"/>
+      <c r="F27" s="17" t="n"/>
+      <c r="G27" s="18" t="n"/>
+    </row>
+    <row r="28" ht="34" customHeight="1">
+      <c r="A28" s="20" t="inlineStr">
+        <is>
+          <t>⚑ Signed GFP SHD Version 02</t>
+        </is>
+      </c>
+      <c r="B28" s="17" t="n"/>
+      <c r="C28" s="17" t="n"/>
+      <c r="D28" s="17" t="n"/>
+      <c r="E28" s="17" t="n"/>
+      <c r="F28" s="17" t="n"/>
+      <c r="G28" s="18" t="n"/>
+    </row>
+    <row r="29" ht="34" customHeight="1">
+      <c r="A29" s="16" t="inlineStr">
+        <is>
+          <t>Fit-out SHD V00 &amp; preliminary material package</t>
+        </is>
+      </c>
+      <c r="B29" s="17" t="n"/>
+      <c r="C29" s="17" t="n"/>
+      <c r="D29" s="17" t="n"/>
+      <c r="E29" s="17" t="n"/>
+      <c r="F29" s="18" t="n"/>
+      <c r="G29" s="14" t="n"/>
+    </row>
+    <row r="30" ht="34" customHeight="1">
+      <c r="A30" s="21" t="inlineStr">
+        <is>
+          <t>Fit-Out SHD Version 00</t>
+        </is>
+      </c>
+      <c r="B30" s="17" t="n"/>
+      <c r="C30" s="17" t="n"/>
+      <c r="D30" s="17" t="n"/>
+      <c r="E30" s="18" t="n"/>
+      <c r="F30" s="19" t="inlineStr">
+        <is>
+          <t>Send project update to internal WDCO K5M group</t>
+        </is>
+      </c>
+      <c r="G30" s="14" t="n"/>
+    </row>
+    <row r="31" ht="34" customHeight="1">
+      <c r="A31" s="14" t="n"/>
+      <c r="B31" s="14" t="n"/>
+      <c r="C31" s="14" t="n"/>
+      <c r="D31" s="14" t="n"/>
+      <c r="E31" s="14" t="n"/>
+      <c r="F31" s="14" t="n"/>
+      <c r="G31" s="14" t="n"/>
+    </row>
+    <row r="32" ht="34" customHeight="1">
+      <c r="A32" s="14" t="n"/>
+      <c r="B32" s="14" t="n"/>
+      <c r="C32" s="14" t="n"/>
+      <c r="D32" s="14" t="n"/>
+      <c r="E32" s="14" t="n"/>
+      <c r="F32" s="14" t="n"/>
+      <c r="G32" s="14" t="n"/>
+    </row>
+    <row r="33" ht="16" customHeight="1">
+      <c r="A33" s="13" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="B9" s="13" t="inlineStr">
-        <is>
-          <t>24
-⚑ [Client] G&amp;B team availability resumes
-[Client] FF&amp;E SHD V01 &amp; Material Package review (24–28 Aug)
-[Client] Fit-out SHD V00 review &amp; agreement in principle (24–28 Aug)</t>
-        </is>
-      </c>
-      <c r="C9" s="15" t="inlineStr">
-        <is>
-          <t>25
-[WDCO Internal PM] Site holiday period (Mawlid) (25–15 Sep)</t>
-        </is>
-      </c>
-      <c r="D9" s="12" t="inlineStr">
+      <c r="B33" s="13" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="C33" s="13" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D33" s="13" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="E9" s="12" t="inlineStr">
+      <c r="E33" s="13" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="F9" s="12" t="inlineStr">
+      <c r="F33" s="13" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="G9" s="12" t="inlineStr">
+      <c r="G33" s="13" t="inlineStr">
         <is>
           <t>29</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="136" customHeight="1">
-      <c r="A10" s="12" t="inlineStr">
+    <row r="34" ht="34" customHeight="1">
+      <c r="A34" s="21" t="inlineStr">
+        <is>
+          <t>Feedback round &amp; final approved material box</t>
+        </is>
+      </c>
+      <c r="B34" s="17" t="n"/>
+      <c r="C34" s="17" t="n"/>
+      <c r="D34" s="17" t="n"/>
+      <c r="E34" s="17" t="n"/>
+      <c r="F34" s="17" t="n"/>
+      <c r="G34" s="18" t="n"/>
+    </row>
+    <row r="35" ht="34" customHeight="1">
+      <c r="A35" s="20" t="inlineStr">
+        <is>
+          <t>⚑ Signed GFP SHD Version 02</t>
+        </is>
+      </c>
+      <c r="B35" s="17" t="n"/>
+      <c r="C35" s="17" t="n"/>
+      <c r="D35" s="17" t="n"/>
+      <c r="E35" s="17" t="n"/>
+      <c r="F35" s="17" t="n"/>
+      <c r="G35" s="18" t="n"/>
+    </row>
+    <row r="36" ht="34" customHeight="1">
+      <c r="A36" s="14" t="n"/>
+      <c r="B36" s="16" t="inlineStr">
+        <is>
+          <t>FF&amp;E SHD V01 &amp; Material Package review</t>
+        </is>
+      </c>
+      <c r="C36" s="17" t="n"/>
+      <c r="D36" s="17" t="n"/>
+      <c r="E36" s="17" t="n"/>
+      <c r="F36" s="18" t="n"/>
+      <c r="G36" s="14" t="n"/>
+    </row>
+    <row r="37" ht="34" customHeight="1">
+      <c r="A37" s="14" t="n"/>
+      <c r="B37" s="16" t="inlineStr">
+        <is>
+          <t>Fit-out SHD V00 review &amp; agreement in principle</t>
+        </is>
+      </c>
+      <c r="C37" s="17" t="n"/>
+      <c r="D37" s="17" t="n"/>
+      <c r="E37" s="17" t="n"/>
+      <c r="F37" s="18" t="n"/>
+      <c r="G37" s="14" t="n"/>
+    </row>
+    <row r="38" ht="34" customHeight="1">
+      <c r="A38" s="14" t="n"/>
+      <c r="B38" s="15" t="inlineStr">
+        <is>
+          <t>⚑ G&amp;B team availability resumes</t>
+        </is>
+      </c>
+      <c r="C38" s="24" t="inlineStr">
+        <is>
+          <t>Site holiday period (Mawlid)</t>
+        </is>
+      </c>
+      <c r="D38" s="17" t="n"/>
+      <c r="E38" s="17" t="n"/>
+      <c r="F38" s="17" t="n"/>
+      <c r="G38" s="18" t="n"/>
+    </row>
+    <row r="39" ht="34" customHeight="1">
+      <c r="A39" s="14" t="n"/>
+      <c r="B39" s="14" t="n"/>
+      <c r="C39" s="14" t="n"/>
+      <c r="D39" s="14" t="n"/>
+      <c r="E39" s="14" t="n"/>
+      <c r="F39" s="25" t="inlineStr">
+        <is>
+          <t>Send project update to client-facing group / +1 more (see Data tab)</t>
+        </is>
+      </c>
+      <c r="G39" s="14" t="n"/>
+    </row>
+    <row r="40" ht="16" customHeight="1">
+      <c r="A40" s="13" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="B10" s="18" t="inlineStr">
-        <is>
-          <t>31
-[Client] FF&amp;E SHD V02 drafting (31–2 Sep)
-[Client] Fit-out site survey
-[Supplier] Site visit / measurement</t>
-        </is>
-      </c>
-      <c r="C10" s="11" t="n"/>
-      <c r="D10" s="11" t="n"/>
-      <c r="E10" s="11" t="n"/>
-      <c r="F10" s="11" t="n"/>
-      <c r="G10" s="11" t="n"/>
+      <c r="B40" s="13" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="C40" s="12" t="n"/>
+      <c r="D40" s="12" t="n"/>
+      <c r="E40" s="12" t="n"/>
+      <c r="F40" s="12" t="n"/>
+      <c r="G40" s="12" t="n"/>
+    </row>
+    <row r="41" ht="34" customHeight="1">
+      <c r="A41" s="21" t="inlineStr">
+        <is>
+          <t>Feedback round &amp; final approved material box</t>
+        </is>
+      </c>
+      <c r="B41" s="17" t="n"/>
+      <c r="C41" s="17" t="n"/>
+      <c r="D41" s="17" t="n"/>
+      <c r="E41" s="17" t="n"/>
+      <c r="F41" s="17" t="n"/>
+      <c r="G41" s="18" t="n"/>
+    </row>
+    <row r="42" ht="34" customHeight="1">
+      <c r="A42" s="20" t="inlineStr">
+        <is>
+          <t>⚑ Signed GFP SHD Version 02</t>
+        </is>
+      </c>
+      <c r="B42" s="17" t="n"/>
+      <c r="C42" s="17" t="n"/>
+      <c r="D42" s="17" t="n"/>
+      <c r="E42" s="17" t="n"/>
+      <c r="F42" s="17" t="n"/>
+      <c r="G42" s="18" t="n"/>
+    </row>
+    <row r="43" ht="34" customHeight="1">
+      <c r="A43" s="24" t="inlineStr">
+        <is>
+          <t>Site holiday period (Mawlid)</t>
+        </is>
+      </c>
+      <c r="B43" s="17" t="n"/>
+      <c r="C43" s="17" t="n"/>
+      <c r="D43" s="17" t="n"/>
+      <c r="E43" s="17" t="n"/>
+      <c r="F43" s="17" t="n"/>
+      <c r="G43" s="18" t="n"/>
+    </row>
+    <row r="44" ht="34" customHeight="1">
+      <c r="A44" s="14" t="n"/>
+      <c r="B44" s="16" t="inlineStr">
+        <is>
+          <t>FF&amp;E SHD V02 drafting</t>
+        </is>
+      </c>
+      <c r="C44" s="17" t="n"/>
+      <c r="D44" s="18" t="n"/>
+      <c r="E44" s="26" t="inlineStr">
+        <is>
+          <t>⚑ Signed FF&amp;E SHD V02 &amp; confirmed material package</t>
+        </is>
+      </c>
+      <c r="F44" s="17" t="n"/>
+      <c r="G44" s="18" t="n"/>
+    </row>
+    <row r="45" ht="34" customHeight="1">
+      <c r="A45" s="14" t="n"/>
+      <c r="B45" s="23" t="inlineStr">
+        <is>
+          <t>Fit-out site survey</t>
+        </is>
+      </c>
+      <c r="C45" s="16" t="inlineStr">
+        <is>
+          <t>Fit-out site-survey report</t>
+        </is>
+      </c>
+      <c r="D45" s="17" t="n"/>
+      <c r="E45" s="17" t="n"/>
+      <c r="F45" s="18" t="n"/>
+      <c r="G45" s="14" t="n"/>
+    </row>
+    <row r="46" ht="34" customHeight="1">
+      <c r="A46" s="14" t="n"/>
+      <c r="B46" s="27" t="inlineStr">
+        <is>
+          <t>Site visit / measurement</t>
+        </is>
+      </c>
+      <c r="C46" s="21" t="inlineStr">
+        <is>
+          <t>Site survey report</t>
+        </is>
+      </c>
+      <c r="D46" s="17" t="n"/>
+      <c r="E46" s="18" t="n"/>
+      <c r="F46" s="28" t="inlineStr">
+        <is>
+          <t>Fit-Out SHD V01 incorporating survey / +1 more (see Data tab)</t>
+        </is>
+      </c>
+      <c r="G46" s="18" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="5">
-    <mergeCell ref="A2:B2"/>
+  <mergeCells count="40">
+    <mergeCell ref="A30:E30"/>
+    <mergeCell ref="B17:G17"/>
+    <mergeCell ref="A35:G35"/>
+    <mergeCell ref="B8:G8"/>
+    <mergeCell ref="A20:G20"/>
+    <mergeCell ref="D15:G15"/>
+    <mergeCell ref="B44:D44"/>
+    <mergeCell ref="A43:G43"/>
+    <mergeCell ref="E6:G6"/>
+    <mergeCell ref="A28:G28"/>
+    <mergeCell ref="C46:E46"/>
+    <mergeCell ref="A13:G13"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="A14:F14"/>
+    <mergeCell ref="A34:G34"/>
+    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="A29:F29"/>
+    <mergeCell ref="D22:G22"/>
+    <mergeCell ref="C45:F45"/>
     <mergeCell ref="A1:G1"/>
-    <mergeCell ref="C2:D2"/>
-    <mergeCell ref="G2:H2"/>
-    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="A6:D6"/>
+    <mergeCell ref="B37:F37"/>
+    <mergeCell ref="B2"/>
+    <mergeCell ref="F46:G46"/>
+    <mergeCell ref="D2"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="A15:C15"/>
+    <mergeCell ref="C23:G23"/>
+    <mergeCell ref="A41:G41"/>
+    <mergeCell ref="F9:G9"/>
+    <mergeCell ref="A27:G27"/>
+    <mergeCell ref="C38:G38"/>
+    <mergeCell ref="A21:G21"/>
+    <mergeCell ref="D7:G7"/>
+    <mergeCell ref="A2"/>
+    <mergeCell ref="C2"/>
+    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="E44:G44"/>
+    <mergeCell ref="A7:C7"/>
+    <mergeCell ref="A42:G42"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2602,267 +3865,703 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:G39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="26" customWidth="1" min="5" max="5"/>
+    <col width="26" customWidth="1" min="6" max="6"/>
+    <col width="26" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="5" t="inlineStr">
+      <c r="A1" s="10" t="inlineStr">
         <is>
           <t>K5M — SEPTEMBER 2026</t>
         </is>
       </c>
     </row>
     <row r="2" ht="16" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">  Client</t>
         </is>
       </c>
-      <c r="C2" s="7" t="inlineStr">
+      <c r="B2" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">  Supplier</t>
         </is>
       </c>
-      <c r="E2" s="8" t="inlineStr">
+      <c r="C2" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">  WDCO Internal PM</t>
         </is>
       </c>
-      <c r="G2" s="9" t="inlineStr">
+      <c r="D2" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">  Deadline (red border)</t>
         </is>
       </c>
     </row>
     <row r="4" ht="18" customHeight="1">
-      <c r="A4" s="10" t="inlineStr">
+      <c r="A4" s="11" t="inlineStr">
         <is>
           <t>Sunday</t>
         </is>
       </c>
-      <c r="B4" s="10" t="inlineStr">
+      <c r="B4" s="11" t="inlineStr">
         <is>
           <t>Monday</t>
         </is>
       </c>
-      <c r="C4" s="10" t="inlineStr">
+      <c r="C4" s="11" t="inlineStr">
         <is>
           <t>Tuesday</t>
         </is>
       </c>
-      <c r="D4" s="10" t="inlineStr">
+      <c r="D4" s="11" t="inlineStr">
         <is>
           <t>Wednesday</t>
         </is>
       </c>
-      <c r="E4" s="10" t="inlineStr">
+      <c r="E4" s="11" t="inlineStr">
         <is>
           <t>Thursday</t>
         </is>
       </c>
-      <c r="F4" s="10" t="inlineStr">
+      <c r="F4" s="11" t="inlineStr">
         <is>
           <t>Friday</t>
         </is>
       </c>
-      <c r="G4" s="10" t="inlineStr">
+      <c r="G4" s="11" t="inlineStr">
         <is>
           <t>Saturday</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="102" customHeight="1">
-      <c r="A5" s="11" t="n"/>
-      <c r="B5" s="11" t="n"/>
-      <c r="C5" s="18" t="inlineStr">
-        <is>
-          <t>1
-[Client] Fit-out site-survey report (1–4 Sep)
-[Supplier] Site survey report (1–3 Sep)</t>
-        </is>
-      </c>
-      <c r="D5" s="12" t="inlineStr">
+    <row r="5" ht="16" customHeight="1">
+      <c r="A5" s="12" t="n"/>
+      <c r="B5" s="12" t="n"/>
+      <c r="C5" s="13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D5" s="13" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E5" s="19" t="inlineStr">
-        <is>
-          <t>3
-⚑ [Client] Signed FF&amp;E SHD V02 &amp; confirmed material package (3–8 Sep)</t>
-        </is>
-      </c>
-      <c r="F5" s="17" t="inlineStr">
-        <is>
-          <t>4
-[Supplier] Fit-Out SHD V01 incorporating survey (4–10 Sep)</t>
-        </is>
-      </c>
-      <c r="G5" s="12" t="inlineStr">
+      <c r="E5" s="13" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F5" s="13" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G5" s="13" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="136" customHeight="1">
-      <c r="A6" s="12" t="inlineStr">
+    <row r="6" ht="34" customHeight="1">
+      <c r="A6" s="21" t="inlineStr">
+        <is>
+          <t>Feedback round &amp; final approved material box</t>
+        </is>
+      </c>
+      <c r="B6" s="17" t="n"/>
+      <c r="C6" s="17" t="n"/>
+      <c r="D6" s="17" t="n"/>
+      <c r="E6" s="17" t="n"/>
+      <c r="F6" s="17" t="n"/>
+      <c r="G6" s="18" t="n"/>
+    </row>
+    <row r="7" ht="34" customHeight="1">
+      <c r="A7" s="20" t="inlineStr">
+        <is>
+          <t>⚑ Signed GFP SHD Version 02</t>
+        </is>
+      </c>
+      <c r="B7" s="17" t="n"/>
+      <c r="C7" s="17" t="n"/>
+      <c r="D7" s="17" t="n"/>
+      <c r="E7" s="17" t="n"/>
+      <c r="F7" s="17" t="n"/>
+      <c r="G7" s="18" t="n"/>
+    </row>
+    <row r="8" ht="34" customHeight="1">
+      <c r="A8" s="24" t="inlineStr">
+        <is>
+          <t>Site holiday period (Mawlid)</t>
+        </is>
+      </c>
+      <c r="B8" s="17" t="n"/>
+      <c r="C8" s="17" t="n"/>
+      <c r="D8" s="17" t="n"/>
+      <c r="E8" s="17" t="n"/>
+      <c r="F8" s="17" t="n"/>
+      <c r="G8" s="18" t="n"/>
+    </row>
+    <row r="9" ht="34" customHeight="1">
+      <c r="A9" s="14" t="n"/>
+      <c r="B9" s="16" t="inlineStr">
+        <is>
+          <t>FF&amp;E SHD V02 drafting</t>
+        </is>
+      </c>
+      <c r="C9" s="17" t="n"/>
+      <c r="D9" s="18" t="n"/>
+      <c r="E9" s="26" t="inlineStr">
+        <is>
+          <t>⚑ Signed FF&amp;E SHD V02 &amp; confirmed material package</t>
+        </is>
+      </c>
+      <c r="F9" s="17" t="n"/>
+      <c r="G9" s="18" t="n"/>
+    </row>
+    <row r="10" ht="34" customHeight="1">
+      <c r="A10" s="14" t="n"/>
+      <c r="B10" s="23" t="inlineStr">
+        <is>
+          <t>Fit-out site survey</t>
+        </is>
+      </c>
+      <c r="C10" s="16" t="inlineStr">
+        <is>
+          <t>Fit-out site-survey report</t>
+        </is>
+      </c>
+      <c r="D10" s="17" t="n"/>
+      <c r="E10" s="17" t="n"/>
+      <c r="F10" s="18" t="n"/>
+      <c r="G10" s="14" t="n"/>
+    </row>
+    <row r="11" ht="34" customHeight="1">
+      <c r="A11" s="14" t="n"/>
+      <c r="B11" s="27" t="inlineStr">
+        <is>
+          <t>Site visit / measurement</t>
+        </is>
+      </c>
+      <c r="C11" s="21" t="inlineStr">
+        <is>
+          <t>Site survey report</t>
+        </is>
+      </c>
+      <c r="D11" s="17" t="n"/>
+      <c r="E11" s="18" t="n"/>
+      <c r="F11" s="28" t="inlineStr">
+        <is>
+          <t>Fit-Out SHD V01 incorporating survey / +1 more (see Data tab)</t>
+        </is>
+      </c>
+      <c r="G11" s="18" t="n"/>
+    </row>
+    <row r="12" ht="16" customHeight="1">
+      <c r="A12" s="13" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="B6" s="14" t="inlineStr">
-        <is>
-          <t>7
-[Client] Fit-out SHD V01 revisions (7–15 Sep)</t>
-        </is>
-      </c>
-      <c r="C6" s="12" t="inlineStr">
+      <c r="B12" s="13" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="C12" s="13" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D6" s="14" t="inlineStr">
-        <is>
-          <t>9
-[Client] FF&amp;E mock-up production, QC and packing (9–23 Oct)</t>
-        </is>
-      </c>
-      <c r="E6" s="13" t="inlineStr">
-        <is>
-          <t>10
-[Supplier] FF&amp;E production (10–9 Oct)
-⚑ [Supplier] Signed GFP Fit-Out SHD
-[Supplier] Fit-Out production (10–24 Sep)</t>
-        </is>
-      </c>
-      <c r="F6" s="12" t="inlineStr">
+      <c r="D12" s="13" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E12" s="13" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="F12" s="13" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="G6" s="12" t="inlineStr">
+      <c r="G12" s="13" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="68" customHeight="1">
-      <c r="A7" s="12" t="inlineStr">
+    <row r="13" ht="34" customHeight="1">
+      <c r="A13" s="24" t="inlineStr">
+        <is>
+          <t>Site holiday period (Mawlid)</t>
+        </is>
+      </c>
+      <c r="B13" s="17" t="n"/>
+      <c r="C13" s="17" t="n"/>
+      <c r="D13" s="17" t="n"/>
+      <c r="E13" s="17" t="n"/>
+      <c r="F13" s="17" t="n"/>
+      <c r="G13" s="18" t="n"/>
+    </row>
+    <row r="14" ht="34" customHeight="1">
+      <c r="A14" s="21" t="inlineStr">
+        <is>
+          <t>Feedback round &amp; final approved material box</t>
+        </is>
+      </c>
+      <c r="B14" s="17" t="n"/>
+      <c r="C14" s="17" t="n"/>
+      <c r="D14" s="17" t="n"/>
+      <c r="E14" s="18" t="n"/>
+      <c r="F14" s="23" t="inlineStr">
+        <is>
+          <t>Send project update to client-facing group</t>
+        </is>
+      </c>
+      <c r="G14" s="14" t="n"/>
+    </row>
+    <row r="15" ht="34" customHeight="1">
+      <c r="A15" s="20" t="inlineStr">
+        <is>
+          <t>⚑ Signed GFP SHD Version 02</t>
+        </is>
+      </c>
+      <c r="B15" s="17" t="n"/>
+      <c r="C15" s="17" t="n"/>
+      <c r="D15" s="17" t="n"/>
+      <c r="E15" s="18" t="n"/>
+      <c r="F15" s="19" t="inlineStr">
+        <is>
+          <t>Send project update to internal WDCO K5M group</t>
+        </is>
+      </c>
+      <c r="G15" s="14" t="n"/>
+    </row>
+    <row r="16" ht="34" customHeight="1">
+      <c r="A16" s="21" t="inlineStr">
+        <is>
+          <t>Fit-Out SHD V01 incorporating survey</t>
+        </is>
+      </c>
+      <c r="B16" s="17" t="n"/>
+      <c r="C16" s="17" t="n"/>
+      <c r="D16" s="17" t="n"/>
+      <c r="E16" s="18" t="n"/>
+      <c r="F16" s="14" t="n"/>
+      <c r="G16" s="14" t="n"/>
+    </row>
+    <row r="17" ht="34" customHeight="1">
+      <c r="A17" s="26" t="inlineStr">
+        <is>
+          <t>⚑ Signed FF&amp;E SHD V02 &amp; confirmed material package</t>
+        </is>
+      </c>
+      <c r="B17" s="17" t="n"/>
+      <c r="C17" s="18" t="n"/>
+      <c r="D17" s="16" t="inlineStr">
+        <is>
+          <t>FF&amp;E mock-up production, QC and packing</t>
+        </is>
+      </c>
+      <c r="E17" s="17" t="n"/>
+      <c r="F17" s="17" t="n"/>
+      <c r="G17" s="18" t="n"/>
+    </row>
+    <row r="18" ht="34" customHeight="1">
+      <c r="A18" s="14" t="n"/>
+      <c r="B18" s="16" t="inlineStr">
+        <is>
+          <t>Fit-out SHD V01 revisions</t>
+        </is>
+      </c>
+      <c r="C18" s="17" t="n"/>
+      <c r="D18" s="17" t="n"/>
+      <c r="E18" s="17" t="n"/>
+      <c r="F18" s="17" t="n"/>
+      <c r="G18" s="18" t="n"/>
+    </row>
+    <row r="19" ht="16" customHeight="1">
+      <c r="A19" s="13" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="B7" s="12" t="inlineStr">
+      <c r="B19" s="13" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="C7" s="12" t="inlineStr">
+      <c r="C19" s="13" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="D7" s="19" t="inlineStr">
-        <is>
-          <t>16
-⚑ [Client] Fit-out SHD V01 &amp; material-package approval (16–21 Sep)</t>
-        </is>
-      </c>
-      <c r="E7" s="12" t="inlineStr">
+      <c r="D19" s="13" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="E19" s="13" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="F7" s="12" t="inlineStr">
+      <c r="F19" s="13" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="G7" s="12" t="inlineStr">
+      <c r="G19" s="13" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="68" customHeight="1">
-      <c r="A8" s="12" t="inlineStr">
+    <row r="20" ht="34" customHeight="1">
+      <c r="A20" s="16" t="inlineStr">
+        <is>
+          <t>FF&amp;E mock-up production, QC and packing</t>
+        </is>
+      </c>
+      <c r="B20" s="17" t="n"/>
+      <c r="C20" s="17" t="n"/>
+      <c r="D20" s="17" t="n"/>
+      <c r="E20" s="17" t="n"/>
+      <c r="F20" s="17" t="n"/>
+      <c r="G20" s="18" t="n"/>
+    </row>
+    <row r="21" ht="34" customHeight="1">
+      <c r="A21" s="21" t="inlineStr">
+        <is>
+          <t>FF&amp;E production</t>
+        </is>
+      </c>
+      <c r="B21" s="17" t="n"/>
+      <c r="C21" s="17" t="n"/>
+      <c r="D21" s="17" t="n"/>
+      <c r="E21" s="17" t="n"/>
+      <c r="F21" s="17" t="n"/>
+      <c r="G21" s="18" t="n"/>
+    </row>
+    <row r="22" ht="34" customHeight="1">
+      <c r="A22" s="21" t="inlineStr">
+        <is>
+          <t>Fit-Out production</t>
+        </is>
+      </c>
+      <c r="B22" s="17" t="n"/>
+      <c r="C22" s="17" t="n"/>
+      <c r="D22" s="17" t="n"/>
+      <c r="E22" s="17" t="n"/>
+      <c r="F22" s="17" t="n"/>
+      <c r="G22" s="18" t="n"/>
+    </row>
+    <row r="23" ht="34" customHeight="1">
+      <c r="A23" s="16" t="inlineStr">
+        <is>
+          <t>Fit-out SHD V01 revisions</t>
+        </is>
+      </c>
+      <c r="B23" s="17" t="n"/>
+      <c r="C23" s="18" t="n"/>
+      <c r="D23" s="26" t="inlineStr">
+        <is>
+          <t>⚑ Fit-out SHD V01 &amp; material-package approval</t>
+        </is>
+      </c>
+      <c r="E23" s="17" t="n"/>
+      <c r="F23" s="17" t="n"/>
+      <c r="G23" s="18" t="n"/>
+    </row>
+    <row r="24" ht="34" customHeight="1">
+      <c r="A24" s="24" t="inlineStr">
+        <is>
+          <t>Site holiday period (Mawlid)</t>
+        </is>
+      </c>
+      <c r="B24" s="17" t="n"/>
+      <c r="C24" s="18" t="n"/>
+      <c r="D24" s="14" t="n"/>
+      <c r="E24" s="14" t="n"/>
+      <c r="F24" s="19" t="inlineStr">
+        <is>
+          <t>Send project update to internal WDCO K5M group</t>
+        </is>
+      </c>
+      <c r="G24" s="14" t="n"/>
+    </row>
+    <row r="25" ht="34" customHeight="1">
+      <c r="A25" s="14" t="n"/>
+      <c r="B25" s="14" t="n"/>
+      <c r="C25" s="14" t="n"/>
+      <c r="D25" s="14" t="n"/>
+      <c r="E25" s="14" t="n"/>
+      <c r="F25" s="14" t="n"/>
+      <c r="G25" s="14" t="n"/>
+    </row>
+    <row r="26" ht="16" customHeight="1">
+      <c r="A26" s="13" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="B8" s="12" t="inlineStr">
+      <c r="B26" s="13" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="C8" s="14" t="inlineStr">
-        <is>
-          <t>22
-[Client] Fit-out production, QC and packing (22–16 Oct)</t>
-        </is>
-      </c>
-      <c r="D8" s="12" t="inlineStr">
+      <c r="C26" s="13" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D26" s="13" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="E8" s="12" t="inlineStr">
+      <c r="E26" s="13" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="F8" s="12" t="inlineStr">
+      <c r="F26" s="13" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="G8" s="12" t="inlineStr">
+      <c r="G26" s="13" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="60" customHeight="1">
-      <c r="A9" s="12" t="inlineStr">
+    <row r="27" ht="34" customHeight="1">
+      <c r="A27" s="16" t="inlineStr">
+        <is>
+          <t>FF&amp;E mock-up production, QC and packing</t>
+        </is>
+      </c>
+      <c r="B27" s="17" t="n"/>
+      <c r="C27" s="17" t="n"/>
+      <c r="D27" s="17" t="n"/>
+      <c r="E27" s="17" t="n"/>
+      <c r="F27" s="17" t="n"/>
+      <c r="G27" s="18" t="n"/>
+    </row>
+    <row r="28" ht="34" customHeight="1">
+      <c r="A28" s="21" t="inlineStr">
+        <is>
+          <t>FF&amp;E production</t>
+        </is>
+      </c>
+      <c r="B28" s="17" t="n"/>
+      <c r="C28" s="17" t="n"/>
+      <c r="D28" s="17" t="n"/>
+      <c r="E28" s="17" t="n"/>
+      <c r="F28" s="17" t="n"/>
+      <c r="G28" s="18" t="n"/>
+    </row>
+    <row r="29" ht="34" customHeight="1">
+      <c r="A29" s="21" t="inlineStr">
+        <is>
+          <t>Fit-Out production</t>
+        </is>
+      </c>
+      <c r="B29" s="17" t="n"/>
+      <c r="C29" s="17" t="n"/>
+      <c r="D29" s="17" t="n"/>
+      <c r="E29" s="18" t="n"/>
+      <c r="F29" s="23" t="inlineStr">
+        <is>
+          <t>Send project update to client-facing group</t>
+        </is>
+      </c>
+      <c r="G29" s="14" t="n"/>
+    </row>
+    <row r="30" ht="34" customHeight="1">
+      <c r="A30" s="26" t="inlineStr">
+        <is>
+          <t>⚑ Fit-out SHD V01 &amp; material-package approval</t>
+        </is>
+      </c>
+      <c r="B30" s="18" t="n"/>
+      <c r="C30" s="16" t="inlineStr">
+        <is>
+          <t>Fit-out production, QC and packing</t>
+        </is>
+      </c>
+      <c r="D30" s="17" t="n"/>
+      <c r="E30" s="17" t="n"/>
+      <c r="F30" s="17" t="n"/>
+      <c r="G30" s="18" t="n"/>
+    </row>
+    <row r="31" ht="34" customHeight="1">
+      <c r="A31" s="14" t="n"/>
+      <c r="B31" s="14" t="n"/>
+      <c r="C31" s="14" t="n"/>
+      <c r="D31" s="14" t="n"/>
+      <c r="E31" s="14" t="n"/>
+      <c r="F31" s="19" t="inlineStr">
+        <is>
+          <t>Send project update to internal WDCO K5M group</t>
+        </is>
+      </c>
+      <c r="G31" s="14" t="n"/>
+    </row>
+    <row r="32" ht="34" customHeight="1">
+      <c r="A32" s="14" t="n"/>
+      <c r="B32" s="14" t="n"/>
+      <c r="C32" s="14" t="n"/>
+      <c r="D32" s="14" t="n"/>
+      <c r="E32" s="14" t="n"/>
+      <c r="F32" s="14" t="n"/>
+      <c r="G32" s="14" t="n"/>
+    </row>
+    <row r="33" ht="16" customHeight="1">
+      <c r="A33" s="13" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="B9" s="12" t="inlineStr">
+      <c r="B33" s="13" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="C9" s="12" t="inlineStr">
+      <c r="C33" s="13" t="inlineStr">
         <is>
           <t>29</t>
         </is>
       </c>
-      <c r="D9" s="12" t="inlineStr">
+      <c r="D33" s="13" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="E9" s="11" t="n"/>
-      <c r="F9" s="11" t="n"/>
-      <c r="G9" s="11" t="n"/>
+      <c r="E33" s="12" t="n"/>
+      <c r="F33" s="12" t="n"/>
+      <c r="G33" s="12" t="n"/>
+    </row>
+    <row r="34" ht="34" customHeight="1">
+      <c r="A34" s="16" t="inlineStr">
+        <is>
+          <t>FF&amp;E mock-up production, QC and packing</t>
+        </is>
+      </c>
+      <c r="B34" s="17" t="n"/>
+      <c r="C34" s="17" t="n"/>
+      <c r="D34" s="17" t="n"/>
+      <c r="E34" s="17" t="n"/>
+      <c r="F34" s="17" t="n"/>
+      <c r="G34" s="18" t="n"/>
+    </row>
+    <row r="35" ht="34" customHeight="1">
+      <c r="A35" s="16" t="inlineStr">
+        <is>
+          <t>Fit-out production, QC and packing</t>
+        </is>
+      </c>
+      <c r="B35" s="17" t="n"/>
+      <c r="C35" s="17" t="n"/>
+      <c r="D35" s="17" t="n"/>
+      <c r="E35" s="17" t="n"/>
+      <c r="F35" s="17" t="n"/>
+      <c r="G35" s="18" t="n"/>
+    </row>
+    <row r="36" ht="34" customHeight="1">
+      <c r="A36" s="21" t="inlineStr">
+        <is>
+          <t>FF&amp;E production</t>
+        </is>
+      </c>
+      <c r="B36" s="17" t="n"/>
+      <c r="C36" s="17" t="n"/>
+      <c r="D36" s="17" t="n"/>
+      <c r="E36" s="17" t="n"/>
+      <c r="F36" s="17" t="n"/>
+      <c r="G36" s="18" t="n"/>
+    </row>
+    <row r="37" ht="34" customHeight="1">
+      <c r="A37" s="14" t="n"/>
+      <c r="B37" s="14" t="n"/>
+      <c r="C37" s="14" t="n"/>
+      <c r="D37" s="14" t="n"/>
+      <c r="E37" s="14" t="n"/>
+      <c r="F37" s="19" t="inlineStr">
+        <is>
+          <t>Send project update to internal WDCO K5M group</t>
+        </is>
+      </c>
+      <c r="G37" s="14" t="n"/>
+    </row>
+    <row r="38" ht="34" customHeight="1">
+      <c r="A38" s="14" t="n"/>
+      <c r="B38" s="14" t="n"/>
+      <c r="C38" s="14" t="n"/>
+      <c r="D38" s="14" t="n"/>
+      <c r="E38" s="14" t="n"/>
+      <c r="F38" s="14" t="n"/>
+      <c r="G38" s="14" t="n"/>
+    </row>
+    <row r="39" ht="34" customHeight="1">
+      <c r="A39" s="14" t="n"/>
+      <c r="B39" s="14" t="n"/>
+      <c r="C39" s="14" t="n"/>
+      <c r="D39" s="14" t="n"/>
+      <c r="E39" s="14" t="n"/>
+      <c r="F39" s="14" t="n"/>
+      <c r="G39" s="14" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="5">
-    <mergeCell ref="A2:B2"/>
+  <mergeCells count="34">
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="A30:B30"/>
+    <mergeCell ref="C30:G30"/>
+    <mergeCell ref="A8:G8"/>
+    <mergeCell ref="A15:E15"/>
+    <mergeCell ref="A22:G22"/>
+    <mergeCell ref="A35:G35"/>
+    <mergeCell ref="A20:G20"/>
+    <mergeCell ref="E9:G9"/>
+    <mergeCell ref="A28:G28"/>
+    <mergeCell ref="A13:G13"/>
+    <mergeCell ref="D23:G23"/>
+    <mergeCell ref="C11:E11"/>
+    <mergeCell ref="A16:E16"/>
+    <mergeCell ref="A23:C23"/>
+    <mergeCell ref="A34:G34"/>
+    <mergeCell ref="A17:C17"/>
+    <mergeCell ref="B9:D9"/>
+    <mergeCell ref="A36:G36"/>
     <mergeCell ref="A1:G1"/>
-    <mergeCell ref="C2:D2"/>
-    <mergeCell ref="G2:H2"/>
-    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="A6:G6"/>
+    <mergeCell ref="B2"/>
+    <mergeCell ref="D2"/>
+    <mergeCell ref="A7:G7"/>
+    <mergeCell ref="A14:E14"/>
+    <mergeCell ref="C10:F10"/>
+    <mergeCell ref="A24:C24"/>
+    <mergeCell ref="A29:E29"/>
+    <mergeCell ref="D17:G17"/>
+    <mergeCell ref="A27:G27"/>
+    <mergeCell ref="A21:G21"/>
+    <mergeCell ref="A2"/>
+    <mergeCell ref="C2"/>
+    <mergeCell ref="B18:G18"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2874,263 +4573,631 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:G39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="26" customWidth="1" min="5" max="5"/>
+    <col width="26" customWidth="1" min="6" max="6"/>
+    <col width="26" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="5" t="inlineStr">
+      <c r="A1" s="10" t="inlineStr">
         <is>
           <t>K5M — OCTOBER 2026</t>
         </is>
       </c>
     </row>
     <row r="2" ht="16" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">  Client</t>
         </is>
       </c>
-      <c r="C2" s="7" t="inlineStr">
+      <c r="B2" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">  Supplier</t>
         </is>
       </c>
-      <c r="E2" s="8" t="inlineStr">
+      <c r="C2" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">  WDCO Internal PM</t>
         </is>
       </c>
-      <c r="G2" s="9" t="inlineStr">
+      <c r="D2" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">  Deadline (red border)</t>
         </is>
       </c>
     </row>
     <row r="4" ht="18" customHeight="1">
-      <c r="A4" s="10" t="inlineStr">
+      <c r="A4" s="11" t="inlineStr">
         <is>
           <t>Sunday</t>
         </is>
       </c>
-      <c r="B4" s="10" t="inlineStr">
+      <c r="B4" s="11" t="inlineStr">
         <is>
           <t>Monday</t>
         </is>
       </c>
-      <c r="C4" s="10" t="inlineStr">
+      <c r="C4" s="11" t="inlineStr">
         <is>
           <t>Tuesday</t>
         </is>
       </c>
-      <c r="D4" s="10" t="inlineStr">
+      <c r="D4" s="11" t="inlineStr">
         <is>
           <t>Wednesday</t>
         </is>
       </c>
-      <c r="E4" s="10" t="inlineStr">
+      <c r="E4" s="11" t="inlineStr">
         <is>
           <t>Thursday</t>
         </is>
       </c>
-      <c r="F4" s="10" t="inlineStr">
+      <c r="F4" s="11" t="inlineStr">
         <is>
           <t>Friday</t>
         </is>
       </c>
-      <c r="G4" s="10" t="inlineStr">
+      <c r="G4" s="11" t="inlineStr">
         <is>
           <t>Saturday</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="60" customHeight="1">
-      <c r="A5" s="11" t="n"/>
-      <c r="B5" s="11" t="n"/>
-      <c r="C5" s="11" t="n"/>
-      <c r="D5" s="11" t="n"/>
-      <c r="E5" s="12" t="inlineStr">
+    <row r="5" ht="16" customHeight="1">
+      <c r="A5" s="12" t="n"/>
+      <c r="B5" s="12" t="n"/>
+      <c r="C5" s="12" t="n"/>
+      <c r="D5" s="12" t="n"/>
+      <c r="E5" s="13" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="F5" s="12" t="inlineStr">
+      <c r="F5" s="13" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="G5" s="12" t="inlineStr">
+      <c r="G5" s="13" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="68" customHeight="1">
-      <c r="A6" s="12" t="inlineStr">
+    <row r="6" ht="34" customHeight="1">
+      <c r="A6" s="16" t="inlineStr">
+        <is>
+          <t>FF&amp;E mock-up production, QC and packing</t>
+        </is>
+      </c>
+      <c r="B6" s="17" t="n"/>
+      <c r="C6" s="17" t="n"/>
+      <c r="D6" s="17" t="n"/>
+      <c r="E6" s="17" t="n"/>
+      <c r="F6" s="17" t="n"/>
+      <c r="G6" s="18" t="n"/>
+    </row>
+    <row r="7" ht="34" customHeight="1">
+      <c r="A7" s="16" t="inlineStr">
+        <is>
+          <t>Fit-out production, QC and packing</t>
+        </is>
+      </c>
+      <c r="B7" s="17" t="n"/>
+      <c r="C7" s="17" t="n"/>
+      <c r="D7" s="17" t="n"/>
+      <c r="E7" s="17" t="n"/>
+      <c r="F7" s="17" t="n"/>
+      <c r="G7" s="18" t="n"/>
+    </row>
+    <row r="8" ht="34" customHeight="1">
+      <c r="A8" s="21" t="inlineStr">
+        <is>
+          <t>FF&amp;E production</t>
+        </is>
+      </c>
+      <c r="B8" s="17" t="n"/>
+      <c r="C8" s="17" t="n"/>
+      <c r="D8" s="17" t="n"/>
+      <c r="E8" s="17" t="n"/>
+      <c r="F8" s="17" t="n"/>
+      <c r="G8" s="18" t="n"/>
+    </row>
+    <row r="9" ht="34" customHeight="1">
+      <c r="A9" s="14" t="n"/>
+      <c r="B9" s="14" t="n"/>
+      <c r="C9" s="14" t="n"/>
+      <c r="D9" s="14" t="n"/>
+      <c r="E9" s="14" t="n"/>
+      <c r="F9" s="19" t="inlineStr">
+        <is>
+          <t>Send project update to internal WDCO K5M group</t>
+        </is>
+      </c>
+      <c r="G9" s="14" t="n"/>
+    </row>
+    <row r="10" ht="34" customHeight="1">
+      <c r="A10" s="14" t="n"/>
+      <c r="B10" s="14" t="n"/>
+      <c r="C10" s="14" t="n"/>
+      <c r="D10" s="14" t="n"/>
+      <c r="E10" s="14" t="n"/>
+      <c r="F10" s="14" t="n"/>
+      <c r="G10" s="14" t="n"/>
+    </row>
+    <row r="11" ht="34" customHeight="1">
+      <c r="A11" s="14" t="n"/>
+      <c r="B11" s="14" t="n"/>
+      <c r="C11" s="14" t="n"/>
+      <c r="D11" s="14" t="n"/>
+      <c r="E11" s="14" t="n"/>
+      <c r="F11" s="14" t="n"/>
+      <c r="G11" s="14" t="n"/>
+    </row>
+    <row r="12" ht="16" customHeight="1">
+      <c r="A12" s="13" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B6" s="12" t="inlineStr">
+      <c r="B12" s="13" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="C6" s="12" t="inlineStr">
+      <c r="C12" s="13" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D6" s="12" t="inlineStr">
+      <c r="D12" s="13" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="E6" s="12" t="inlineStr">
+      <c r="E12" s="13" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="F6" s="12" t="inlineStr">
+      <c r="F12" s="13" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="G6" s="17" t="inlineStr">
-        <is>
-          <t>10
-[Supplier] Packing, dispatch, sea freight, customs, delivery (10–28 Nov)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="60" customHeight="1">
-      <c r="A7" s="12" t="inlineStr">
+      <c r="G12" s="13" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="34" customHeight="1">
+      <c r="A13" s="16" t="inlineStr">
+        <is>
+          <t>FF&amp;E mock-up production, QC and packing</t>
+        </is>
+      </c>
+      <c r="B13" s="17" t="n"/>
+      <c r="C13" s="17" t="n"/>
+      <c r="D13" s="17" t="n"/>
+      <c r="E13" s="17" t="n"/>
+      <c r="F13" s="17" t="n"/>
+      <c r="G13" s="18" t="n"/>
+    </row>
+    <row r="14" ht="34" customHeight="1">
+      <c r="A14" s="16" t="inlineStr">
+        <is>
+          <t>Fit-out production, QC and packing</t>
+        </is>
+      </c>
+      <c r="B14" s="17" t="n"/>
+      <c r="C14" s="17" t="n"/>
+      <c r="D14" s="17" t="n"/>
+      <c r="E14" s="17" t="n"/>
+      <c r="F14" s="17" t="n"/>
+      <c r="G14" s="18" t="n"/>
+    </row>
+    <row r="15" ht="34" customHeight="1">
+      <c r="A15" s="21" t="inlineStr">
+        <is>
+          <t>FF&amp;E production</t>
+        </is>
+      </c>
+      <c r="B15" s="17" t="n"/>
+      <c r="C15" s="17" t="n"/>
+      <c r="D15" s="17" t="n"/>
+      <c r="E15" s="17" t="n"/>
+      <c r="F15" s="18" t="n"/>
+      <c r="G15" s="27" t="inlineStr">
+        <is>
+          <t>Packing, dispatch, sea freight, customs, delivery</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="34" customHeight="1">
+      <c r="A16" s="14" t="n"/>
+      <c r="B16" s="14" t="n"/>
+      <c r="C16" s="14" t="n"/>
+      <c r="D16" s="14" t="n"/>
+      <c r="E16" s="14" t="n"/>
+      <c r="F16" s="23" t="inlineStr">
+        <is>
+          <t>Send project update to client-facing group</t>
+        </is>
+      </c>
+      <c r="G16" s="14" t="n"/>
+    </row>
+    <row r="17" ht="34" customHeight="1">
+      <c r="A17" s="14" t="n"/>
+      <c r="B17" s="14" t="n"/>
+      <c r="C17" s="14" t="n"/>
+      <c r="D17" s="14" t="n"/>
+      <c r="E17" s="14" t="n"/>
+      <c r="F17" s="19" t="inlineStr">
+        <is>
+          <t>Send project update to internal WDCO K5M group</t>
+        </is>
+      </c>
+      <c r="G17" s="14" t="n"/>
+    </row>
+    <row r="18" ht="34" customHeight="1">
+      <c r="A18" s="14" t="n"/>
+      <c r="B18" s="14" t="n"/>
+      <c r="C18" s="14" t="n"/>
+      <c r="D18" s="14" t="n"/>
+      <c r="E18" s="14" t="n"/>
+      <c r="F18" s="14" t="n"/>
+      <c r="G18" s="14" t="n"/>
+    </row>
+    <row r="19" ht="16" customHeight="1">
+      <c r="A19" s="13" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="B7" s="12" t="inlineStr">
+      <c r="B19" s="13" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="C7" s="12" t="inlineStr">
+      <c r="C19" s="13" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="D7" s="12" t="inlineStr">
+      <c r="D19" s="13" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="E7" s="12" t="inlineStr">
+      <c r="E19" s="13" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="F7" s="12" t="inlineStr">
+      <c r="F19" s="13" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="G7" s="12" t="inlineStr">
+      <c r="G19" s="13" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="60" customHeight="1">
-      <c r="A8" s="12" t="inlineStr">
+    <row r="20" ht="34" customHeight="1">
+      <c r="A20" s="16" t="inlineStr">
+        <is>
+          <t>FF&amp;E mock-up production, QC and packing</t>
+        </is>
+      </c>
+      <c r="B20" s="17" t="n"/>
+      <c r="C20" s="17" t="n"/>
+      <c r="D20" s="17" t="n"/>
+      <c r="E20" s="17" t="n"/>
+      <c r="F20" s="17" t="n"/>
+      <c r="G20" s="18" t="n"/>
+    </row>
+    <row r="21" ht="34" customHeight="1">
+      <c r="A21" s="21" t="inlineStr">
+        <is>
+          <t>Packing, dispatch, sea freight, customs, delivery</t>
+        </is>
+      </c>
+      <c r="B21" s="17" t="n"/>
+      <c r="C21" s="17" t="n"/>
+      <c r="D21" s="17" t="n"/>
+      <c r="E21" s="17" t="n"/>
+      <c r="F21" s="17" t="n"/>
+      <c r="G21" s="18" t="n"/>
+    </row>
+    <row r="22" ht="34" customHeight="1">
+      <c r="A22" s="16" t="inlineStr">
+        <is>
+          <t>Fit-out production, QC and packing</t>
+        </is>
+      </c>
+      <c r="B22" s="17" t="n"/>
+      <c r="C22" s="17" t="n"/>
+      <c r="D22" s="17" t="n"/>
+      <c r="E22" s="17" t="n"/>
+      <c r="F22" s="18" t="n"/>
+      <c r="G22" s="14" t="n"/>
+    </row>
+    <row r="23" ht="34" customHeight="1">
+      <c r="A23" s="14" t="n"/>
+      <c r="B23" s="14" t="n"/>
+      <c r="C23" s="14" t="n"/>
+      <c r="D23" s="14" t="n"/>
+      <c r="E23" s="14" t="n"/>
+      <c r="F23" s="19" t="inlineStr">
+        <is>
+          <t>Send project update to internal WDCO K5M group</t>
+        </is>
+      </c>
+      <c r="G23" s="14" t="n"/>
+    </row>
+    <row r="24" ht="34" customHeight="1">
+      <c r="A24" s="14" t="n"/>
+      <c r="B24" s="14" t="n"/>
+      <c r="C24" s="14" t="n"/>
+      <c r="D24" s="14" t="n"/>
+      <c r="E24" s="14" t="n"/>
+      <c r="F24" s="14" t="n"/>
+      <c r="G24" s="14" t="n"/>
+    </row>
+    <row r="25" ht="34" customHeight="1">
+      <c r="A25" s="14" t="n"/>
+      <c r="B25" s="14" t="n"/>
+      <c r="C25" s="14" t="n"/>
+      <c r="D25" s="14" t="n"/>
+      <c r="E25" s="14" t="n"/>
+      <c r="F25" s="14" t="n"/>
+      <c r="G25" s="14" t="n"/>
+    </row>
+    <row r="26" ht="16" customHeight="1">
+      <c r="A26" s="13" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="B8" s="12" t="inlineStr">
+      <c r="B26" s="13" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="C8" s="12" t="inlineStr">
+      <c r="C26" s="13" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="D8" s="12" t="inlineStr">
+      <c r="D26" s="13" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="E8" s="12" t="inlineStr">
+      <c r="E26" s="13" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="F8" s="12" t="inlineStr">
+      <c r="F26" s="13" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="G8" s="12" t="inlineStr">
+      <c r="G26" s="13" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="102" customHeight="1">
-      <c r="A9" s="13" t="inlineStr">
-        <is>
-          <t>25
-⚑ [Client] Combined dispatch on next available sailing
-[Client] Sea freight to Casablanca (25–3 Dec)</t>
-        </is>
-      </c>
-      <c r="B9" s="12" t="inlineStr">
+    <row r="27" ht="34" customHeight="1">
+      <c r="A27" s="21" t="inlineStr">
+        <is>
+          <t>Packing, dispatch, sea freight, customs, delivery</t>
+        </is>
+      </c>
+      <c r="B27" s="17" t="n"/>
+      <c r="C27" s="17" t="n"/>
+      <c r="D27" s="17" t="n"/>
+      <c r="E27" s="17" t="n"/>
+      <c r="F27" s="17" t="n"/>
+      <c r="G27" s="18" t="n"/>
+    </row>
+    <row r="28" ht="34" customHeight="1">
+      <c r="A28" s="16" t="inlineStr">
+        <is>
+          <t>FF&amp;E mock-up production, QC and packing</t>
+        </is>
+      </c>
+      <c r="B28" s="17" t="n"/>
+      <c r="C28" s="17" t="n"/>
+      <c r="D28" s="17" t="n"/>
+      <c r="E28" s="17" t="n"/>
+      <c r="F28" s="18" t="n"/>
+      <c r="G28" s="14" t="n"/>
+    </row>
+    <row r="29" ht="34" customHeight="1">
+      <c r="A29" s="14" t="n"/>
+      <c r="B29" s="14" t="n"/>
+      <c r="C29" s="14" t="n"/>
+      <c r="D29" s="14" t="n"/>
+      <c r="E29" s="14" t="n"/>
+      <c r="F29" s="23" t="inlineStr">
+        <is>
+          <t>Send project update to client-facing group</t>
+        </is>
+      </c>
+      <c r="G29" s="14" t="n"/>
+    </row>
+    <row r="30" ht="34" customHeight="1">
+      <c r="A30" s="14" t="n"/>
+      <c r="B30" s="14" t="n"/>
+      <c r="C30" s="14" t="n"/>
+      <c r="D30" s="14" t="n"/>
+      <c r="E30" s="14" t="n"/>
+      <c r="F30" s="19" t="inlineStr">
+        <is>
+          <t>Send project update to internal WDCO K5M group</t>
+        </is>
+      </c>
+      <c r="G30" s="14" t="n"/>
+    </row>
+    <row r="31" ht="34" customHeight="1">
+      <c r="A31" s="14" t="n"/>
+      <c r="B31" s="14" t="n"/>
+      <c r="C31" s="14" t="n"/>
+      <c r="D31" s="14" t="n"/>
+      <c r="E31" s="14" t="n"/>
+      <c r="F31" s="14" t="n"/>
+      <c r="G31" s="14" t="n"/>
+    </row>
+    <row r="32" ht="34" customHeight="1">
+      <c r="A32" s="14" t="n"/>
+      <c r="B32" s="14" t="n"/>
+      <c r="C32" s="14" t="n"/>
+      <c r="D32" s="14" t="n"/>
+      <c r="E32" s="14" t="n"/>
+      <c r="F32" s="14" t="n"/>
+      <c r="G32" s="14" t="n"/>
+    </row>
+    <row r="33" ht="16" customHeight="1">
+      <c r="A33" s="13" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B33" s="13" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="C9" s="12" t="inlineStr">
+      <c r="C33" s="13" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="D9" s="12" t="inlineStr">
+      <c r="D33" s="13" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="E9" s="12" t="inlineStr">
+      <c r="E33" s="13" t="inlineStr">
         <is>
           <t>29</t>
         </is>
       </c>
-      <c r="F9" s="12" t="inlineStr">
+      <c r="F33" s="13" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="G9" s="12" t="inlineStr">
+      <c r="G33" s="13" t="inlineStr">
         <is>
           <t>31</t>
         </is>
       </c>
     </row>
+    <row r="34" ht="34" customHeight="1">
+      <c r="A34" s="16" t="inlineStr">
+        <is>
+          <t>Sea freight to Casablanca</t>
+        </is>
+      </c>
+      <c r="B34" s="17" t="n"/>
+      <c r="C34" s="17" t="n"/>
+      <c r="D34" s="17" t="n"/>
+      <c r="E34" s="17" t="n"/>
+      <c r="F34" s="17" t="n"/>
+      <c r="G34" s="18" t="n"/>
+    </row>
+    <row r="35" ht="34" customHeight="1">
+      <c r="A35" s="21" t="inlineStr">
+        <is>
+          <t>Packing, dispatch, sea freight, customs, delivery</t>
+        </is>
+      </c>
+      <c r="B35" s="17" t="n"/>
+      <c r="C35" s="17" t="n"/>
+      <c r="D35" s="17" t="n"/>
+      <c r="E35" s="17" t="n"/>
+      <c r="F35" s="17" t="n"/>
+      <c r="G35" s="18" t="n"/>
+    </row>
+    <row r="36" ht="34" customHeight="1">
+      <c r="A36" s="15" t="inlineStr">
+        <is>
+          <t>⚑ Combined dispatch on next available sailing</t>
+        </is>
+      </c>
+      <c r="B36" s="14" t="n"/>
+      <c r="C36" s="14" t="n"/>
+      <c r="D36" s="14" t="n"/>
+      <c r="E36" s="14" t="n"/>
+      <c r="F36" s="19" t="inlineStr">
+        <is>
+          <t>Send project update to internal WDCO K5M group</t>
+        </is>
+      </c>
+      <c r="G36" s="14" t="n"/>
+    </row>
+    <row r="37" ht="34" customHeight="1">
+      <c r="A37" s="14" t="n"/>
+      <c r="B37" s="14" t="n"/>
+      <c r="C37" s="14" t="n"/>
+      <c r="D37" s="14" t="n"/>
+      <c r="E37" s="14" t="n"/>
+      <c r="F37" s="14" t="n"/>
+      <c r="G37" s="14" t="n"/>
+    </row>
+    <row r="38" ht="34" customHeight="1">
+      <c r="A38" s="14" t="n"/>
+      <c r="B38" s="14" t="n"/>
+      <c r="C38" s="14" t="n"/>
+      <c r="D38" s="14" t="n"/>
+      <c r="E38" s="14" t="n"/>
+      <c r="F38" s="14" t="n"/>
+      <c r="G38" s="14" t="n"/>
+    </row>
+    <row r="39" ht="34" customHeight="1">
+      <c r="A39" s="14" t="n"/>
+      <c r="B39" s="14" t="n"/>
+      <c r="C39" s="14" t="n"/>
+      <c r="D39" s="14" t="n"/>
+      <c r="E39" s="14" t="n"/>
+      <c r="F39" s="14" t="n"/>
+      <c r="G39" s="14" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="5">
-    <mergeCell ref="A2:B2"/>
+  <mergeCells count="18">
+    <mergeCell ref="A13:G13"/>
+    <mergeCell ref="A14:G14"/>
     <mergeCell ref="A1:G1"/>
-    <mergeCell ref="C2:D2"/>
-    <mergeCell ref="G2:H2"/>
-    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="A28:F28"/>
+    <mergeCell ref="A27:G27"/>
+    <mergeCell ref="A8:G8"/>
+    <mergeCell ref="A6:G6"/>
+    <mergeCell ref="A21:G21"/>
+    <mergeCell ref="A34:G34"/>
+    <mergeCell ref="A35:G35"/>
+    <mergeCell ref="A20:G20"/>
+    <mergeCell ref="B2"/>
+    <mergeCell ref="A2"/>
+    <mergeCell ref="A22:F22"/>
+    <mergeCell ref="D2"/>
+    <mergeCell ref="C2"/>
+    <mergeCell ref="A7:G7"/>
+    <mergeCell ref="A15:F15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3142,258 +5209,622 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:G39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="26" customWidth="1" min="5" max="5"/>
+    <col width="26" customWidth="1" min="6" max="6"/>
+    <col width="26" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="5" t="inlineStr">
+      <c r="A1" s="10" t="inlineStr">
         <is>
           <t>K5M — NOVEMBER 2026</t>
         </is>
       </c>
     </row>
     <row r="2" ht="16" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">  Client</t>
         </is>
       </c>
-      <c r="C2" s="7" t="inlineStr">
+      <c r="B2" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">  Supplier</t>
         </is>
       </c>
-      <c r="E2" s="8" t="inlineStr">
+      <c r="C2" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">  WDCO Internal PM</t>
         </is>
       </c>
-      <c r="G2" s="9" t="inlineStr">
+      <c r="D2" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">  Deadline (red border)</t>
         </is>
       </c>
     </row>
     <row r="4" ht="18" customHeight="1">
-      <c r="A4" s="10" t="inlineStr">
+      <c r="A4" s="11" t="inlineStr">
         <is>
           <t>Sunday</t>
         </is>
       </c>
-      <c r="B4" s="10" t="inlineStr">
+      <c r="B4" s="11" t="inlineStr">
         <is>
           <t>Monday</t>
         </is>
       </c>
-      <c r="C4" s="10" t="inlineStr">
+      <c r="C4" s="11" t="inlineStr">
         <is>
           <t>Tuesday</t>
         </is>
       </c>
-      <c r="D4" s="10" t="inlineStr">
+      <c r="D4" s="11" t="inlineStr">
         <is>
           <t>Wednesday</t>
         </is>
       </c>
-      <c r="E4" s="10" t="inlineStr">
+      <c r="E4" s="11" t="inlineStr">
         <is>
           <t>Thursday</t>
         </is>
       </c>
-      <c r="F4" s="10" t="inlineStr">
+      <c r="F4" s="11" t="inlineStr">
         <is>
           <t>Friday</t>
         </is>
       </c>
-      <c r="G4" s="10" t="inlineStr">
+      <c r="G4" s="11" t="inlineStr">
         <is>
           <t>Saturday</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="60" customHeight="1">
-      <c r="A5" s="12" t="inlineStr">
+    <row r="5" ht="16" customHeight="1">
+      <c r="A5" s="13" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B5" s="12" t="inlineStr">
+      <c r="B5" s="13" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="C5" s="12" t="inlineStr">
+      <c r="C5" s="13" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D5" s="12" t="inlineStr">
+      <c r="D5" s="13" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E5" s="12" t="inlineStr">
+      <c r="E5" s="13" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="F5" s="12" t="inlineStr">
+      <c r="F5" s="13" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="G5" s="12" t="inlineStr">
+      <c r="G5" s="13" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="60" customHeight="1">
-      <c r="A6" s="12" t="inlineStr">
+    <row r="6" ht="34" customHeight="1">
+      <c r="A6" s="16" t="inlineStr">
+        <is>
+          <t>Sea freight to Casablanca</t>
+        </is>
+      </c>
+      <c r="B6" s="17" t="n"/>
+      <c r="C6" s="17" t="n"/>
+      <c r="D6" s="17" t="n"/>
+      <c r="E6" s="17" t="n"/>
+      <c r="F6" s="17" t="n"/>
+      <c r="G6" s="18" t="n"/>
+    </row>
+    <row r="7" ht="34" customHeight="1">
+      <c r="A7" s="21" t="inlineStr">
+        <is>
+          <t>Packing, dispatch, sea freight, customs, delivery</t>
+        </is>
+      </c>
+      <c r="B7" s="17" t="n"/>
+      <c r="C7" s="17" t="n"/>
+      <c r="D7" s="17" t="n"/>
+      <c r="E7" s="17" t="n"/>
+      <c r="F7" s="17" t="n"/>
+      <c r="G7" s="18" t="n"/>
+    </row>
+    <row r="8" ht="34" customHeight="1">
+      <c r="A8" s="14" t="n"/>
+      <c r="B8" s="14" t="n"/>
+      <c r="C8" s="14" t="n"/>
+      <c r="D8" s="14" t="n"/>
+      <c r="E8" s="14" t="n"/>
+      <c r="F8" s="23" t="inlineStr">
+        <is>
+          <t>Send project update to client-facing group</t>
+        </is>
+      </c>
+      <c r="G8" s="14" t="n"/>
+    </row>
+    <row r="9" ht="34" customHeight="1">
+      <c r="A9" s="14" t="n"/>
+      <c r="B9" s="14" t="n"/>
+      <c r="C9" s="14" t="n"/>
+      <c r="D9" s="14" t="n"/>
+      <c r="E9" s="14" t="n"/>
+      <c r="F9" s="19" t="inlineStr">
+        <is>
+          <t>Send project update to internal WDCO K5M group</t>
+        </is>
+      </c>
+      <c r="G9" s="14" t="n"/>
+    </row>
+    <row r="10" ht="34" customHeight="1">
+      <c r="A10" s="14" t="n"/>
+      <c r="B10" s="14" t="n"/>
+      <c r="C10" s="14" t="n"/>
+      <c r="D10" s="14" t="n"/>
+      <c r="E10" s="14" t="n"/>
+      <c r="F10" s="14" t="n"/>
+      <c r="G10" s="14" t="n"/>
+    </row>
+    <row r="11" ht="34" customHeight="1">
+      <c r="A11" s="14" t="n"/>
+      <c r="B11" s="14" t="n"/>
+      <c r="C11" s="14" t="n"/>
+      <c r="D11" s="14" t="n"/>
+      <c r="E11" s="14" t="n"/>
+      <c r="F11" s="14" t="n"/>
+      <c r="G11" s="14" t="n"/>
+    </row>
+    <row r="12" ht="16" customHeight="1">
+      <c r="A12" s="13" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="B6" s="12" t="inlineStr">
+      <c r="B12" s="13" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="C6" s="12" t="inlineStr">
+      <c r="C12" s="13" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D6" s="12" t="inlineStr">
+      <c r="D12" s="13" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="E6" s="12" t="inlineStr">
+      <c r="E12" s="13" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="F6" s="12" t="inlineStr">
+      <c r="F12" s="13" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="G6" s="12" t="inlineStr">
+      <c r="G12" s="13" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="68" customHeight="1">
-      <c r="A7" s="20" t="inlineStr">
-        <is>
-          <t>15
-⚑ [WDCO Internal PM] Internal working deadline</t>
-        </is>
-      </c>
-      <c r="B7" s="12" t="inlineStr">
+    <row r="13" ht="34" customHeight="1">
+      <c r="A13" s="16" t="inlineStr">
+        <is>
+          <t>Sea freight to Casablanca</t>
+        </is>
+      </c>
+      <c r="B13" s="17" t="n"/>
+      <c r="C13" s="17" t="n"/>
+      <c r="D13" s="17" t="n"/>
+      <c r="E13" s="17" t="n"/>
+      <c r="F13" s="17" t="n"/>
+      <c r="G13" s="18" t="n"/>
+    </row>
+    <row r="14" ht="34" customHeight="1">
+      <c r="A14" s="21" t="inlineStr">
+        <is>
+          <t>Packing, dispatch, sea freight, customs, delivery</t>
+        </is>
+      </c>
+      <c r="B14" s="17" t="n"/>
+      <c r="C14" s="17" t="n"/>
+      <c r="D14" s="17" t="n"/>
+      <c r="E14" s="17" t="n"/>
+      <c r="F14" s="17" t="n"/>
+      <c r="G14" s="18" t="n"/>
+    </row>
+    <row r="15" ht="34" customHeight="1">
+      <c r="A15" s="14" t="n"/>
+      <c r="B15" s="14" t="n"/>
+      <c r="C15" s="14" t="n"/>
+      <c r="D15" s="14" t="n"/>
+      <c r="E15" s="14" t="n"/>
+      <c r="F15" s="19" t="inlineStr">
+        <is>
+          <t>Send project update to internal WDCO K5M group</t>
+        </is>
+      </c>
+      <c r="G15" s="14" t="n"/>
+    </row>
+    <row r="16" ht="34" customHeight="1">
+      <c r="A16" s="14" t="n"/>
+      <c r="B16" s="14" t="n"/>
+      <c r="C16" s="14" t="n"/>
+      <c r="D16" s="14" t="n"/>
+      <c r="E16" s="14" t="n"/>
+      <c r="F16" s="14" t="n"/>
+      <c r="G16" s="14" t="n"/>
+    </row>
+    <row r="17" ht="34" customHeight="1">
+      <c r="A17" s="14" t="n"/>
+      <c r="B17" s="14" t="n"/>
+      <c r="C17" s="14" t="n"/>
+      <c r="D17" s="14" t="n"/>
+      <c r="E17" s="14" t="n"/>
+      <c r="F17" s="14" t="n"/>
+      <c r="G17" s="14" t="n"/>
+    </row>
+    <row r="18" ht="34" customHeight="1">
+      <c r="A18" s="14" t="n"/>
+      <c r="B18" s="14" t="n"/>
+      <c r="C18" s="14" t="n"/>
+      <c r="D18" s="14" t="n"/>
+      <c r="E18" s="14" t="n"/>
+      <c r="F18" s="14" t="n"/>
+      <c r="G18" s="14" t="n"/>
+    </row>
+    <row r="19" ht="16" customHeight="1">
+      <c r="A19" s="13" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B19" s="13" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="C7" s="12" t="inlineStr">
+      <c r="C19" s="13" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="D7" s="12" t="inlineStr">
+      <c r="D19" s="13" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="E7" s="12" t="inlineStr">
+      <c r="E19" s="13" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="F7" s="12" t="inlineStr">
+      <c r="F19" s="13" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="G7" s="12" t="inlineStr">
+      <c r="G19" s="13" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="60" customHeight="1">
-      <c r="A8" s="12" t="inlineStr">
+    <row r="20" ht="34" customHeight="1">
+      <c r="A20" s="16" t="inlineStr">
+        <is>
+          <t>Sea freight to Casablanca</t>
+        </is>
+      </c>
+      <c r="B20" s="17" t="n"/>
+      <c r="C20" s="17" t="n"/>
+      <c r="D20" s="17" t="n"/>
+      <c r="E20" s="17" t="n"/>
+      <c r="F20" s="17" t="n"/>
+      <c r="G20" s="18" t="n"/>
+    </row>
+    <row r="21" ht="34" customHeight="1">
+      <c r="A21" s="21" t="inlineStr">
+        <is>
+          <t>Packing, dispatch, sea freight, customs, delivery</t>
+        </is>
+      </c>
+      <c r="B21" s="17" t="n"/>
+      <c r="C21" s="17" t="n"/>
+      <c r="D21" s="17" t="n"/>
+      <c r="E21" s="17" t="n"/>
+      <c r="F21" s="17" t="n"/>
+      <c r="G21" s="18" t="n"/>
+    </row>
+    <row r="22" ht="34" customHeight="1">
+      <c r="A22" s="29" t="inlineStr">
+        <is>
+          <t>⚑ Internal working deadline</t>
+        </is>
+      </c>
+      <c r="B22" s="14" t="n"/>
+      <c r="C22" s="14" t="n"/>
+      <c r="D22" s="14" t="n"/>
+      <c r="E22" s="14" t="n"/>
+      <c r="F22" s="23" t="inlineStr">
+        <is>
+          <t>Send project update to client-facing group</t>
+        </is>
+      </c>
+      <c r="G22" s="14" t="n"/>
+    </row>
+    <row r="23" ht="34" customHeight="1">
+      <c r="A23" s="14" t="n"/>
+      <c r="B23" s="14" t="n"/>
+      <c r="C23" s="14" t="n"/>
+      <c r="D23" s="14" t="n"/>
+      <c r="E23" s="14" t="n"/>
+      <c r="F23" s="19" t="inlineStr">
+        <is>
+          <t>Send project update to internal WDCO K5M group</t>
+        </is>
+      </c>
+      <c r="G23" s="14" t="n"/>
+    </row>
+    <row r="24" ht="34" customHeight="1">
+      <c r="A24" s="14" t="n"/>
+      <c r="B24" s="14" t="n"/>
+      <c r="C24" s="14" t="n"/>
+      <c r="D24" s="14" t="n"/>
+      <c r="E24" s="14" t="n"/>
+      <c r="F24" s="14" t="n"/>
+      <c r="G24" s="14" t="n"/>
+    </row>
+    <row r="25" ht="34" customHeight="1">
+      <c r="A25" s="14" t="n"/>
+      <c r="B25" s="14" t="n"/>
+      <c r="C25" s="14" t="n"/>
+      <c r="D25" s="14" t="n"/>
+      <c r="E25" s="14" t="n"/>
+      <c r="F25" s="14" t="n"/>
+      <c r="G25" s="14" t="n"/>
+    </row>
+    <row r="26" ht="16" customHeight="1">
+      <c r="A26" s="13" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="B8" s="12" t="inlineStr">
+      <c r="B26" s="13" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="C8" s="12" t="inlineStr">
+      <c r="C26" s="13" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="D8" s="12" t="inlineStr">
+      <c r="D26" s="13" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="E8" s="12" t="inlineStr">
+      <c r="E26" s="13" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="F8" s="12" t="inlineStr">
+      <c r="F26" s="13" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="G8" s="12" t="inlineStr">
+      <c r="G26" s="13" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="68" customHeight="1">
-      <c r="A9" s="17" t="inlineStr">
-        <is>
-          <t>29
-[Supplier] Fit-Out and FF&amp;E installation (29–13 Dec)</t>
-        </is>
-      </c>
-      <c r="B9" s="12" t="inlineStr">
+    <row r="27" ht="34" customHeight="1">
+      <c r="A27" s="16" t="inlineStr">
+        <is>
+          <t>Sea freight to Casablanca</t>
+        </is>
+      </c>
+      <c r="B27" s="17" t="n"/>
+      <c r="C27" s="17" t="n"/>
+      <c r="D27" s="17" t="n"/>
+      <c r="E27" s="17" t="n"/>
+      <c r="F27" s="17" t="n"/>
+      <c r="G27" s="18" t="n"/>
+    </row>
+    <row r="28" ht="34" customHeight="1">
+      <c r="A28" s="21" t="inlineStr">
+        <is>
+          <t>Packing, dispatch, sea freight, customs, delivery</t>
+        </is>
+      </c>
+      <c r="B28" s="17" t="n"/>
+      <c r="C28" s="17" t="n"/>
+      <c r="D28" s="17" t="n"/>
+      <c r="E28" s="17" t="n"/>
+      <c r="F28" s="17" t="n"/>
+      <c r="G28" s="18" t="n"/>
+    </row>
+    <row r="29" ht="34" customHeight="1">
+      <c r="A29" s="14" t="n"/>
+      <c r="B29" s="14" t="n"/>
+      <c r="C29" s="14" t="n"/>
+      <c r="D29" s="14" t="n"/>
+      <c r="E29" s="14" t="n"/>
+      <c r="F29" s="19" t="inlineStr">
+        <is>
+          <t>Send project update to internal WDCO K5M group</t>
+        </is>
+      </c>
+      <c r="G29" s="14" t="n"/>
+    </row>
+    <row r="30" ht="34" customHeight="1">
+      <c r="A30" s="14" t="n"/>
+      <c r="B30" s="14" t="n"/>
+      <c r="C30" s="14" t="n"/>
+      <c r="D30" s="14" t="n"/>
+      <c r="E30" s="14" t="n"/>
+      <c r="F30" s="14" t="n"/>
+      <c r="G30" s="14" t="n"/>
+    </row>
+    <row r="31" ht="34" customHeight="1">
+      <c r="A31" s="14" t="n"/>
+      <c r="B31" s="14" t="n"/>
+      <c r="C31" s="14" t="n"/>
+      <c r="D31" s="14" t="n"/>
+      <c r="E31" s="14" t="n"/>
+      <c r="F31" s="14" t="n"/>
+      <c r="G31" s="14" t="n"/>
+    </row>
+    <row r="32" ht="34" customHeight="1">
+      <c r="A32" s="14" t="n"/>
+      <c r="B32" s="14" t="n"/>
+      <c r="C32" s="14" t="n"/>
+      <c r="D32" s="14" t="n"/>
+      <c r="E32" s="14" t="n"/>
+      <c r="F32" s="14" t="n"/>
+      <c r="G32" s="14" t="n"/>
+    </row>
+    <row r="33" ht="16" customHeight="1">
+      <c r="A33" s="13" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="B33" s="13" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="C9" s="11" t="n"/>
-      <c r="D9" s="11" t="n"/>
-      <c r="E9" s="11" t="n"/>
-      <c r="F9" s="11" t="n"/>
-      <c r="G9" s="11" t="n"/>
+      <c r="C33" s="12" t="n"/>
+      <c r="D33" s="12" t="n"/>
+      <c r="E33" s="12" t="n"/>
+      <c r="F33" s="12" t="n"/>
+      <c r="G33" s="12" t="n"/>
+    </row>
+    <row r="34" ht="34" customHeight="1">
+      <c r="A34" s="21" t="inlineStr">
+        <is>
+          <t>Fit-Out and FF&amp;E installation</t>
+        </is>
+      </c>
+      <c r="B34" s="17" t="n"/>
+      <c r="C34" s="17" t="n"/>
+      <c r="D34" s="17" t="n"/>
+      <c r="E34" s="17" t="n"/>
+      <c r="F34" s="17" t="n"/>
+      <c r="G34" s="18" t="n"/>
+    </row>
+    <row r="35" ht="34" customHeight="1">
+      <c r="A35" s="16" t="inlineStr">
+        <is>
+          <t>Sea freight to Casablanca</t>
+        </is>
+      </c>
+      <c r="B35" s="17" t="n"/>
+      <c r="C35" s="17" t="n"/>
+      <c r="D35" s="17" t="n"/>
+      <c r="E35" s="18" t="n"/>
+      <c r="F35" s="16" t="inlineStr">
+        <is>
+          <t>Fit-out installation</t>
+        </is>
+      </c>
+      <c r="G35" s="18" t="n"/>
+    </row>
+    <row r="36" ht="34" customHeight="1">
+      <c r="A36" s="14" t="n"/>
+      <c r="B36" s="14" t="n"/>
+      <c r="C36" s="14" t="n"/>
+      <c r="D36" s="14" t="n"/>
+      <c r="E36" s="16" t="inlineStr">
+        <is>
+          <t>Customs, port release, delivery to site</t>
+        </is>
+      </c>
+      <c r="F36" s="17" t="n"/>
+      <c r="G36" s="18" t="n"/>
+    </row>
+    <row r="37" ht="34" customHeight="1">
+      <c r="A37" s="14" t="n"/>
+      <c r="B37" s="14" t="n"/>
+      <c r="C37" s="14" t="n"/>
+      <c r="D37" s="14" t="n"/>
+      <c r="E37" s="14" t="n"/>
+      <c r="F37" s="23" t="inlineStr">
+        <is>
+          <t>Send project update to client-facing group</t>
+        </is>
+      </c>
+      <c r="G37" s="14" t="n"/>
+    </row>
+    <row r="38" ht="34" customHeight="1">
+      <c r="A38" s="14" t="n"/>
+      <c r="B38" s="14" t="n"/>
+      <c r="C38" s="14" t="n"/>
+      <c r="D38" s="14" t="n"/>
+      <c r="E38" s="14" t="n"/>
+      <c r="F38" s="19" t="inlineStr">
+        <is>
+          <t>Send project update to internal WDCO K5M group</t>
+        </is>
+      </c>
+      <c r="G38" s="14" t="n"/>
+    </row>
+    <row r="39" ht="34" customHeight="1">
+      <c r="A39" s="14" t="n"/>
+      <c r="B39" s="14" t="n"/>
+      <c r="C39" s="14" t="n"/>
+      <c r="D39" s="14" t="n"/>
+      <c r="E39" s="14" t="n"/>
+      <c r="F39" s="14" t="n"/>
+      <c r="G39" s="14" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="5">
-    <mergeCell ref="A2:B2"/>
+  <mergeCells count="17">
+    <mergeCell ref="A13:G13"/>
+    <mergeCell ref="A14:G14"/>
+    <mergeCell ref="A35:E35"/>
     <mergeCell ref="A1:G1"/>
-    <mergeCell ref="C2:D2"/>
-    <mergeCell ref="G2:H2"/>
-    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="E36:G36"/>
+    <mergeCell ref="A27:G27"/>
+    <mergeCell ref="A6:G6"/>
+    <mergeCell ref="A21:G21"/>
+    <mergeCell ref="A34:G34"/>
+    <mergeCell ref="A20:G20"/>
+    <mergeCell ref="B2"/>
+    <mergeCell ref="A2"/>
+    <mergeCell ref="D2"/>
+    <mergeCell ref="C2"/>
+    <mergeCell ref="A7:G7"/>
+    <mergeCell ref="F35:G35"/>
+    <mergeCell ref="A28:G28"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3405,266 +5836,618 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:G39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="26" customWidth="1" min="5" max="5"/>
+    <col width="26" customWidth="1" min="6" max="6"/>
+    <col width="26" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="5" t="inlineStr">
+      <c r="A1" s="10" t="inlineStr">
         <is>
           <t>K5M — DECEMBER 2026</t>
         </is>
       </c>
     </row>
     <row r="2" ht="16" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">  Client</t>
         </is>
       </c>
-      <c r="C2" s="7" t="inlineStr">
+      <c r="B2" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">  Supplier</t>
         </is>
       </c>
-      <c r="E2" s="8" t="inlineStr">
+      <c r="C2" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">  WDCO Internal PM</t>
         </is>
       </c>
-      <c r="G2" s="9" t="inlineStr">
+      <c r="D2" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">  Deadline (red border)</t>
         </is>
       </c>
     </row>
     <row r="4" ht="18" customHeight="1">
-      <c r="A4" s="10" t="inlineStr">
+      <c r="A4" s="11" t="inlineStr">
         <is>
           <t>Sunday</t>
         </is>
       </c>
-      <c r="B4" s="10" t="inlineStr">
+      <c r="B4" s="11" t="inlineStr">
         <is>
           <t>Monday</t>
         </is>
       </c>
-      <c r="C4" s="10" t="inlineStr">
+      <c r="C4" s="11" t="inlineStr">
         <is>
           <t>Tuesday</t>
         </is>
       </c>
-      <c r="D4" s="10" t="inlineStr">
+      <c r="D4" s="11" t="inlineStr">
         <is>
           <t>Wednesday</t>
         </is>
       </c>
-      <c r="E4" s="10" t="inlineStr">
+      <c r="E4" s="11" t="inlineStr">
         <is>
           <t>Thursday</t>
         </is>
       </c>
-      <c r="F4" s="10" t="inlineStr">
+      <c r="F4" s="11" t="inlineStr">
         <is>
           <t>Friday</t>
         </is>
       </c>
-      <c r="G4" s="10" t="inlineStr">
+      <c r="G4" s="11" t="inlineStr">
         <is>
           <t>Saturday</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="68" customHeight="1">
-      <c r="A5" s="11" t="n"/>
-      <c r="B5" s="11" t="n"/>
-      <c r="C5" s="12" t="inlineStr">
+    <row r="5" ht="16" customHeight="1">
+      <c r="A5" s="12" t="n"/>
+      <c r="B5" s="12" t="n"/>
+      <c r="C5" s="13" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D5" s="12" t="inlineStr">
+      <c r="D5" s="13" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E5" s="14" t="inlineStr">
-        <is>
-          <t>3
-[Client] Customs, port release, delivery to site (3–7 Dec)</t>
-        </is>
-      </c>
-      <c r="F5" s="14" t="inlineStr">
-        <is>
-          <t>4
-[Client] Fit-out installation (4–18 Dec)</t>
-        </is>
-      </c>
-      <c r="G5" s="12" t="inlineStr">
+      <c r="E5" s="13" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F5" s="13" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G5" s="13" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="60" customHeight="1">
-      <c r="A6" s="12" t="inlineStr">
+    <row r="6" ht="34" customHeight="1">
+      <c r="A6" s="21" t="inlineStr">
+        <is>
+          <t>Fit-Out and FF&amp;E installation</t>
+        </is>
+      </c>
+      <c r="B6" s="17" t="n"/>
+      <c r="C6" s="17" t="n"/>
+      <c r="D6" s="17" t="n"/>
+      <c r="E6" s="17" t="n"/>
+      <c r="F6" s="17" t="n"/>
+      <c r="G6" s="18" t="n"/>
+    </row>
+    <row r="7" ht="34" customHeight="1">
+      <c r="A7" s="16" t="inlineStr">
+        <is>
+          <t>Sea freight to Casablanca</t>
+        </is>
+      </c>
+      <c r="B7" s="17" t="n"/>
+      <c r="C7" s="17" t="n"/>
+      <c r="D7" s="17" t="n"/>
+      <c r="E7" s="18" t="n"/>
+      <c r="F7" s="16" t="inlineStr">
+        <is>
+          <t>Fit-out installation</t>
+        </is>
+      </c>
+      <c r="G7" s="18" t="n"/>
+    </row>
+    <row r="8" ht="34" customHeight="1">
+      <c r="A8" s="14" t="n"/>
+      <c r="B8" s="14" t="n"/>
+      <c r="C8" s="14" t="n"/>
+      <c r="D8" s="14" t="n"/>
+      <c r="E8" s="16" t="inlineStr">
+        <is>
+          <t>Customs, port release, delivery to site</t>
+        </is>
+      </c>
+      <c r="F8" s="17" t="n"/>
+      <c r="G8" s="18" t="n"/>
+    </row>
+    <row r="9" ht="34" customHeight="1">
+      <c r="A9" s="14" t="n"/>
+      <c r="B9" s="14" t="n"/>
+      <c r="C9" s="14" t="n"/>
+      <c r="D9" s="14" t="n"/>
+      <c r="E9" s="14" t="n"/>
+      <c r="F9" s="23" t="inlineStr">
+        <is>
+          <t>Send project update to client-facing group</t>
+        </is>
+      </c>
+      <c r="G9" s="14" t="n"/>
+    </row>
+    <row r="10" ht="34" customHeight="1">
+      <c r="A10" s="14" t="n"/>
+      <c r="B10" s="14" t="n"/>
+      <c r="C10" s="14" t="n"/>
+      <c r="D10" s="14" t="n"/>
+      <c r="E10" s="14" t="n"/>
+      <c r="F10" s="19" t="inlineStr">
+        <is>
+          <t>Send project update to internal WDCO K5M group</t>
+        </is>
+      </c>
+      <c r="G10" s="14" t="n"/>
+    </row>
+    <row r="11" ht="34" customHeight="1">
+      <c r="A11" s="14" t="n"/>
+      <c r="B11" s="14" t="n"/>
+      <c r="C11" s="14" t="n"/>
+      <c r="D11" s="14" t="n"/>
+      <c r="E11" s="14" t="n"/>
+      <c r="F11" s="14" t="n"/>
+      <c r="G11" s="14" t="n"/>
+    </row>
+    <row r="12" ht="16" customHeight="1">
+      <c r="A12" s="13" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="B6" s="12" t="inlineStr">
+      <c r="B12" s="13" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="C6" s="12" t="inlineStr">
+      <c r="C12" s="13" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D6" s="12" t="inlineStr">
+      <c r="D12" s="13" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="E6" s="12" t="inlineStr">
+      <c r="E12" s="13" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="F6" s="12" t="inlineStr">
+      <c r="F12" s="13" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="G6" s="12" t="inlineStr">
+      <c r="G12" s="13" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="68" customHeight="1">
-      <c r="A7" s="12" t="inlineStr">
+    <row r="13" ht="34" customHeight="1">
+      <c r="A13" s="16" t="inlineStr">
+        <is>
+          <t>Fit-out installation</t>
+        </is>
+      </c>
+      <c r="B13" s="17" t="n"/>
+      <c r="C13" s="17" t="n"/>
+      <c r="D13" s="17" t="n"/>
+      <c r="E13" s="17" t="n"/>
+      <c r="F13" s="17" t="n"/>
+      <c r="G13" s="18" t="n"/>
+    </row>
+    <row r="14" ht="34" customHeight="1">
+      <c r="A14" s="21" t="inlineStr">
+        <is>
+          <t>Fit-Out and FF&amp;E installation</t>
+        </is>
+      </c>
+      <c r="B14" s="17" t="n"/>
+      <c r="C14" s="17" t="n"/>
+      <c r="D14" s="17" t="n"/>
+      <c r="E14" s="17" t="n"/>
+      <c r="F14" s="17" t="n"/>
+      <c r="G14" s="18" t="n"/>
+    </row>
+    <row r="15" ht="34" customHeight="1">
+      <c r="A15" s="16" t="inlineStr">
+        <is>
+          <t>Customs, port release, delivery to site</t>
+        </is>
+      </c>
+      <c r="B15" s="18" t="n"/>
+      <c r="C15" s="14" t="n"/>
+      <c r="D15" s="14" t="n"/>
+      <c r="E15" s="14" t="n"/>
+      <c r="F15" s="19" t="inlineStr">
+        <is>
+          <t>Send project update to internal WDCO K5M group</t>
+        </is>
+      </c>
+      <c r="G15" s="14" t="n"/>
+    </row>
+    <row r="16" ht="34" customHeight="1">
+      <c r="A16" s="14" t="n"/>
+      <c r="B16" s="14" t="n"/>
+      <c r="C16" s="14" t="n"/>
+      <c r="D16" s="14" t="n"/>
+      <c r="E16" s="14" t="n"/>
+      <c r="F16" s="14" t="n"/>
+      <c r="G16" s="14" t="n"/>
+    </row>
+    <row r="17" ht="34" customHeight="1">
+      <c r="A17" s="14" t="n"/>
+      <c r="B17" s="14" t="n"/>
+      <c r="C17" s="14" t="n"/>
+      <c r="D17" s="14" t="n"/>
+      <c r="E17" s="14" t="n"/>
+      <c r="F17" s="14" t="n"/>
+      <c r="G17" s="14" t="n"/>
+    </row>
+    <row r="18" ht="34" customHeight="1">
+      <c r="A18" s="14" t="n"/>
+      <c r="B18" s="14" t="n"/>
+      <c r="C18" s="14" t="n"/>
+      <c r="D18" s="14" t="n"/>
+      <c r="E18" s="14" t="n"/>
+      <c r="F18" s="14" t="n"/>
+      <c r="G18" s="14" t="n"/>
+    </row>
+    <row r="19" ht="16" customHeight="1">
+      <c r="A19" s="13" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="B7" s="16" t="inlineStr">
-        <is>
-          <t>14
-⚑ [Supplier] Ready for site inspection</t>
-        </is>
-      </c>
-      <c r="C7" s="16" t="inlineStr">
-        <is>
-          <t>15
-⚑ [Supplier] Hard deadline (as communicated to supplier)</t>
-        </is>
-      </c>
-      <c r="D7" s="12" t="inlineStr">
+      <c r="B19" s="13" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="C19" s="13" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D19" s="13" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="E7" s="12" t="inlineStr">
+      <c r="E19" s="13" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="F7" s="12" t="inlineStr">
+      <c r="F19" s="13" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="G7" s="14" t="inlineStr">
-        <is>
-          <t>19
-[Client] FF&amp;E installation (19–20 Dec)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="68" customHeight="1">
-      <c r="A8" s="19" t="inlineStr">
-        <is>
-          <t>20
-⚑ [Client] Complete T1B1 mock-up ready for inspection</t>
-        </is>
-      </c>
-      <c r="B8" s="12" t="inlineStr">
+      <c r="G19" s="13" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="34" customHeight="1">
+      <c r="A20" s="16" t="inlineStr">
+        <is>
+          <t>Fit-out installation</t>
+        </is>
+      </c>
+      <c r="B20" s="17" t="n"/>
+      <c r="C20" s="17" t="n"/>
+      <c r="D20" s="17" t="n"/>
+      <c r="E20" s="17" t="n"/>
+      <c r="F20" s="18" t="n"/>
+      <c r="G20" s="23" t="inlineStr">
+        <is>
+          <t>FF&amp;E installation</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="34" customHeight="1">
+      <c r="A21" s="27" t="inlineStr">
+        <is>
+          <t>Fit-Out and FF&amp;E installation</t>
+        </is>
+      </c>
+      <c r="B21" s="22" t="inlineStr">
+        <is>
+          <t>⚑ Ready for site inspection</t>
+        </is>
+      </c>
+      <c r="C21" s="22" t="inlineStr">
+        <is>
+          <t>⚑ Hard deadline (as communicated to supplier)</t>
+        </is>
+      </c>
+      <c r="D21" s="14" t="n"/>
+      <c r="E21" s="14" t="n"/>
+      <c r="F21" s="23" t="inlineStr">
+        <is>
+          <t>Send project update to client-facing group</t>
+        </is>
+      </c>
+      <c r="G21" s="14" t="n"/>
+    </row>
+    <row r="22" ht="34" customHeight="1">
+      <c r="A22" s="14" t="n"/>
+      <c r="B22" s="14" t="n"/>
+      <c r="C22" s="14" t="n"/>
+      <c r="D22" s="14" t="n"/>
+      <c r="E22" s="14" t="n"/>
+      <c r="F22" s="19" t="inlineStr">
+        <is>
+          <t>Send project update to internal WDCO K5M group</t>
+        </is>
+      </c>
+      <c r="G22" s="14" t="n"/>
+    </row>
+    <row r="23" ht="34" customHeight="1">
+      <c r="A23" s="14" t="n"/>
+      <c r="B23" s="14" t="n"/>
+      <c r="C23" s="14" t="n"/>
+      <c r="D23" s="14" t="n"/>
+      <c r="E23" s="14" t="n"/>
+      <c r="F23" s="14" t="n"/>
+      <c r="G23" s="14" t="n"/>
+    </row>
+    <row r="24" ht="34" customHeight="1">
+      <c r="A24" s="14" t="n"/>
+      <c r="B24" s="14" t="n"/>
+      <c r="C24" s="14" t="n"/>
+      <c r="D24" s="14" t="n"/>
+      <c r="E24" s="14" t="n"/>
+      <c r="F24" s="14" t="n"/>
+      <c r="G24" s="14" t="n"/>
+    </row>
+    <row r="25" ht="34" customHeight="1">
+      <c r="A25" s="14" t="n"/>
+      <c r="B25" s="14" t="n"/>
+      <c r="C25" s="14" t="n"/>
+      <c r="D25" s="14" t="n"/>
+      <c r="E25" s="14" t="n"/>
+      <c r="F25" s="14" t="n"/>
+      <c r="G25" s="14" t="n"/>
+    </row>
+    <row r="26" ht="16" customHeight="1">
+      <c r="A26" s="13" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B26" s="13" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="C8" s="12" t="inlineStr">
+      <c r="C26" s="13" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="D8" s="12" t="inlineStr">
+      <c r="D26" s="13" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="E8" s="12" t="inlineStr">
+      <c r="E26" s="13" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="F8" s="12" t="inlineStr">
+      <c r="F26" s="13" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="G8" s="12" t="inlineStr">
+      <c r="G26" s="13" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="60" customHeight="1">
-      <c r="A9" s="12" t="inlineStr">
+    <row r="27" ht="34" customHeight="1">
+      <c r="A27" s="23" t="inlineStr">
+        <is>
+          <t>FF&amp;E installation</t>
+        </is>
+      </c>
+      <c r="B27" s="14" t="n"/>
+      <c r="C27" s="14" t="n"/>
+      <c r="D27" s="14" t="n"/>
+      <c r="E27" s="14" t="n"/>
+      <c r="F27" s="19" t="inlineStr">
+        <is>
+          <t>Send project update to internal WDCO K5M group</t>
+        </is>
+      </c>
+      <c r="G27" s="14" t="n"/>
+    </row>
+    <row r="28" ht="34" customHeight="1">
+      <c r="A28" s="15" t="inlineStr">
+        <is>
+          <t>⚑ Complete T1B1 mock-up ready for inspection</t>
+        </is>
+      </c>
+      <c r="B28" s="14" t="n"/>
+      <c r="C28" s="14" t="n"/>
+      <c r="D28" s="14" t="n"/>
+      <c r="E28" s="14" t="n"/>
+      <c r="F28" s="14" t="n"/>
+      <c r="G28" s="14" t="n"/>
+    </row>
+    <row r="29" ht="34" customHeight="1">
+      <c r="A29" s="14" t="n"/>
+      <c r="B29" s="14" t="n"/>
+      <c r="C29" s="14" t="n"/>
+      <c r="D29" s="14" t="n"/>
+      <c r="E29" s="14" t="n"/>
+      <c r="F29" s="14" t="n"/>
+      <c r="G29" s="14" t="n"/>
+    </row>
+    <row r="30" ht="34" customHeight="1">
+      <c r="A30" s="14" t="n"/>
+      <c r="B30" s="14" t="n"/>
+      <c r="C30" s="14" t="n"/>
+      <c r="D30" s="14" t="n"/>
+      <c r="E30" s="14" t="n"/>
+      <c r="F30" s="14" t="n"/>
+      <c r="G30" s="14" t="n"/>
+    </row>
+    <row r="31" ht="34" customHeight="1">
+      <c r="A31" s="14" t="n"/>
+      <c r="B31" s="14" t="n"/>
+      <c r="C31" s="14" t="n"/>
+      <c r="D31" s="14" t="n"/>
+      <c r="E31" s="14" t="n"/>
+      <c r="F31" s="14" t="n"/>
+      <c r="G31" s="14" t="n"/>
+    </row>
+    <row r="32" ht="34" customHeight="1">
+      <c r="A32" s="14" t="n"/>
+      <c r="B32" s="14" t="n"/>
+      <c r="C32" s="14" t="n"/>
+      <c r="D32" s="14" t="n"/>
+      <c r="E32" s="14" t="n"/>
+      <c r="F32" s="14" t="n"/>
+      <c r="G32" s="14" t="n"/>
+    </row>
+    <row r="33" ht="16" customHeight="1">
+      <c r="A33" s="13" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="B9" s="12" t="inlineStr">
+      <c r="B33" s="13" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="C9" s="12" t="inlineStr">
+      <c r="C33" s="13" t="inlineStr">
         <is>
           <t>29</t>
         </is>
       </c>
-      <c r="D9" s="12" t="inlineStr">
+      <c r="D33" s="13" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="E9" s="12" t="inlineStr">
+      <c r="E33" s="13" t="inlineStr">
         <is>
           <t>31</t>
         </is>
       </c>
-      <c r="F9" s="11" t="n"/>
-      <c r="G9" s="11" t="n"/>
+      <c r="F33" s="12" t="n"/>
+      <c r="G33" s="12" t="n"/>
+    </row>
+    <row r="34" ht="34" customHeight="1">
+      <c r="A34" s="14" t="n"/>
+      <c r="B34" s="14" t="n"/>
+      <c r="C34" s="14" t="n"/>
+      <c r="D34" s="14" t="n"/>
+      <c r="E34" s="14" t="n"/>
+      <c r="F34" s="14" t="n"/>
+      <c r="G34" s="14" t="n"/>
+    </row>
+    <row r="35" ht="34" customHeight="1">
+      <c r="A35" s="14" t="n"/>
+      <c r="B35" s="14" t="n"/>
+      <c r="C35" s="14" t="n"/>
+      <c r="D35" s="14" t="n"/>
+      <c r="E35" s="14" t="n"/>
+      <c r="F35" s="14" t="n"/>
+      <c r="G35" s="14" t="n"/>
+    </row>
+    <row r="36" ht="34" customHeight="1">
+      <c r="A36" s="14" t="n"/>
+      <c r="B36" s="14" t="n"/>
+      <c r="C36" s="14" t="n"/>
+      <c r="D36" s="14" t="n"/>
+      <c r="E36" s="14" t="n"/>
+      <c r="F36" s="14" t="n"/>
+      <c r="G36" s="14" t="n"/>
+    </row>
+    <row r="37" ht="34" customHeight="1">
+      <c r="A37" s="14" t="n"/>
+      <c r="B37" s="14" t="n"/>
+      <c r="C37" s="14" t="n"/>
+      <c r="D37" s="14" t="n"/>
+      <c r="E37" s="14" t="n"/>
+      <c r="F37" s="14" t="n"/>
+      <c r="G37" s="14" t="n"/>
+    </row>
+    <row r="38" ht="34" customHeight="1">
+      <c r="A38" s="14" t="n"/>
+      <c r="B38" s="14" t="n"/>
+      <c r="C38" s="14" t="n"/>
+      <c r="D38" s="14" t="n"/>
+      <c r="E38" s="14" t="n"/>
+      <c r="F38" s="14" t="n"/>
+      <c r="G38" s="14" t="n"/>
+    </row>
+    <row r="39" ht="34" customHeight="1">
+      <c r="A39" s="14" t="n"/>
+      <c r="B39" s="14" t="n"/>
+      <c r="C39" s="14" t="n"/>
+      <c r="D39" s="14" t="n"/>
+      <c r="E39" s="14" t="n"/>
+      <c r="F39" s="14" t="n"/>
+      <c r="G39" s="14" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="5">
-    <mergeCell ref="A2:B2"/>
+  <mergeCells count="13">
+    <mergeCell ref="A13:G13"/>
+    <mergeCell ref="A14:G14"/>
     <mergeCell ref="A1:G1"/>
-    <mergeCell ref="C2:D2"/>
-    <mergeCell ref="G2:H2"/>
-    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="A6:G6"/>
+    <mergeCell ref="A7:E7"/>
+    <mergeCell ref="E8:G8"/>
+    <mergeCell ref="B2"/>
+    <mergeCell ref="A2"/>
+    <mergeCell ref="D2"/>
+    <mergeCell ref="C2"/>
+    <mergeCell ref="A20:F20"/>
+    <mergeCell ref="F7:G7"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3676,385 +6459,1276 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D19"/>
+  <dimension ref="A1:V33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="44" customWidth="1" min="3" max="3"/>
-    <col width="50" customWidth="1" min="4" max="4"/>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="5" customWidth="1" min="2" max="2"/>
+    <col width="5" customWidth="1" min="3" max="3"/>
+    <col width="5" customWidth="1" min="4" max="4"/>
+    <col width="5" customWidth="1" min="5" max="5"/>
+    <col width="5" customWidth="1" min="6" max="6"/>
+    <col width="5" customWidth="1" min="7" max="7"/>
+    <col width="5" customWidth="1" min="8" max="8"/>
+    <col width="5" customWidth="1" min="9" max="9"/>
+    <col width="5" customWidth="1" min="10" max="10"/>
+    <col width="5" customWidth="1" min="11" max="11"/>
+    <col width="5" customWidth="1" min="12" max="12"/>
+    <col width="5" customWidth="1" min="13" max="13"/>
+    <col width="5" customWidth="1" min="14" max="14"/>
+    <col width="5" customWidth="1" min="15" max="15"/>
+    <col width="5" customWidth="1" min="16" max="16"/>
+    <col width="12" customWidth="1" min="18" max="18"/>
+    <col width="16" customWidth="1" min="19" max="19"/>
+    <col width="40" customWidth="1" min="20" max="20"/>
+    <col width="44" customWidth="1" min="21" max="21"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>K5M — PROJECT CALENDAR — DEADLINES SUMMARY</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="28" customHeight="1">
+          <t>K5M — HARD MILESTONES</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>v1 draft — deadlines marked here are a first pass (explicit milestones from both source schedules plus the one internal working-deadline note). Not yet confirmed as the final definition of "deadline" — to be refined once reviewed.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="18" customHeight="1">
-      <c r="A4" s="21" t="inlineStr">
+          <t xml:space="preserve">  Client</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Supplier</t>
+        </is>
+      </c>
+      <c r="K2" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  WDCO Internal PM</t>
+        </is>
+      </c>
+      <c r="P2" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Deadline (red border)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="26" customHeight="1">
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>v2 draft — mini-month overview, Jul-Dec 2026. Deadline days highlighted directly on the mini calendars; matching list on the right. Not yet confirmed as the final definition of "deadline".</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="16" customHeight="1">
+      <c r="A5" s="30" t="inlineStr">
+        <is>
+          <t>JULY 2026</t>
+        </is>
+      </c>
+      <c r="I5" s="30" t="inlineStr">
+        <is>
+          <t>AUGUST 2026</t>
+        </is>
+      </c>
+      <c r="R5" s="31" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="B4" s="21" t="inlineStr">
+      <c r="S5" s="31" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="C4" s="21" t="inlineStr">
+      <c r="T5" s="31" t="inlineStr">
         <is>
           <t>Deadline</t>
         </is>
       </c>
-      <c r="D4" s="21" t="inlineStr">
+      <c r="U5" s="31" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="28" customHeight="1">
-      <c r="A5" s="22" t="inlineStr">
+    <row r="6" ht="26" customHeight="1">
+      <c r="A6" s="32" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="B6" s="32" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="C6" s="32" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="D6" s="32" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="E6" s="32" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="F6" s="32" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="G6" s="32" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I6" s="32" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="J6" s="32" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="K6" s="32" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="L6" s="32" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="M6" s="32" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="N6" s="32" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="O6" s="32" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="R6" s="33" t="inlineStr">
         <is>
           <t>15 Jul 2026</t>
         </is>
       </c>
-      <c r="B5" s="23" t="inlineStr">
+      <c r="S6" s="34" t="inlineStr">
         <is>
           <t>Client</t>
         </is>
       </c>
-      <c r="C5" s="22" t="inlineStr">
+      <c r="T6" s="33" t="inlineStr">
         <is>
           <t>Project kick-off</t>
         </is>
       </c>
-      <c r="D5" s="22" t="inlineStr">
+      <c r="U6" s="33" t="inlineStr">
         <is>
           <t>Milestone.</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="28" customHeight="1">
-      <c r="A6" s="22" t="inlineStr">
+    <row r="7" ht="26" customHeight="1">
+      <c r="A7" s="35" t="n"/>
+      <c r="B7" s="35" t="n"/>
+      <c r="C7" s="35" t="n"/>
+      <c r="D7" s="36" t="n">
+        <v>1</v>
+      </c>
+      <c r="E7" s="36" t="n">
+        <v>2</v>
+      </c>
+      <c r="F7" s="36" t="n">
+        <v>3</v>
+      </c>
+      <c r="G7" s="36" t="n">
+        <v>4</v>
+      </c>
+      <c r="I7" s="35" t="n"/>
+      <c r="J7" s="35" t="n"/>
+      <c r="K7" s="35" t="n"/>
+      <c r="L7" s="35" t="n"/>
+      <c r="M7" s="35" t="n"/>
+      <c r="N7" s="35" t="n"/>
+      <c r="O7" s="36" t="n">
+        <v>1</v>
+      </c>
+      <c r="R7" s="33" t="inlineStr">
         <is>
           <t>22 Jul 2026</t>
         </is>
       </c>
-      <c r="B6" s="24" t="inlineStr">
+      <c r="S7" s="37" t="inlineStr">
         <is>
           <t>Supplier</t>
         </is>
       </c>
-      <c r="C6" s="22" t="inlineStr">
+      <c r="T7" s="33" t="inlineStr">
         <is>
           <t>SHD V00 parallel review &amp; feedback</t>
         </is>
       </c>
-      <c r="D6" s="22" t="inlineStr">
+      <c r="U7" s="33" t="inlineStr">
         <is>
           <t>28 Jul is the hard feedback deadline.</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="28" customHeight="1">
-      <c r="A7" s="22" t="inlineStr">
+    <row r="8" ht="26" customHeight="1">
+      <c r="A8" s="36" t="n">
+        <v>5</v>
+      </c>
+      <c r="B8" s="36" t="n">
+        <v>6</v>
+      </c>
+      <c r="C8" s="36" t="n">
+        <v>7</v>
+      </c>
+      <c r="D8" s="36" t="n">
+        <v>8</v>
+      </c>
+      <c r="E8" s="36" t="n">
+        <v>9</v>
+      </c>
+      <c r="F8" s="36" t="n">
+        <v>10</v>
+      </c>
+      <c r="G8" s="36" t="n">
+        <v>11</v>
+      </c>
+      <c r="I8" s="36" t="n">
+        <v>2</v>
+      </c>
+      <c r="J8" s="36" t="n">
+        <v>3</v>
+      </c>
+      <c r="K8" s="36" t="n">
+        <v>4</v>
+      </c>
+      <c r="L8" s="36" t="n">
+        <v>5</v>
+      </c>
+      <c r="M8" s="36" t="n">
+        <v>6</v>
+      </c>
+      <c r="N8" s="36" t="n">
+        <v>7</v>
+      </c>
+      <c r="O8" s="38" t="n">
+        <v>8</v>
+      </c>
+      <c r="R8" s="33" t="inlineStr">
         <is>
           <t>27 Jul 2026</t>
         </is>
       </c>
-      <c r="B7" s="24" t="inlineStr">
+      <c r="S8" s="37" t="inlineStr">
         <is>
           <t>Supplier</t>
         </is>
       </c>
-      <c r="C7" s="22" t="inlineStr">
+      <c r="T8" s="33" t="inlineStr">
         <is>
           <t>Material scope issued to Production Partner</t>
         </is>
       </c>
-      <c r="D7" s="22" t="inlineStr">
+      <c r="U8" s="33" t="inlineStr">
         <is>
           <t>Milestone.</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="28" customHeight="1">
-      <c r="A8" s="22" t="inlineStr">
+    <row r="9" ht="26" customHeight="1">
+      <c r="A9" s="36" t="n">
+        <v>12</v>
+      </c>
+      <c r="B9" s="36" t="n">
+        <v>13</v>
+      </c>
+      <c r="C9" s="36" t="n">
+        <v>14</v>
+      </c>
+      <c r="D9" s="38" t="n">
+        <v>15</v>
+      </c>
+      <c r="E9" s="36" t="n">
+        <v>16</v>
+      </c>
+      <c r="F9" s="36" t="n">
+        <v>17</v>
+      </c>
+      <c r="G9" s="36" t="n">
+        <v>18</v>
+      </c>
+      <c r="I9" s="36" t="n">
+        <v>9</v>
+      </c>
+      <c r="J9" s="36" t="n">
+        <v>10</v>
+      </c>
+      <c r="K9" s="36" t="n">
+        <v>11</v>
+      </c>
+      <c r="L9" s="38" t="n">
+        <v>12</v>
+      </c>
+      <c r="M9" s="36" t="n">
+        <v>13</v>
+      </c>
+      <c r="N9" s="36" t="n">
+        <v>14</v>
+      </c>
+      <c r="O9" s="36" t="n">
+        <v>15</v>
+      </c>
+      <c r="R9" s="33" t="inlineStr">
         <is>
           <t>30 Jul 2026</t>
         </is>
       </c>
-      <c r="B8" s="23" t="inlineStr">
+      <c r="S9" s="34" t="inlineStr">
         <is>
           <t>Client</t>
         </is>
       </c>
-      <c r="C8" s="22" t="inlineStr">
+      <c r="T9" s="33" t="inlineStr">
         <is>
           <t>Fit-out RFI closure</t>
         </is>
       </c>
-      <c r="D8" s="22" t="inlineStr">
+      <c r="U9" s="33" t="inlineStr">
         <is>
           <t>Milestone.</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="28" customHeight="1">
-      <c r="A9" s="22" t="inlineStr">
+    <row r="10" ht="26" customHeight="1">
+      <c r="A10" s="36" t="n">
+        <v>19</v>
+      </c>
+      <c r="B10" s="36" t="n">
+        <v>20</v>
+      </c>
+      <c r="C10" s="36" t="n">
+        <v>21</v>
+      </c>
+      <c r="D10" s="38" t="n">
+        <v>22</v>
+      </c>
+      <c r="E10" s="36" t="n">
+        <v>23</v>
+      </c>
+      <c r="F10" s="36" t="n">
+        <v>24</v>
+      </c>
+      <c r="G10" s="36" t="n">
+        <v>25</v>
+      </c>
+      <c r="I10" s="36" t="n">
+        <v>16</v>
+      </c>
+      <c r="J10" s="36" t="n">
+        <v>17</v>
+      </c>
+      <c r="K10" s="36" t="n">
+        <v>18</v>
+      </c>
+      <c r="L10" s="36" t="n">
+        <v>19</v>
+      </c>
+      <c r="M10" s="36" t="n">
+        <v>20</v>
+      </c>
+      <c r="N10" s="36" t="n">
+        <v>21</v>
+      </c>
+      <c r="O10" s="36" t="n">
+        <v>22</v>
+      </c>
+      <c r="R10" s="33" t="inlineStr">
         <is>
           <t>08 Aug 2026</t>
         </is>
       </c>
-      <c r="B9" s="24" t="inlineStr">
+      <c r="S10" s="37" t="inlineStr">
         <is>
           <t>Supplier</t>
         </is>
       </c>
-      <c r="C9" s="22" t="inlineStr">
+      <c r="T10" s="33" t="inlineStr">
         <is>
           <t>Dispatch/delivery Round 1 sample box to Dubai</t>
         </is>
       </c>
-      <c r="D9" s="22" t="inlineStr">
+      <c r="U10" s="33" t="inlineStr">
         <is>
           <t>Must reach WDCO Dubai by 10 Aug.</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="28" customHeight="1">
-      <c r="A10" s="22" t="inlineStr">
+    <row r="11" ht="26" customHeight="1">
+      <c r="A11" s="36" t="n">
+        <v>26</v>
+      </c>
+      <c r="B11" s="38" t="n">
+        <v>27</v>
+      </c>
+      <c r="C11" s="36" t="n">
+        <v>28</v>
+      </c>
+      <c r="D11" s="36" t="n">
+        <v>29</v>
+      </c>
+      <c r="E11" s="38" t="n">
+        <v>30</v>
+      </c>
+      <c r="F11" s="36" t="n">
+        <v>31</v>
+      </c>
+      <c r="G11" s="35" t="n"/>
+      <c r="I11" s="36" t="n">
+        <v>23</v>
+      </c>
+      <c r="J11" s="38" t="n">
+        <v>24</v>
+      </c>
+      <c r="K11" s="36" t="n">
+        <v>25</v>
+      </c>
+      <c r="L11" s="36" t="n">
+        <v>26</v>
+      </c>
+      <c r="M11" s="36" t="n">
+        <v>27</v>
+      </c>
+      <c r="N11" s="36" t="n">
+        <v>28</v>
+      </c>
+      <c r="O11" s="36" t="n">
+        <v>29</v>
+      </c>
+      <c r="R11" s="33" t="inlineStr">
         <is>
           <t>12 Aug 2026</t>
         </is>
       </c>
-      <c r="B10" s="24" t="inlineStr">
+      <c r="S11" s="37" t="inlineStr">
         <is>
           <t>Supplier</t>
         </is>
       </c>
-      <c r="C10" s="22" t="inlineStr">
+      <c r="T11" s="33" t="inlineStr">
         <is>
           <t>Signed GFP SHD Version 02</t>
         </is>
       </c>
-      <c r="D10" s="22" t="inlineStr">
+      <c r="U11" s="33" t="inlineStr">
         <is>
           <t>Required before production release.</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="28" customHeight="1">
-      <c r="A11" s="22" t="inlineStr">
+    <row r="12" ht="26" customHeight="1">
+      <c r="I12" s="36" t="n">
+        <v>30</v>
+      </c>
+      <c r="J12" s="36" t="n">
+        <v>31</v>
+      </c>
+      <c r="K12" s="35" t="n"/>
+      <c r="L12" s="35" t="n"/>
+      <c r="M12" s="35" t="n"/>
+      <c r="N12" s="35" t="n"/>
+      <c r="O12" s="35" t="n"/>
+      <c r="R12" s="33" t="inlineStr">
         <is>
           <t>24 Aug 2026</t>
         </is>
       </c>
-      <c r="B11" s="23" t="inlineStr">
+      <c r="S12" s="34" t="inlineStr">
         <is>
           <t>Client</t>
         </is>
       </c>
-      <c r="C11" s="22" t="inlineStr">
+      <c r="T12" s="33" t="inlineStr">
         <is>
           <t>G&amp;B team availability resumes</t>
         </is>
       </c>
-      <c r="D11" s="22" t="inlineStr">
+      <c r="U12" s="33" t="inlineStr">
         <is>
           <t>Office unavailable 1-24 Aug.</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="28" customHeight="1">
-      <c r="A12" s="22" t="inlineStr">
+    <row r="13" ht="26" customHeight="1">
+      <c r="R13" s="33" t="inlineStr">
         <is>
           <t>03 Sep 2026</t>
         </is>
       </c>
-      <c r="B12" s="23" t="inlineStr">
+      <c r="S13" s="34" t="inlineStr">
         <is>
           <t>Client</t>
         </is>
       </c>
-      <c r="C12" s="22" t="inlineStr">
+      <c r="T13" s="33" t="inlineStr">
         <is>
           <t>Signed FF&amp;E SHD V02 &amp; confirmed material package</t>
         </is>
       </c>
-      <c r="D12" s="22" t="inlineStr">
+      <c r="U13" s="33" t="inlineStr">
         <is>
           <t>Production starts only after this.</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="28" customHeight="1">
-      <c r="A13" s="22" t="inlineStr">
+    <row r="14" ht="26" customHeight="1">
+      <c r="R14" s="33" t="inlineStr">
         <is>
           <t>10 Sep 2026</t>
         </is>
       </c>
-      <c r="B13" s="24" t="inlineStr">
+      <c r="S14" s="37" t="inlineStr">
         <is>
           <t>Supplier</t>
         </is>
       </c>
-      <c r="C13" s="22" t="inlineStr">
+      <c r="T14" s="33" t="inlineStr">
         <is>
           <t>Signed GFP Fit-Out SHD</t>
         </is>
       </c>
-      <c r="D13" s="22" t="inlineStr">
+      <c r="U14" s="33" t="inlineStr">
         <is>
           <t>Required before production starts.</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="28" customHeight="1">
-      <c r="A14" s="22" t="inlineStr">
+    <row r="15" ht="26" customHeight="1">
+      <c r="R15" s="33" t="inlineStr">
         <is>
           <t>16 Sep 2026</t>
         </is>
       </c>
-      <c r="B14" s="23" t="inlineStr">
+      <c r="S15" s="34" t="inlineStr">
         <is>
           <t>Client</t>
         </is>
       </c>
-      <c r="C14" s="22" t="inlineStr">
+      <c r="T15" s="33" t="inlineStr">
         <is>
           <t>Fit-out SHD V01 &amp; material-package approval</t>
         </is>
       </c>
-      <c r="D14" s="22" t="inlineStr">
+      <c r="U15" s="33" t="inlineStr">
         <is>
           <t>Final fit-out production-release gate.</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="28" customHeight="1">
-      <c r="A15" s="22" t="inlineStr">
+    <row r="16" ht="26" customHeight="1">
+      <c r="A16" s="30" t="inlineStr">
+        <is>
+          <t>SEPTEMBER 2026</t>
+        </is>
+      </c>
+      <c r="I16" s="30" t="inlineStr">
+        <is>
+          <t>OCTOBER 2026</t>
+        </is>
+      </c>
+      <c r="R16" s="33" t="inlineStr">
         <is>
           <t>25 Oct 2026</t>
         </is>
       </c>
-      <c r="B15" s="23" t="inlineStr">
+      <c r="S16" s="34" t="inlineStr">
         <is>
           <t>Client</t>
         </is>
       </c>
-      <c r="C15" s="22" t="inlineStr">
+      <c r="T16" s="33" t="inlineStr">
         <is>
           <t>Combined dispatch on next available sailing</t>
         </is>
       </c>
-      <c r="D15" s="22" t="inlineStr">
+      <c r="U16" s="33" t="inlineStr">
         <is>
           <t>Milestone.</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="28" customHeight="1">
-      <c r="A16" s="22" t="inlineStr">
+    <row r="17" ht="26" customHeight="1">
+      <c r="A17" s="32" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="B17" s="32" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="C17" s="32" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="D17" s="32" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="E17" s="32" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="F17" s="32" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="G17" s="32" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I17" s="32" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="J17" s="32" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="K17" s="32" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="L17" s="32" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="M17" s="32" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="N17" s="32" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="O17" s="32" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="R17" s="33" t="inlineStr">
         <is>
           <t>15 Nov 2026</t>
         </is>
       </c>
-      <c r="B16" s="25" t="inlineStr">
+      <c r="S17" s="39" t="inlineStr">
         <is>
           <t>WDCO Internal PM</t>
         </is>
       </c>
-      <c r="C16" s="22" t="inlineStr">
+      <c r="T17" s="33" t="inlineStr">
         <is>
           <t>Internal working deadline</t>
         </is>
       </c>
-      <c r="D16" s="22" t="inlineStr">
-        <is>
-          <t>Supplier's communicated 15 Dec hard deadline is unconfirmed; treat 15 Nov as the real internal target.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="28" customHeight="1">
-      <c r="A17" s="22" t="inlineStr">
+      <c r="U17" s="33" t="inlineStr">
+        <is>
+          <t>Supplier's 15 Dec hard deadline is unconfirmed; treat 15 Nov as the real internal target.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="26" customHeight="1">
+      <c r="A18" s="35" t="n"/>
+      <c r="B18" s="35" t="n"/>
+      <c r="C18" s="36" t="n">
+        <v>1</v>
+      </c>
+      <c r="D18" s="36" t="n">
+        <v>2</v>
+      </c>
+      <c r="E18" s="38" t="n">
+        <v>3</v>
+      </c>
+      <c r="F18" s="36" t="n">
+        <v>4</v>
+      </c>
+      <c r="G18" s="36" t="n">
+        <v>5</v>
+      </c>
+      <c r="I18" s="35" t="n"/>
+      <c r="J18" s="35" t="n"/>
+      <c r="K18" s="35" t="n"/>
+      <c r="L18" s="35" t="n"/>
+      <c r="M18" s="36" t="n">
+        <v>1</v>
+      </c>
+      <c r="N18" s="36" t="n">
+        <v>2</v>
+      </c>
+      <c r="O18" s="36" t="n">
+        <v>3</v>
+      </c>
+      <c r="R18" s="33" t="inlineStr">
         <is>
           <t>14 Dec 2026</t>
         </is>
       </c>
-      <c r="B17" s="24" t="inlineStr">
+      <c r="S18" s="37" t="inlineStr">
         <is>
           <t>Supplier</t>
         </is>
       </c>
-      <c r="C17" s="22" t="inlineStr">
+      <c r="T18" s="33" t="inlineStr">
         <is>
           <t>Ready for site inspection</t>
         </is>
       </c>
-      <c r="D17" s="22" t="inlineStr">
+      <c r="U18" s="33" t="inlineStr">
         <is>
           <t>All contracted installation complete.</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="28" customHeight="1">
-      <c r="A18" s="22" t="inlineStr">
+    <row r="19" ht="26" customHeight="1">
+      <c r="A19" s="36" t="n">
+        <v>6</v>
+      </c>
+      <c r="B19" s="36" t="n">
+        <v>7</v>
+      </c>
+      <c r="C19" s="36" t="n">
+        <v>8</v>
+      </c>
+      <c r="D19" s="36" t="n">
+        <v>9</v>
+      </c>
+      <c r="E19" s="38" t="n">
+        <v>10</v>
+      </c>
+      <c r="F19" s="36" t="n">
+        <v>11</v>
+      </c>
+      <c r="G19" s="36" t="n">
+        <v>12</v>
+      </c>
+      <c r="I19" s="36" t="n">
+        <v>4</v>
+      </c>
+      <c r="J19" s="36" t="n">
+        <v>5</v>
+      </c>
+      <c r="K19" s="36" t="n">
+        <v>6</v>
+      </c>
+      <c r="L19" s="36" t="n">
+        <v>7</v>
+      </c>
+      <c r="M19" s="36" t="n">
+        <v>8</v>
+      </c>
+      <c r="N19" s="36" t="n">
+        <v>9</v>
+      </c>
+      <c r="O19" s="36" t="n">
+        <v>10</v>
+      </c>
+      <c r="R19" s="33" t="inlineStr">
         <is>
           <t>15 Dec 2026</t>
         </is>
       </c>
-      <c r="B18" s="24" t="inlineStr">
+      <c r="S19" s="37" t="inlineStr">
         <is>
           <t>Supplier</t>
         </is>
       </c>
-      <c r="C18" s="22" t="inlineStr">
+      <c r="T19" s="33" t="inlineStr">
         <is>
           <t>Hard deadline (as communicated to supplier)</t>
         </is>
       </c>
-      <c r="D18" s="22" t="inlineStr">
+      <c r="U19" s="33" t="inlineStr">
         <is>
           <t>Tentative, not yet confirmed.</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="28" customHeight="1">
-      <c r="A19" s="22" t="inlineStr">
+    <row r="20" ht="26" customHeight="1">
+      <c r="A20" s="36" t="n">
+        <v>13</v>
+      </c>
+      <c r="B20" s="36" t="n">
+        <v>14</v>
+      </c>
+      <c r="C20" s="36" t="n">
+        <v>15</v>
+      </c>
+      <c r="D20" s="38" t="n">
+        <v>16</v>
+      </c>
+      <c r="E20" s="36" t="n">
+        <v>17</v>
+      </c>
+      <c r="F20" s="36" t="n">
+        <v>18</v>
+      </c>
+      <c r="G20" s="36" t="n">
+        <v>19</v>
+      </c>
+      <c r="I20" s="36" t="n">
+        <v>11</v>
+      </c>
+      <c r="J20" s="36" t="n">
+        <v>12</v>
+      </c>
+      <c r="K20" s="36" t="n">
+        <v>13</v>
+      </c>
+      <c r="L20" s="36" t="n">
+        <v>14</v>
+      </c>
+      <c r="M20" s="36" t="n">
+        <v>15</v>
+      </c>
+      <c r="N20" s="36" t="n">
+        <v>16</v>
+      </c>
+      <c r="O20" s="36" t="n">
+        <v>17</v>
+      </c>
+      <c r="R20" s="33" t="inlineStr">
         <is>
           <t>20 Dec 2026</t>
         </is>
       </c>
-      <c r="B19" s="23" t="inlineStr">
+      <c r="S20" s="34" t="inlineStr">
         <is>
           <t>Client</t>
         </is>
       </c>
-      <c r="C19" s="22" t="inlineStr">
+      <c r="T20" s="33" t="inlineStr">
         <is>
           <t>Complete T1B1 mock-up ready for inspection</t>
         </is>
       </c>
-      <c r="D19" s="22" t="inlineStr">
+      <c r="U20" s="33" t="inlineStr">
         <is>
           <t>Indicative revised readiness date.</t>
         </is>
       </c>
     </row>
+    <row r="21" ht="14" customHeight="1">
+      <c r="A21" s="36" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" s="36" t="n">
+        <v>21</v>
+      </c>
+      <c r="C21" s="36" t="n">
+        <v>22</v>
+      </c>
+      <c r="D21" s="36" t="n">
+        <v>23</v>
+      </c>
+      <c r="E21" s="36" t="n">
+        <v>24</v>
+      </c>
+      <c r="F21" s="36" t="n">
+        <v>25</v>
+      </c>
+      <c r="G21" s="36" t="n">
+        <v>26</v>
+      </c>
+      <c r="I21" s="36" t="n">
+        <v>18</v>
+      </c>
+      <c r="J21" s="36" t="n">
+        <v>19</v>
+      </c>
+      <c r="K21" s="36" t="n">
+        <v>20</v>
+      </c>
+      <c r="L21" s="36" t="n">
+        <v>21</v>
+      </c>
+      <c r="M21" s="36" t="n">
+        <v>22</v>
+      </c>
+      <c r="N21" s="36" t="n">
+        <v>23</v>
+      </c>
+      <c r="O21" s="36" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="22" ht="14" customHeight="1">
+      <c r="A22" s="36" t="n">
+        <v>27</v>
+      </c>
+      <c r="B22" s="36" t="n">
+        <v>28</v>
+      </c>
+      <c r="C22" s="36" t="n">
+        <v>29</v>
+      </c>
+      <c r="D22" s="36" t="n">
+        <v>30</v>
+      </c>
+      <c r="E22" s="35" t="n"/>
+      <c r="F22" s="35" t="n"/>
+      <c r="G22" s="35" t="n"/>
+      <c r="I22" s="38" t="n">
+        <v>25</v>
+      </c>
+      <c r="J22" s="36" t="n">
+        <v>26</v>
+      </c>
+      <c r="K22" s="36" t="n">
+        <v>27</v>
+      </c>
+      <c r="L22" s="36" t="n">
+        <v>28</v>
+      </c>
+      <c r="M22" s="36" t="n">
+        <v>29</v>
+      </c>
+      <c r="N22" s="36" t="n">
+        <v>30</v>
+      </c>
+      <c r="O22" s="36" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="27" ht="16" customHeight="1">
+      <c r="A27" s="30" t="inlineStr">
+        <is>
+          <t>NOVEMBER 2026</t>
+        </is>
+      </c>
+      <c r="I27" s="30" t="inlineStr">
+        <is>
+          <t>DECEMBER 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="14" customHeight="1">
+      <c r="A28" s="32" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="B28" s="32" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="C28" s="32" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="D28" s="32" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="E28" s="32" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="F28" s="32" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="G28" s="32" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I28" s="32" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="J28" s="32" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="K28" s="32" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="L28" s="32" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="M28" s="32" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="N28" s="32" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="O28" s="32" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="14" customHeight="1">
+      <c r="A29" s="36" t="n">
+        <v>1</v>
+      </c>
+      <c r="B29" s="36" t="n">
+        <v>2</v>
+      </c>
+      <c r="C29" s="36" t="n">
+        <v>3</v>
+      </c>
+      <c r="D29" s="36" t="n">
+        <v>4</v>
+      </c>
+      <c r="E29" s="36" t="n">
+        <v>5</v>
+      </c>
+      <c r="F29" s="36" t="n">
+        <v>6</v>
+      </c>
+      <c r="G29" s="36" t="n">
+        <v>7</v>
+      </c>
+      <c r="I29" s="35" t="n"/>
+      <c r="J29" s="35" t="n"/>
+      <c r="K29" s="36" t="n">
+        <v>1</v>
+      </c>
+      <c r="L29" s="36" t="n">
+        <v>2</v>
+      </c>
+      <c r="M29" s="36" t="n">
+        <v>3</v>
+      </c>
+      <c r="N29" s="36" t="n">
+        <v>4</v>
+      </c>
+      <c r="O29" s="36" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="30" ht="14" customHeight="1">
+      <c r="A30" s="36" t="n">
+        <v>8</v>
+      </c>
+      <c r="B30" s="36" t="n">
+        <v>9</v>
+      </c>
+      <c r="C30" s="36" t="n">
+        <v>10</v>
+      </c>
+      <c r="D30" s="36" t="n">
+        <v>11</v>
+      </c>
+      <c r="E30" s="36" t="n">
+        <v>12</v>
+      </c>
+      <c r="F30" s="36" t="n">
+        <v>13</v>
+      </c>
+      <c r="G30" s="36" t="n">
+        <v>14</v>
+      </c>
+      <c r="I30" s="36" t="n">
+        <v>6</v>
+      </c>
+      <c r="J30" s="36" t="n">
+        <v>7</v>
+      </c>
+      <c r="K30" s="36" t="n">
+        <v>8</v>
+      </c>
+      <c r="L30" s="36" t="n">
+        <v>9</v>
+      </c>
+      <c r="M30" s="36" t="n">
+        <v>10</v>
+      </c>
+      <c r="N30" s="36" t="n">
+        <v>11</v>
+      </c>
+      <c r="O30" s="36" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="31" ht="14" customHeight="1">
+      <c r="A31" s="38" t="n">
+        <v>15</v>
+      </c>
+      <c r="B31" s="36" t="n">
+        <v>16</v>
+      </c>
+      <c r="C31" s="36" t="n">
+        <v>17</v>
+      </c>
+      <c r="D31" s="36" t="n">
+        <v>18</v>
+      </c>
+      <c r="E31" s="36" t="n">
+        <v>19</v>
+      </c>
+      <c r="F31" s="36" t="n">
+        <v>20</v>
+      </c>
+      <c r="G31" s="36" t="n">
+        <v>21</v>
+      </c>
+      <c r="I31" s="36" t="n">
+        <v>13</v>
+      </c>
+      <c r="J31" s="38" t="n">
+        <v>14</v>
+      </c>
+      <c r="K31" s="38" t="n">
+        <v>15</v>
+      </c>
+      <c r="L31" s="36" t="n">
+        <v>16</v>
+      </c>
+      <c r="M31" s="36" t="n">
+        <v>17</v>
+      </c>
+      <c r="N31" s="36" t="n">
+        <v>18</v>
+      </c>
+      <c r="O31" s="36" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="32" ht="14" customHeight="1">
+      <c r="A32" s="36" t="n">
+        <v>22</v>
+      </c>
+      <c r="B32" s="36" t="n">
+        <v>23</v>
+      </c>
+      <c r="C32" s="36" t="n">
+        <v>24</v>
+      </c>
+      <c r="D32" s="36" t="n">
+        <v>25</v>
+      </c>
+      <c r="E32" s="36" t="n">
+        <v>26</v>
+      </c>
+      <c r="F32" s="36" t="n">
+        <v>27</v>
+      </c>
+      <c r="G32" s="36" t="n">
+        <v>28</v>
+      </c>
+      <c r="I32" s="38" t="n">
+        <v>20</v>
+      </c>
+      <c r="J32" s="36" t="n">
+        <v>21</v>
+      </c>
+      <c r="K32" s="36" t="n">
+        <v>22</v>
+      </c>
+      <c r="L32" s="36" t="n">
+        <v>23</v>
+      </c>
+      <c r="M32" s="36" t="n">
+        <v>24</v>
+      </c>
+      <c r="N32" s="36" t="n">
+        <v>25</v>
+      </c>
+      <c r="O32" s="36" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="33" ht="14" customHeight="1">
+      <c r="A33" s="36" t="n">
+        <v>29</v>
+      </c>
+      <c r="B33" s="36" t="n">
+        <v>30</v>
+      </c>
+      <c r="C33" s="35" t="n"/>
+      <c r="D33" s="35" t="n"/>
+      <c r="E33" s="35" t="n"/>
+      <c r="F33" s="35" t="n"/>
+      <c r="G33" s="35" t="n"/>
+      <c r="I33" s="36" t="n">
+        <v>27</v>
+      </c>
+      <c r="J33" s="36" t="n">
+        <v>28</v>
+      </c>
+      <c r="K33" s="36" t="n">
+        <v>29</v>
+      </c>
+      <c r="L33" s="36" t="n">
+        <v>30</v>
+      </c>
+      <c r="M33" s="36" t="n">
+        <v>31</v>
+      </c>
+      <c r="N33" s="35" t="n"/>
+      <c r="O33" s="35" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A2:D2"/>
+  <mergeCells count="12">
+    <mergeCell ref="I27:O27"/>
+    <mergeCell ref="I5:O5"/>
+    <mergeCell ref="I16:O16"/>
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A27:G27"/>
+    <mergeCell ref="A1:V1"/>
+    <mergeCell ref="K2:O2"/>
+    <mergeCell ref="A16:G16"/>
+    <mergeCell ref="P2:T2"/>
+    <mergeCell ref="A3:V3"/>
+    <mergeCell ref="A5:G5"/>
+    <mergeCell ref="F2:J2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4066,11 +7740,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:E45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="90" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="60" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
@@ -4080,30 +7757,359 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="28" customHeight="1">
+    <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Free-running narrative log. Fed by Shagun's daily '#product development' updates (date + update); Claude reflects any schedule-relevant change into the Data/month tabs at the same time an entry is added here.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+          <t xml:space="preserve">  Client</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Supplier</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  WDCO Internal PM</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Deadline (red border)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="30" customHeight="1">
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>Free-running narrative log, fed by '#projectdevelopment' entries. Category and Umbrella Task are tagged at end-of-day during #totalcheck, not necessarily live. Evidence is a hyperlink to whatever source Shagun provides (email, document, etc.), for cross-checking later.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="7" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="C5" s="7" t="inlineStr">
+        <is>
+          <t>Umbrella Task</t>
+        </is>
+      </c>
+      <c r="D5" s="7" t="inlineStr">
         <is>
           <t>Update</t>
         </is>
       </c>
+      <c r="E5" s="7" t="inlineStr">
+        <is>
+          <t>Evidence</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="40" t="n"/>
+      <c r="B6" s="40" t="n"/>
+      <c r="C6" s="40" t="n"/>
+      <c r="D6" s="40" t="n"/>
+      <c r="E6" s="40" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="40" t="n"/>
+      <c r="B7" s="40" t="n"/>
+      <c r="C7" s="40" t="n"/>
+      <c r="D7" s="40" t="n"/>
+      <c r="E7" s="40" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="40" t="n"/>
+      <c r="B8" s="40" t="n"/>
+      <c r="C8" s="40" t="n"/>
+      <c r="D8" s="40" t="n"/>
+      <c r="E8" s="40" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="40" t="n"/>
+      <c r="B9" s="40" t="n"/>
+      <c r="C9" s="40" t="n"/>
+      <c r="D9" s="40" t="n"/>
+      <c r="E9" s="40" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="40" t="n"/>
+      <c r="B10" s="40" t="n"/>
+      <c r="C10" s="40" t="n"/>
+      <c r="D10" s="40" t="n"/>
+      <c r="E10" s="40" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="40" t="n"/>
+      <c r="B11" s="40" t="n"/>
+      <c r="C11" s="40" t="n"/>
+      <c r="D11" s="40" t="n"/>
+      <c r="E11" s="40" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="40" t="n"/>
+      <c r="B12" s="40" t="n"/>
+      <c r="C12" s="40" t="n"/>
+      <c r="D12" s="40" t="n"/>
+      <c r="E12" s="40" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="40" t="n"/>
+      <c r="B13" s="40" t="n"/>
+      <c r="C13" s="40" t="n"/>
+      <c r="D13" s="40" t="n"/>
+      <c r="E13" s="40" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="40" t="n"/>
+      <c r="B14" s="40" t="n"/>
+      <c r="C14" s="40" t="n"/>
+      <c r="D14" s="40" t="n"/>
+      <c r="E14" s="40" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="40" t="n"/>
+      <c r="B15" s="40" t="n"/>
+      <c r="C15" s="40" t="n"/>
+      <c r="D15" s="40" t="n"/>
+      <c r="E15" s="40" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="40" t="n"/>
+      <c r="B16" s="40" t="n"/>
+      <c r="C16" s="40" t="n"/>
+      <c r="D16" s="40" t="n"/>
+      <c r="E16" s="40" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="40" t="n"/>
+      <c r="B17" s="40" t="n"/>
+      <c r="C17" s="40" t="n"/>
+      <c r="D17" s="40" t="n"/>
+      <c r="E17" s="40" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="40" t="n"/>
+      <c r="B18" s="40" t="n"/>
+      <c r="C18" s="40" t="n"/>
+      <c r="D18" s="40" t="n"/>
+      <c r="E18" s="40" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="40" t="n"/>
+      <c r="B19" s="40" t="n"/>
+      <c r="C19" s="40" t="n"/>
+      <c r="D19" s="40" t="n"/>
+      <c r="E19" s="40" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="40" t="n"/>
+      <c r="B20" s="40" t="n"/>
+      <c r="C20" s="40" t="n"/>
+      <c r="D20" s="40" t="n"/>
+      <c r="E20" s="40" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="40" t="n"/>
+      <c r="B21" s="40" t="n"/>
+      <c r="C21" s="40" t="n"/>
+      <c r="D21" s="40" t="n"/>
+      <c r="E21" s="40" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="40" t="n"/>
+      <c r="B22" s="40" t="n"/>
+      <c r="C22" s="40" t="n"/>
+      <c r="D22" s="40" t="n"/>
+      <c r="E22" s="40" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="40" t="n"/>
+      <c r="B23" s="40" t="n"/>
+      <c r="C23" s="40" t="n"/>
+      <c r="D23" s="40" t="n"/>
+      <c r="E23" s="40" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="40" t="n"/>
+      <c r="B24" s="40" t="n"/>
+      <c r="C24" s="40" t="n"/>
+      <c r="D24" s="40" t="n"/>
+      <c r="E24" s="40" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="40" t="n"/>
+      <c r="B25" s="40" t="n"/>
+      <c r="C25" s="40" t="n"/>
+      <c r="D25" s="40" t="n"/>
+      <c r="E25" s="40" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="40" t="n"/>
+      <c r="B26" s="40" t="n"/>
+      <c r="C26" s="40" t="n"/>
+      <c r="D26" s="40" t="n"/>
+      <c r="E26" s="40" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="40" t="n"/>
+      <c r="B27" s="40" t="n"/>
+      <c r="C27" s="40" t="n"/>
+      <c r="D27" s="40" t="n"/>
+      <c r="E27" s="40" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="40" t="n"/>
+      <c r="B28" s="40" t="n"/>
+      <c r="C28" s="40" t="n"/>
+      <c r="D28" s="40" t="n"/>
+      <c r="E28" s="40" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="40" t="n"/>
+      <c r="B29" s="40" t="n"/>
+      <c r="C29" s="40" t="n"/>
+      <c r="D29" s="40" t="n"/>
+      <c r="E29" s="40" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="40" t="n"/>
+      <c r="B30" s="40" t="n"/>
+      <c r="C30" s="40" t="n"/>
+      <c r="D30" s="40" t="n"/>
+      <c r="E30" s="40" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="40" t="n"/>
+      <c r="B31" s="40" t="n"/>
+      <c r="C31" s="40" t="n"/>
+      <c r="D31" s="40" t="n"/>
+      <c r="E31" s="40" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="40" t="n"/>
+      <c r="B32" s="40" t="n"/>
+      <c r="C32" s="40" t="n"/>
+      <c r="D32" s="40" t="n"/>
+      <c r="E32" s="40" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="40" t="n"/>
+      <c r="B33" s="40" t="n"/>
+      <c r="C33" s="40" t="n"/>
+      <c r="D33" s="40" t="n"/>
+      <c r="E33" s="40" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="40" t="n"/>
+      <c r="B34" s="40" t="n"/>
+      <c r="C34" s="40" t="n"/>
+      <c r="D34" s="40" t="n"/>
+      <c r="E34" s="40" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="40" t="n"/>
+      <c r="B35" s="40" t="n"/>
+      <c r="C35" s="40" t="n"/>
+      <c r="D35" s="40" t="n"/>
+      <c r="E35" s="40" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="40" t="n"/>
+      <c r="B36" s="40" t="n"/>
+      <c r="C36" s="40" t="n"/>
+      <c r="D36" s="40" t="n"/>
+      <c r="E36" s="40" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="40" t="n"/>
+      <c r="B37" s="40" t="n"/>
+      <c r="C37" s="40" t="n"/>
+      <c r="D37" s="40" t="n"/>
+      <c r="E37" s="40" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="40" t="n"/>
+      <c r="B38" s="40" t="n"/>
+      <c r="C38" s="40" t="n"/>
+      <c r="D38" s="40" t="n"/>
+      <c r="E38" s="40" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="40" t="n"/>
+      <c r="B39" s="40" t="n"/>
+      <c r="C39" s="40" t="n"/>
+      <c r="D39" s="40" t="n"/>
+      <c r="E39" s="40" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="40" t="n"/>
+      <c r="B40" s="40" t="n"/>
+      <c r="C40" s="40" t="n"/>
+      <c r="D40" s="40" t="n"/>
+      <c r="E40" s="40" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="40" t="n"/>
+      <c r="B41" s="40" t="n"/>
+      <c r="C41" s="40" t="n"/>
+      <c r="D41" s="40" t="n"/>
+      <c r="E41" s="40" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="40" t="n"/>
+      <c r="B42" s="40" t="n"/>
+      <c r="C42" s="40" t="n"/>
+      <c r="D42" s="40" t="n"/>
+      <c r="E42" s="40" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="40" t="n"/>
+      <c r="B43" s="40" t="n"/>
+      <c r="C43" s="40" t="n"/>
+      <c r="D43" s="40" t="n"/>
+      <c r="E43" s="40" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="40" t="n"/>
+      <c r="B44" s="40" t="n"/>
+      <c r="C44" s="40" t="n"/>
+      <c r="D44" s="40" t="n"/>
+      <c r="E44" s="40" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="40" t="n"/>
+      <c r="B45" s="40" t="n"/>
+      <c r="C45" s="40" t="n"/>
+      <c r="D45" s="40" t="n"/>
+      <c r="E45" s="40" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="A1:B1"/>
+  <mergeCells count="6">
+    <mergeCell ref="B2"/>
+    <mergeCell ref="A2"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="D2"/>
+    <mergeCell ref="C2"/>
+    <mergeCell ref="A3:E3"/>
   </mergeCells>
+  <dataValidations count="2">
+    <dataValidation sqref="B6:B45" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Client,Supplier,WDCO Internal PM"</formula1>
+    </dataValidation>
+    <dataValidation sqref="C6:C45" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Project Scope,Project Schedule,Compliance Collection,FFE SHD,Material Package FFE,Material Package Fitout,Specifications from client,RFI - Client, Internal, Production Partner,Fitout SHD,COC Management,Communication Management - Internal, Production Partner, Client,Site Survey Planning"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/260729_K5M_Project Calendar.xlsx
+++ b/260729_K5M_Project Calendar.xlsx
@@ -27,7 +27,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="11">
+  <fonts count="12">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -93,6 +93,12 @@
       <color rgb="00E4572E"/>
       <sz val="7"/>
     </font>
+    <font>
+      <name val="Lato"/>
+      <color rgb="00292B2B"/>
+      <sz val="9"/>
+      <u val="single"/>
+    </font>
   </fonts>
   <fills count="12">
     <fill>
@@ -152,7 +158,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="7">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -232,11 +238,55 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thick">
+        <color rgb="00E4572E"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thick">
+        <color rgb="00E4572E"/>
+      </right>
+      <top style="thick">
+        <color rgb="00E4572E"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thick">
+        <color rgb="00E4572E"/>
+      </right>
+      <top style="thick">
+        <color rgb="00E4572E"/>
+      </top>
+      <bottom style="thick">
+        <color rgb="00E4572E"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thick">
+        <color rgb="00E4572E"/>
+      </top>
+      <bottom style="thick">
+        <color rgb="00E4572E"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -338,6 +388,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -745,6 +798,7 @@
           <t xml:space="preserve">  Deadline (red border)</t>
         </is>
       </c>
+      <c r="H2" s="41" t="n"/>
     </row>
     <row r="3" ht="26" customHeight="1">
       <c r="A3" s="6" t="inlineStr">
@@ -2845,9 +2899,9 @@
           <t>⚑ SHD V00 parallel review &amp; feedback</t>
         </is>
       </c>
-      <c r="E28" s="17" t="n"/>
-      <c r="F28" s="17" t="n"/>
-      <c r="G28" s="18" t="n"/>
+      <c r="E28" s="42" t="n"/>
+      <c r="F28" s="42" t="n"/>
+      <c r="G28" s="41" t="n"/>
     </row>
     <row r="29" ht="34" customHeight="1">
       <c r="A29" s="14" t="n"/>
@@ -2941,8 +2995,8 @@
           <t>⚑ SHD V00 parallel review &amp; feedback</t>
         </is>
       </c>
-      <c r="B35" s="17" t="n"/>
-      <c r="C35" s="18" t="n"/>
+      <c r="B35" s="42" t="n"/>
+      <c r="C35" s="41" t="n"/>
       <c r="D35" s="21" t="inlineStr">
         <is>
           <t>SHD V01 drafting and issue</t>
@@ -3154,8 +3208,8 @@
           <t>⚑ SHD V00 parallel review &amp; feedback</t>
         </is>
       </c>
-      <c r="B7" s="17" t="n"/>
-      <c r="C7" s="18" t="n"/>
+      <c r="B7" s="42" t="n"/>
+      <c r="C7" s="41" t="n"/>
       <c r="D7" s="21" t="inlineStr">
         <is>
           <t>SHD V01 drafting and issue</t>
@@ -3424,9 +3478,9 @@
           <t>⚑ Signed GFP SHD Version 02</t>
         </is>
       </c>
-      <c r="E22" s="17" t="n"/>
-      <c r="F22" s="17" t="n"/>
-      <c r="G22" s="18" t="n"/>
+      <c r="E22" s="42" t="n"/>
+      <c r="F22" s="42" t="n"/>
+      <c r="G22" s="41" t="n"/>
     </row>
     <row r="23" ht="34" customHeight="1">
       <c r="A23" s="20" t="inlineStr">
@@ -3434,7 +3488,7 @@
           <t>⚑ Dispatch/delivery Round 1 sample box to Dubai</t>
         </is>
       </c>
-      <c r="B23" s="18" t="n"/>
+      <c r="B23" s="41" t="n"/>
       <c r="C23" s="21" t="inlineStr">
         <is>
           <t>Feedback round &amp; final approved material box</t>
@@ -3527,12 +3581,12 @@
           <t>⚑ Signed GFP SHD Version 02</t>
         </is>
       </c>
-      <c r="B28" s="17" t="n"/>
-      <c r="C28" s="17" t="n"/>
-      <c r="D28" s="17" t="n"/>
-      <c r="E28" s="17" t="n"/>
-      <c r="F28" s="17" t="n"/>
-      <c r="G28" s="18" t="n"/>
+      <c r="B28" s="42" t="n"/>
+      <c r="C28" s="42" t="n"/>
+      <c r="D28" s="42" t="n"/>
+      <c r="E28" s="42" t="n"/>
+      <c r="F28" s="42" t="n"/>
+      <c r="G28" s="41" t="n"/>
     </row>
     <row r="29" ht="34" customHeight="1">
       <c r="A29" s="16" t="inlineStr">
@@ -3638,12 +3692,12 @@
           <t>⚑ Signed GFP SHD Version 02</t>
         </is>
       </c>
-      <c r="B35" s="17" t="n"/>
-      <c r="C35" s="17" t="n"/>
-      <c r="D35" s="17" t="n"/>
-      <c r="E35" s="17" t="n"/>
-      <c r="F35" s="17" t="n"/>
-      <c r="G35" s="18" t="n"/>
+      <c r="B35" s="42" t="n"/>
+      <c r="C35" s="42" t="n"/>
+      <c r="D35" s="42" t="n"/>
+      <c r="E35" s="42" t="n"/>
+      <c r="F35" s="42" t="n"/>
+      <c r="G35" s="41" t="n"/>
     </row>
     <row r="36" ht="34" customHeight="1">
       <c r="A36" s="14" t="n"/>
@@ -3737,12 +3791,12 @@
           <t>⚑ Signed GFP SHD Version 02</t>
         </is>
       </c>
-      <c r="B42" s="17" t="n"/>
-      <c r="C42" s="17" t="n"/>
-      <c r="D42" s="17" t="n"/>
-      <c r="E42" s="17" t="n"/>
-      <c r="F42" s="17" t="n"/>
-      <c r="G42" s="18" t="n"/>
+      <c r="B42" s="42" t="n"/>
+      <c r="C42" s="42" t="n"/>
+      <c r="D42" s="42" t="n"/>
+      <c r="E42" s="42" t="n"/>
+      <c r="F42" s="42" t="n"/>
+      <c r="G42" s="41" t="n"/>
     </row>
     <row r="43" ht="34" customHeight="1">
       <c r="A43" s="24" t="inlineStr">
@@ -3771,8 +3825,8 @@
           <t>⚑ Signed FF&amp;E SHD V02 &amp; confirmed material package</t>
         </is>
       </c>
-      <c r="F44" s="17" t="n"/>
-      <c r="G44" s="18" t="n"/>
+      <c r="F44" s="42" t="n"/>
+      <c r="G44" s="41" t="n"/>
     </row>
     <row r="45" ht="34" customHeight="1">
       <c r="A45" s="14" t="n"/>
@@ -3991,12 +4045,12 @@
           <t>⚑ Signed GFP SHD Version 02</t>
         </is>
       </c>
-      <c r="B7" s="17" t="n"/>
-      <c r="C7" s="17" t="n"/>
-      <c r="D7" s="17" t="n"/>
-      <c r="E7" s="17" t="n"/>
-      <c r="F7" s="17" t="n"/>
-      <c r="G7" s="18" t="n"/>
+      <c r="B7" s="42" t="n"/>
+      <c r="C7" s="42" t="n"/>
+      <c r="D7" s="42" t="n"/>
+      <c r="E7" s="42" t="n"/>
+      <c r="F7" s="42" t="n"/>
+      <c r="G7" s="41" t="n"/>
     </row>
     <row r="8" ht="34" customHeight="1">
       <c r="A8" s="24" t="inlineStr">
@@ -4025,8 +4079,8 @@
           <t>⚑ Signed FF&amp;E SHD V02 &amp; confirmed material package</t>
         </is>
       </c>
-      <c r="F9" s="17" t="n"/>
-      <c r="G9" s="18" t="n"/>
+      <c r="F9" s="42" t="n"/>
+      <c r="G9" s="41" t="n"/>
     </row>
     <row r="10" ht="34" customHeight="1">
       <c r="A10" s="14" t="n"/>
@@ -4139,10 +4193,10 @@
           <t>⚑ Signed GFP SHD Version 02</t>
         </is>
       </c>
-      <c r="B15" s="17" t="n"/>
-      <c r="C15" s="17" t="n"/>
-      <c r="D15" s="17" t="n"/>
-      <c r="E15" s="18" t="n"/>
+      <c r="B15" s="42" t="n"/>
+      <c r="C15" s="42" t="n"/>
+      <c r="D15" s="42" t="n"/>
+      <c r="E15" s="41" t="n"/>
       <c r="F15" s="19" t="inlineStr">
         <is>
           <t>Send project update to internal WDCO K5M group</t>
@@ -4169,8 +4223,8 @@
           <t>⚑ Signed FF&amp;E SHD V02 &amp; confirmed material package</t>
         </is>
       </c>
-      <c r="B17" s="17" t="n"/>
-      <c r="C17" s="18" t="n"/>
+      <c r="B17" s="42" t="n"/>
+      <c r="C17" s="41" t="n"/>
       <c r="D17" s="16" t="inlineStr">
         <is>
           <t>FF&amp;E mock-up production, QC and packing</t>
@@ -4282,9 +4336,9 @@
           <t>⚑ Fit-out SHD V01 &amp; material-package approval</t>
         </is>
       </c>
-      <c r="E23" s="17" t="n"/>
-      <c r="F23" s="17" t="n"/>
-      <c r="G23" s="18" t="n"/>
+      <c r="E23" s="42" t="n"/>
+      <c r="F23" s="42" t="n"/>
+      <c r="G23" s="41" t="n"/>
     </row>
     <row r="24" ht="34" customHeight="1">
       <c r="A24" s="24" t="inlineStr">
@@ -4398,7 +4452,7 @@
           <t>⚑ Fit-out SHD V01 &amp; material-package approval</t>
         </is>
       </c>
-      <c r="B30" s="18" t="n"/>
+      <c r="B30" s="41" t="n"/>
       <c r="C30" s="16" t="inlineStr">
         <is>
           <t>Fit-out production, QC and packing</t>
@@ -6512,6 +6566,10 @@
           <t xml:space="preserve">  Deadline (red border)</t>
         </is>
       </c>
+      <c r="Q2" s="42" t="n"/>
+      <c r="R2" s="42" t="n"/>
+      <c r="S2" s="42" t="n"/>
+      <c r="T2" s="41" t="n"/>
     </row>
     <row r="3" ht="26" customHeight="1">
       <c r="A3" s="6" t="inlineStr">
@@ -7814,53 +7872,177 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="40" t="n"/>
-      <c r="B6" s="40" t="n"/>
-      <c r="C6" s="40" t="n"/>
-      <c r="D6" s="40" t="n"/>
-      <c r="E6" s="40" t="n"/>
+      <c r="A6" s="40" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B6" s="40" t="inlineStr">
+        <is>
+          <t>Client</t>
+        </is>
+      </c>
+      <c r="C6" s="40" t="inlineStr">
+        <is>
+          <t>COMM-C</t>
+        </is>
+      </c>
+      <c r="D6" s="40" t="inlineStr">
+        <is>
+          <t>Sent full Material Package email to G&amp;B, covering both FFE and Fitout.</t>
+        </is>
+      </c>
+      <c r="E6" s="43" t="inlineStr">
+        <is>
+          <t>Link</t>
+        </is>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="40" t="n"/>
-      <c r="B7" s="40" t="n"/>
-      <c r="C7" s="40" t="n"/>
-      <c r="D7" s="40" t="n"/>
+      <c r="A7" s="40" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B7" s="40" t="inlineStr">
+        <is>
+          <t>WDCO Internal PM</t>
+        </is>
+      </c>
+      <c r="C7" s="40" t="inlineStr">
+        <is>
+          <t>WIPM</t>
+        </is>
+      </c>
+      <c r="D7" s="40" t="inlineStr">
+        <is>
+          <t>Project Calendar built (v1 + v2) — only aesthetic alignment left.</t>
+        </is>
+      </c>
       <c r="E7" s="40" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="40" t="n"/>
-      <c r="B8" s="40" t="n"/>
-      <c r="C8" s="40" t="n"/>
-      <c r="D8" s="40" t="n"/>
-      <c r="E8" s="40" t="n"/>
+      <c r="A8" s="40" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B8" s="40" t="inlineStr">
+        <is>
+          <t>Client</t>
+        </is>
+      </c>
+      <c r="C8" s="40" t="inlineStr">
+        <is>
+          <t>RFI-C</t>
+        </is>
+      </c>
+      <c r="D8" s="40" t="inlineStr">
+        <is>
+          <t>Raised an RFI with the client regarding a high-resolution picture of GL-8.</t>
+        </is>
+      </c>
+      <c r="E8" s="43" t="inlineStr">
+        <is>
+          <t>Link</t>
+        </is>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" s="40" t="n"/>
-      <c r="B9" s="40" t="n"/>
-      <c r="C9" s="40" t="n"/>
-      <c r="D9" s="40" t="n"/>
-      <c r="E9" s="40" t="n"/>
+      <c r="A9" s="40" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B9" s="40" t="inlineStr">
+        <is>
+          <t>Client</t>
+        </is>
+      </c>
+      <c r="C9" s="40" t="inlineStr">
+        <is>
+          <t>FOSHD</t>
+        </is>
+      </c>
+      <c r="D9" s="40" t="inlineStr">
+        <is>
+          <t>Adil (architect) sent the DWG file of the entrance door.</t>
+        </is>
+      </c>
+      <c r="E9" s="43" t="inlineStr">
+        <is>
+          <t>Link</t>
+        </is>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" s="40" t="n"/>
-      <c r="B10" s="40" t="n"/>
-      <c r="C10" s="40" t="n"/>
-      <c r="D10" s="40" t="n"/>
+      <c r="A10" s="40" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B10" s="40" t="inlineStr">
+        <is>
+          <t>Client</t>
+        </is>
+      </c>
+      <c r="C10" s="40" t="inlineStr">
+        <is>
+          <t>WIPM</t>
+        </is>
+      </c>
+      <c r="D10" s="40" t="inlineStr">
+        <is>
+          <t>New lighting designer introduced; details to be updated in CONTACT_SHEET.md once confirmed.</t>
+        </is>
+      </c>
       <c r="E10" s="40" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="40" t="n"/>
-      <c r="B11" s="40" t="n"/>
-      <c r="C11" s="40" t="n"/>
-      <c r="D11" s="40" t="n"/>
+      <c r="A11" s="40" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B11" s="40" t="inlineStr">
+        <is>
+          <t>WDCO Internal PM</t>
+        </is>
+      </c>
+      <c r="C11" s="40" t="inlineStr"/>
+      <c r="D11" s="40" t="inlineStr">
+        <is>
+          <t>Meeting with Claire held — MoM to follow tomorrow.</t>
+        </is>
+      </c>
       <c r="E11" s="40" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="40" t="n"/>
-      <c r="B12" s="40" t="n"/>
-      <c r="C12" s="40" t="n"/>
-      <c r="D12" s="40" t="n"/>
-      <c r="E12" s="40" t="n"/>
+      <c r="A12" s="40" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B12" s="40" t="inlineStr">
+        <is>
+          <t>Client</t>
+        </is>
+      </c>
+      <c r="C12" s="40" t="inlineStr">
+        <is>
+          <t>FOSHD</t>
+        </is>
+      </c>
+      <c r="D12" s="40" t="inlineStr">
+        <is>
+          <t>Closed fit-out RFIs with assigned actions; informed the client, will branch out further via email.</t>
+        </is>
+      </c>
+      <c r="E12" s="43" t="inlineStr">
+        <is>
+          <t>Link</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="40" t="n"/>
@@ -8110,6 +8292,12 @@
       <formula1>"Project Scope,Project Schedule,Compliance Collection,FFE SHD,Material Package FFE,Material Package Fitout,Specifications from client,RFI - Client, Internal, Production Partner,Fitout SHD,COC Management,Communication Management - Internal, Production Partner, Client,Site Survey Planning"</formula1>
     </dataValidation>
   </dataValidations>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E6" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E8" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E9" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E12" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/260729_K5M_Project Calendar.xlsx
+++ b/260729_K5M_Project Calendar.xlsx
@@ -756,7 +756,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I53"/>
+  <dimension ref="A1:I54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2449,6 +2449,37 @@
           <t>2026-12-31</t>
         </is>
       </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B54" s="8" t="inlineStr"/>
+      <c r="C54" s="8" t="inlineStr">
+        <is>
+          <t>Client</t>
+        </is>
+      </c>
+      <c r="D54" s="8" t="inlineStr">
+        <is>
+          <t>RFI with lighting designer must be closed</t>
+        </is>
+      </c>
+      <c r="E54" s="8" t="inlineStr">
+        <is>
+          <t>Raised 30 Jul 2026.</t>
+        </is>
+      </c>
+      <c r="F54" s="8" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G54" s="8" t="inlineStr"/>
+      <c r="H54" s="8" t="inlineStr"/>
+      <c r="I54" s="8" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A5:I53"/>
@@ -3372,7 +3403,11 @@
       <c r="B16" s="18" t="n"/>
       <c r="C16" s="14" t="n"/>
       <c r="D16" s="14" t="n"/>
-      <c r="E16" s="14" t="n"/>
+      <c r="E16" s="15" t="inlineStr">
+        <is>
+          <t>⚑ RFI with lighting designer due</t>
+        </is>
+      </c>
       <c r="F16" s="19" t="inlineStr">
         <is>
           <t>Send project update to internal WDCO K5M group</t>
@@ -6782,7 +6817,7 @@
       <c r="L8" s="36" t="n">
         <v>5</v>
       </c>
-      <c r="M8" s="36" t="n">
+      <c r="M8" s="38" t="n">
         <v>6</v>
       </c>
       <c r="N8" s="36" t="n">
@@ -7405,7 +7440,7 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="14" customHeight="1">
+    <row r="21" ht="26" customHeight="1">
       <c r="A21" s="36" t="n">
         <v>20</v>
       </c>
@@ -7447,6 +7482,26 @@
       </c>
       <c r="O21" s="36" t="n">
         <v>24</v>
+      </c>
+      <c r="R21" s="33" t="inlineStr">
+        <is>
+          <t>06 Aug 2026</t>
+        </is>
+      </c>
+      <c r="S21" s="34" t="inlineStr">
+        <is>
+          <t>Client</t>
+        </is>
+      </c>
+      <c r="T21" s="33" t="inlineStr">
+        <is>
+          <t>RFI with lighting designer must be closed</t>
+        </is>
+      </c>
+      <c r="U21" s="33" t="inlineStr">
+        <is>
+          <t>Raised 30 Jul 2026.</t>
+        </is>
       </c>
     </row>
     <row r="22" ht="14" customHeight="1">
@@ -8045,17 +8100,49 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="40" t="n"/>
-      <c r="B13" s="40" t="n"/>
-      <c r="C13" s="40" t="n"/>
-      <c r="D13" s="40" t="n"/>
+      <c r="A13" s="40" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B13" s="40" t="inlineStr">
+        <is>
+          <t>Client</t>
+        </is>
+      </c>
+      <c r="C13" s="40" t="inlineStr">
+        <is>
+          <t>Communication Management - Client</t>
+        </is>
+      </c>
+      <c r="D13" s="40" t="inlineStr">
+        <is>
+          <t>Sent introduction email to the new lighting designer.</t>
+        </is>
+      </c>
       <c r="E13" s="40" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="40" t="n"/>
-      <c r="B14" s="40" t="n"/>
-      <c r="C14" s="40" t="n"/>
-      <c r="D14" s="40" t="n"/>
+      <c r="A14" s="40" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B14" s="40" t="inlineStr">
+        <is>
+          <t>Client</t>
+        </is>
+      </c>
+      <c r="C14" s="40" t="inlineStr">
+        <is>
+          <t>RFI - Client</t>
+        </is>
+      </c>
+      <c r="D14" s="40" t="inlineStr">
+        <is>
+          <t>Raised a new RFI with the lighting designer — must close by 6 Aug 2026.</t>
+        </is>
+      </c>
       <c r="E14" s="40" t="n"/>
     </row>
     <row r="15">

--- a/260729_K5M_Project Calendar.xlsx
+++ b/260729_K5M_Project Calendar.xlsx
@@ -8146,11 +8146,31 @@
       <c r="E14" s="40" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="40" t="n"/>
-      <c r="B15" s="40" t="n"/>
-      <c r="C15" s="40" t="n"/>
-      <c r="D15" s="40" t="n"/>
-      <c r="E15" s="40" t="n"/>
+      <c r="A15" s="40" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B15" s="40" t="inlineStr">
+        <is>
+          <t>Client</t>
+        </is>
+      </c>
+      <c r="C15" s="40" t="inlineStr">
+        <is>
+          <t>RFI - Client</t>
+        </is>
+      </c>
+      <c r="D15" s="40" t="inlineStr">
+        <is>
+          <t>Sent lighting designer (Gisela Steiger) a full status update on both scopes, referencing the still-open FF&amp;E lighting RFI directly.</t>
+        </is>
+      </c>
+      <c r="E15" s="43" t="inlineStr">
+        <is>
+          <t>Link</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="40" t="n"/>
@@ -8384,6 +8404,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E8" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E9" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E12" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E15" r:id="rId5"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/260729_K5M_Project Calendar.xlsx
+++ b/260729_K5M_Project Calendar.xlsx
@@ -756,7 +756,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I54"/>
+  <dimension ref="A1:I55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2480,6 +2480,37 @@
       <c r="G54" s="8" t="inlineStr"/>
       <c r="H54" s="8" t="inlineStr"/>
       <c r="I54" s="8" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B55" s="8" t="inlineStr"/>
+      <c r="C55" s="8" t="inlineStr">
+        <is>
+          <t>Client</t>
+        </is>
+      </c>
+      <c r="D55" s="8" t="inlineStr">
+        <is>
+          <t>BOQ scope gap meeting — all stakeholders</t>
+        </is>
+      </c>
+      <c r="E55" s="8" t="inlineStr">
+        <is>
+          <t>Agenda: stone arch/wardrobe/fitted sofa, suspended glass light over basin, hardware &amp; bathroom fittings.</t>
+        </is>
+      </c>
+      <c r="F55" s="8" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G55" s="8" t="inlineStr"/>
+      <c r="H55" s="8" t="inlineStr"/>
+      <c r="I55" s="8" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A5:I53"/>
@@ -3430,7 +3461,11 @@
     </row>
     <row r="18" ht="34" customHeight="1">
       <c r="A18" s="14" t="n"/>
-      <c r="B18" s="14" t="n"/>
+      <c r="B18" s="15" t="inlineStr">
+        <is>
+          <t>⚑ BOQ scope gap meeting</t>
+        </is>
+      </c>
       <c r="C18" s="14" t="n"/>
       <c r="D18" s="14" t="n"/>
       <c r="E18" s="14" t="n"/>
@@ -6808,7 +6843,7 @@
       <c r="I8" s="36" t="n">
         <v>2</v>
       </c>
-      <c r="J8" s="36" t="n">
+      <c r="J8" s="38" t="n">
         <v>3</v>
       </c>
       <c r="K8" s="36" t="n">
@@ -7504,7 +7539,7 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="14" customHeight="1">
+    <row r="22" ht="26" customHeight="1">
       <c r="A22" s="36" t="n">
         <v>27</v>
       </c>
@@ -7540,6 +7575,26 @@
       </c>
       <c r="O22" s="36" t="n">
         <v>31</v>
+      </c>
+      <c r="R22" s="33" t="inlineStr">
+        <is>
+          <t>03 Aug 2026</t>
+        </is>
+      </c>
+      <c r="S22" s="34" t="inlineStr">
+        <is>
+          <t>Client</t>
+        </is>
+      </c>
+      <c r="T22" s="33" t="inlineStr">
+        <is>
+          <t>BOQ scope gap meeting — all stakeholders</t>
+        </is>
+      </c>
+      <c r="U22" s="33" t="inlineStr">
+        <is>
+          <t>Agenda: see meetings/260803_K5M_Meeting_BOQ_Scope_Gap.</t>
+        </is>
       </c>
     </row>
     <row r="27" ht="16" customHeight="1">
@@ -8173,10 +8228,26 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="40" t="n"/>
-      <c r="B16" s="40" t="n"/>
-      <c r="C16" s="40" t="n"/>
-      <c r="D16" s="40" t="n"/>
+      <c r="A16" s="40" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B16" s="40" t="inlineStr">
+        <is>
+          <t>Client</t>
+        </is>
+      </c>
+      <c r="C16" s="40" t="inlineStr">
+        <is>
+          <t>Project Scope</t>
+        </is>
+      </c>
+      <c r="D16" s="40" t="inlineStr">
+        <is>
+          <t>BOQ scope gap meeting confirmed for Monday 3 Aug — agenda: stone arch over wardrobe/fitted sofa, suspended glass light over basin, hardware &amp; bathroom fittings.</t>
+        </is>
+      </c>
       <c r="E16" s="40" t="n"/>
     </row>
     <row r="17">

--- a/260729_K5M_Project Calendar.xlsx
+++ b/260729_K5M_Project Calendar.xlsx
@@ -7994,7 +7994,7 @@
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>COMM-C</t>
+          <t>Communication Management - Client</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
@@ -8021,7 +8021,7 @@
       </c>
       <c r="C7" s="40" t="inlineStr">
         <is>
-          <t>WIPM</t>
+          <t>WDCO Internal Project Management</t>
         </is>
       </c>
       <c r="D7" s="40" t="inlineStr">
@@ -8044,7 +8044,7 @@
       </c>
       <c r="C8" s="40" t="inlineStr">
         <is>
-          <t>RFI-C</t>
+          <t>RFI - Client</t>
         </is>
       </c>
       <c r="D8" s="40" t="inlineStr">
@@ -8071,7 +8071,7 @@
       </c>
       <c r="C9" s="40" t="inlineStr">
         <is>
-          <t>FOSHD</t>
+          <t>Fitout SHD</t>
         </is>
       </c>
       <c r="D9" s="40" t="inlineStr">
@@ -8098,7 +8098,7 @@
       </c>
       <c r="C10" s="40" t="inlineStr">
         <is>
-          <t>WIPM</t>
+          <t>WDCO Internal Project Management</t>
         </is>
       </c>
       <c r="D10" s="40" t="inlineStr">
@@ -8140,7 +8140,7 @@
       </c>
       <c r="C12" s="40" t="inlineStr">
         <is>
-          <t>FOSHD</t>
+          <t>Fitout SHD</t>
         </is>
       </c>
       <c r="D12" s="40" t="inlineStr">
@@ -8251,38 +8251,118 @@
       <c r="E16" s="40" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="40" t="n"/>
-      <c r="B17" s="40" t="n"/>
-      <c r="C17" s="40" t="n"/>
-      <c r="D17" s="40" t="n"/>
+      <c r="A17" s="40" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B17" s="40" t="inlineStr">
+        <is>
+          <t>Supplier</t>
+        </is>
+      </c>
+      <c r="C17" s="40" t="inlineStr">
+        <is>
+          <t>Material Package FFE</t>
+        </is>
+      </c>
+      <c r="D17" s="40" t="inlineStr">
+        <is>
+          <t>H&amp;T followed up on the Material Package — confirmed today's review meeting at 10am to go through it together.</t>
+        </is>
+      </c>
       <c r="E17" s="40" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="40" t="n"/>
-      <c r="B18" s="40" t="n"/>
-      <c r="C18" s="40" t="n"/>
-      <c r="D18" s="40" t="n"/>
+      <c r="A18" s="40" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B18" s="40" t="inlineStr">
+        <is>
+          <t>Client</t>
+        </is>
+      </c>
+      <c r="C18" s="40" t="inlineStr">
+        <is>
+          <t>Material Package Fitout</t>
+        </is>
+      </c>
+      <c r="D18" s="40" t="inlineStr">
+        <is>
+          <t>Valentine (design team) emailed confirming she's clear on the material package and asked for sample photos if possible. Will try to resolve this in today's H&amp;T meeting; if not, will reply to her directly by 1pm today.</t>
+        </is>
+      </c>
       <c r="E18" s="40" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="40" t="n"/>
-      <c r="B19" s="40" t="n"/>
-      <c r="C19" s="40" t="n"/>
-      <c r="D19" s="40" t="n"/>
+      <c r="A19" s="40" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B19" s="40" t="inlineStr">
+        <is>
+          <t>WDCO Internal PM</t>
+        </is>
+      </c>
+      <c r="C19" s="40" t="inlineStr">
+        <is>
+          <t>WDCO Internal Project Management</t>
+        </is>
+      </c>
+      <c r="D19" s="40" t="inlineStr">
+        <is>
+          <t>Started work on the Google SketchUp model for the project briefing.</t>
+        </is>
+      </c>
       <c r="E19" s="40" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="40" t="n"/>
-      <c r="B20" s="40" t="n"/>
-      <c r="C20" s="40" t="n"/>
-      <c r="D20" s="40" t="n"/>
+      <c r="A20" s="40" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B20" s="40" t="inlineStr">
+        <is>
+          <t>WDCO Internal PM</t>
+        </is>
+      </c>
+      <c r="C20" s="40" t="inlineStr">
+        <is>
+          <t>Project Scope</t>
+        </is>
+      </c>
+      <c r="D20" s="40" t="inlineStr">
+        <is>
+          <t>Drafted a basic agenda for the BOQ scope gap meeting (Monday, 3 Aug) — alongside the formal agenda doc already prepared and stored in the project management folder.</t>
+        </is>
+      </c>
       <c r="E20" s="40" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="40" t="n"/>
-      <c r="B21" s="40" t="n"/>
-      <c r="C21" s="40" t="n"/>
-      <c r="D21" s="40" t="n"/>
+      <c r="A21" s="40" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B21" s="40" t="inlineStr">
+        <is>
+          <t>Supplier</t>
+        </is>
+      </c>
+      <c r="C21" s="40" t="inlineStr">
+        <is>
+          <t>Fitout SHD</t>
+        </is>
+      </c>
+      <c r="D21" s="40" t="inlineStr">
+        <is>
+          <t>Sent Ariel all details for the fit-out drawings; Claire has asked to pause this, as a new team joinee starts Monday (3 Aug) — will assess whether he can take this on before deciding who owns the work.</t>
+        </is>
+      </c>
       <c r="E21" s="40" t="n"/>
     </row>
     <row r="22">

--- a/260729_K5M_Project Calendar.xlsx
+++ b/260729_K5M_Project Calendar.xlsx
@@ -27,7 +27,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="12">
+  <fonts count="13">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -98,6 +98,13 @@
       <color rgb="00292B2B"/>
       <sz val="9"/>
       <u val="single"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <color theme="10"/>
+      <sz val="12"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="12">
@@ -283,10 +290,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -391,9 +399,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -8366,11 +8376,31 @@
       <c r="E21" s="40" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="40" t="n"/>
-      <c r="B22" s="40" t="n"/>
-      <c r="C22" s="40" t="n"/>
-      <c r="D22" s="40" t="n"/>
-      <c r="E22" s="40" t="n"/>
+      <c r="A22" s="40" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B22" s="40" t="inlineStr">
+        <is>
+          <t>Client</t>
+        </is>
+      </c>
+      <c r="C22" s="40" t="inlineStr">
+        <is>
+          <t>Material Package FFE</t>
+        </is>
+      </c>
+      <c r="D22" s="40" t="inlineStr">
+        <is>
+          <t>Sent Valentine (design team) a request for stone reference images for three FFE stones (Calacatta Oro, Taj Mahal, Alabaster) — attached internet-sourced reference images based on the names she provided, purely to align on general visual direction before sample development.</t>
+        </is>
+      </c>
+      <c r="E22" s="44" t="inlineStr">
+        <is>
+          <t>Link</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="40" t="n"/>
@@ -8556,6 +8586,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E9" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E12" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E15" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E22" r:id="rId6"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/260729_K5M_Project Calendar.xlsx
+++ b/260729_K5M_Project Calendar.xlsx
@@ -8403,94 +8403,302 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="40" t="n"/>
-      <c r="B23" s="40" t="n"/>
-      <c r="C23" s="40" t="n"/>
-      <c r="D23" s="40" t="n"/>
+      <c r="A23" s="40" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B23" s="40" t="inlineStr">
+        <is>
+          <t>WDCO Internal PM</t>
+        </is>
+      </c>
+      <c r="C23" s="40" t="inlineStr">
+        <is>
+          <t>Project Scope</t>
+        </is>
+      </c>
+      <c r="D23" s="40" t="inlineStr">
+        <is>
+          <t>BOQ gap meeting held. Decided: Resti's stone arch calculation to be documented clearly and incorporated into the existing scope-gap findings.</t>
+        </is>
+      </c>
       <c r="E23" s="40" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="40" t="n"/>
-      <c r="B24" s="40" t="n"/>
-      <c r="C24" s="40" t="n"/>
-      <c r="D24" s="40" t="n"/>
+      <c r="A24" s="40" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B24" s="40" t="inlineStr">
+        <is>
+          <t>WDCO Internal PM</t>
+        </is>
+      </c>
+      <c r="C24" s="40" t="inlineStr">
+        <is>
+          <t>Communication Management - Internal</t>
+        </is>
+      </c>
+      <c r="D24" s="40" t="inlineStr">
+        <is>
+          <t>Decided to send a consolidated BOQ-changes email (the gap, the difference) to Filippo Sona (WDCO co-founder/main partner) to handle from there.</t>
+        </is>
+      </c>
       <c r="E24" s="40" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="40" t="n"/>
-      <c r="B25" s="40" t="n"/>
-      <c r="C25" s="40" t="n"/>
-      <c r="D25" s="40" t="n"/>
+      <c r="A25" s="40" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B25" s="40" t="inlineStr">
+        <is>
+          <t>WDCO Internal PM</t>
+        </is>
+      </c>
+      <c r="C25" s="40" t="inlineStr">
+        <is>
+          <t>Logistics</t>
+        </is>
+      </c>
+      <c r="D25" s="40" t="inlineStr">
+        <is>
+          <t>Decided to email Maria (WDCO logistics) for container requirements so booking can proceed right away.</t>
+        </is>
+      </c>
       <c r="E25" s="40" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="40" t="n"/>
-      <c r="B26" s="40" t="n"/>
-      <c r="C26" s="40" t="n"/>
-      <c r="D26" s="40" t="n"/>
+      <c r="A26" s="40" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B26" s="40" t="inlineStr">
+        <is>
+          <t>WDCO Internal PM</t>
+        </is>
+      </c>
+      <c r="C26" s="40" t="inlineStr">
+        <is>
+          <t>Project Scope</t>
+        </is>
+      </c>
+      <c r="D26" s="40" t="inlineStr">
+        <is>
+          <t>Decided to build a new Fitout Scope document — fully defined, with a "Doubts" section for removable/uncertain items. Resolves the long-pending Fitout base-scope file (Hard Rule 14).</t>
+        </is>
+      </c>
       <c r="E26" s="40" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="40" t="n"/>
-      <c r="B27" s="40" t="n"/>
-      <c r="C27" s="40" t="n"/>
-      <c r="D27" s="40" t="n"/>
+      <c r="A27" s="40" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B27" s="40" t="inlineStr">
+        <is>
+          <t>Supplier</t>
+        </is>
+      </c>
+      <c r="C27" s="40" t="inlineStr">
+        <is>
+          <t>Fitout SHD</t>
+        </is>
+      </c>
+      <c r="D27" s="40" t="inlineStr">
+        <is>
+          <t>Decided to schedule a fitout scope meeting with H&amp;T ASAP.</t>
+        </is>
+      </c>
       <c r="E27" s="40" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="40" t="n"/>
-      <c r="B28" s="40" t="n"/>
-      <c r="C28" s="40" t="n"/>
-      <c r="D28" s="40" t="n"/>
+      <c r="A28" s="40" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B28" s="40" t="inlineStr">
+        <is>
+          <t>Supplier</t>
+        </is>
+      </c>
+      <c r="C28" s="40" t="inlineStr">
+        <is>
+          <t>Fitout SHD</t>
+        </is>
+      </c>
+      <c r="D28" s="40" t="inlineStr">
+        <is>
+          <t>Ariel to confirm which fitout drawings are shareable — deadline 7 Aug.</t>
+        </is>
+      </c>
       <c r="E28" s="40" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="40" t="n"/>
-      <c r="B29" s="40" t="n"/>
-      <c r="C29" s="40" t="n"/>
-      <c r="D29" s="40" t="n"/>
+      <c r="A29" s="40" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B29" s="40" t="inlineStr">
+        <is>
+          <t>WDCO Internal PM</t>
+        </is>
+      </c>
+      <c r="C29" s="40" t="inlineStr">
+        <is>
+          <t>Site Survey Planning</t>
+        </is>
+      </c>
+      <c r="D29" s="40" t="inlineStr">
+        <is>
+          <t>Site visit timing remains under ambiguity; white-box photos and a post-site-survey deliverable required regardless.</t>
+        </is>
+      </c>
       <c r="E29" s="40" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="40" t="n"/>
-      <c r="B30" s="40" t="n"/>
-      <c r="C30" s="40" t="n"/>
-      <c r="D30" s="40" t="n"/>
+      <c r="A30" s="40" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B30" s="40" t="inlineStr">
+        <is>
+          <t>WDCO Internal PM</t>
+        </is>
+      </c>
+      <c r="C30" s="40" t="inlineStr">
+        <is>
+          <t>Compliance Collection</t>
+        </is>
+      </c>
+      <c r="D30" s="40" t="inlineStr">
+        <is>
+          <t>Decided to compile all compliance documents received into a single consolidated record.</t>
+        </is>
+      </c>
       <c r="E30" s="40" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="40" t="n"/>
-      <c r="B31" s="40" t="n"/>
-      <c r="C31" s="40" t="n"/>
-      <c r="D31" s="40" t="n"/>
+      <c r="A31" s="40" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B31" s="40" t="inlineStr">
+        <is>
+          <t>Client</t>
+        </is>
+      </c>
+      <c r="C31" s="40" t="inlineStr">
+        <is>
+          <t>Compliance Collection</t>
+        </is>
+      </c>
+      <c r="D31" s="40" t="inlineStr">
+        <is>
+          <t>Compliance documents request sent to Abdellatif Menbar (per Claire's direction); targeting close by 10 Aug.</t>
+        </is>
+      </c>
       <c r="E31" s="40" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="40" t="n"/>
-      <c r="B32" s="40" t="n"/>
-      <c r="C32" s="40" t="n"/>
-      <c r="D32" s="40" t="n"/>
+      <c r="A32" s="40" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B32" s="40" t="inlineStr">
+        <is>
+          <t>Client</t>
+        </is>
+      </c>
+      <c r="C32" s="40" t="inlineStr">
+        <is>
+          <t>Fitout SHD</t>
+        </is>
+      </c>
+      <c r="D32" s="40" t="inlineStr">
+        <is>
+          <t>Sent Abdellatif Menbar the substructure requirements per Claire's direction; further discussion ongoing via email with the client team.</t>
+        </is>
+      </c>
       <c r="E32" s="40" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="40" t="n"/>
-      <c r="B33" s="40" t="n"/>
-      <c r="C33" s="40" t="n"/>
-      <c r="D33" s="40" t="n"/>
+      <c r="A33" s="40" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B33" s="40" t="inlineStr">
+        <is>
+          <t>Client</t>
+        </is>
+      </c>
+      <c r="C33" s="40" t="inlineStr">
+        <is>
+          <t>Material Package FFE</t>
+        </is>
+      </c>
+      <c r="D33" s="40" t="inlineStr">
+        <is>
+          <t>Met with Khamille on sample development — agreed swatch quantities per material (Fitout: 5 Stone/3 Wood/4 Metal/4 Glass/3 Fabric/1 Seating; FFE: 2 Wood/5 Metal/2 Glass/3 Stone/10 Fabric) and swatch sizes (Fabric/Wood/Glass 14x10cm, Metal 10x7cm), plus a wood-swatch construction spec (real wood + associated veneer). Already shared with H&amp;T. Presentation concept for the swatch box still to be developed.</t>
+        </is>
+      </c>
       <c r="E33" s="40" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="40" t="n"/>
-      <c r="B34" s="40" t="n"/>
-      <c r="C34" s="40" t="n"/>
-      <c r="D34" s="40" t="n"/>
+      <c r="A34" s="40" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B34" s="40" t="inlineStr">
+        <is>
+          <t>WDCO Internal PM</t>
+        </is>
+      </c>
+      <c r="C34" s="40" t="inlineStr">
+        <is>
+          <t>FFE SHD</t>
+        </is>
+      </c>
+      <c r="D34" s="40" t="inlineStr">
+        <is>
+          <t>Internal FFE Shop Drawing (SHD01) review meeting held, 10:30am. MOM to follow.</t>
+        </is>
+      </c>
       <c r="E34" s="40" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="40" t="n"/>
-      <c r="B35" s="40" t="n"/>
-      <c r="C35" s="40" t="n"/>
-      <c r="D35" s="40" t="n"/>
+      <c r="A35" s="40" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B35" s="40" t="inlineStr">
+        <is>
+          <t>WDCO Internal PM</t>
+        </is>
+      </c>
+      <c r="C35" s="40" t="inlineStr">
+        <is>
+          <t>Project Scope</t>
+        </is>
+      </c>
+      <c r="D35" s="40" t="inlineStr">
+        <is>
+          <t>Resti completed the stone arch BOQ gap calculation requested — write-up still to follow.</t>
+        </is>
+      </c>
       <c r="E35" s="40" t="n"/>
     </row>
     <row r="36">
